--- a/data/inventario-limpo.xlsx
+++ b/data/inventario-limpo.xlsx
@@ -45,9 +45,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="R$ #,##0"/>
     <numFmt numFmtId="165" formatCode="R$ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="68">
     <font>
@@ -753,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1120,6 +1121,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="41" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="41" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1444,7 +1466,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Distribuicao do Patrimonio Atual</a:t>
+              <a:t>Distribuicao do Patrimonio por Categoria</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1456,6 +1478,11 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!D16</f>
+            </strRef>
+          </tx>
           <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -1551,27 +1578,24 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'DASHBOARD'!$N$17:$N$24</f>
+              <f>'DASHBOARD'!$X$17:$X$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DASHBOARD'!$E$17:$E$24</f>
+              <f>'DASHBOARD'!$D$17:$D$24</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
           <showVal val="0"/>
           <showCatName val="1"/>
-          <showPercent val="1"/>
+          <showPercent val="0"/>
           <showLeaderLines val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1627,12 +1651,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3600000"/>
+    <ext cx="3168000" cy="4140000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2481,7 +2505,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="90" t="inlineStr">
         <is>
-          <t>24 itens   |   Valor: R$ 30.811,49   |   Desgaste medio: 2,9/5</t>
+          <t>24 itens   |   Valor: R$ 34.050,41   |   Desgaste medio: 2,9/5</t>
         </is>
       </c>
     </row>
@@ -2603,13 +2627,14 @@
         </is>
       </c>
       <c r="J6" s="142" t="n">
-        <v>4199</v>
+        <v>2205</v>
       </c>
       <c r="K6" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L6" s="98" t="n">
-        <v>39</v>
+        <v>3581.65</v>
+      </c>
+      <c r="L6" s="98">
+        <f>IF(J6&gt;0,(J6-K6)/J6,"")</f>
+        <v/>
       </c>
       <c r="M6" s="99" t="inlineStr"/>
     </row>
@@ -2659,13 +2684,14 @@
         </is>
       </c>
       <c r="J8" s="141" t="n">
-        <v>567.4400000000001</v>
+        <v>950</v>
       </c>
       <c r="K8" s="143" t="n">
-        <v>221.3</v>
-      </c>
-      <c r="L8" s="101" t="n">
-        <v>39</v>
+        <v>1282.99</v>
+      </c>
+      <c r="L8" s="101">
+        <f>IF(J8&gt;0,(J8-K8)/J8,"")</f>
+        <v/>
       </c>
       <c r="M8" s="102" t="inlineStr"/>
     </row>
@@ -2722,10 +2748,11 @@
         <v>1499</v>
       </c>
       <c r="K10" s="143" t="n">
-        <v>584.61</v>
-      </c>
-      <c r="L10" s="98" t="n">
-        <v>39</v>
+        <v>1375.98</v>
+      </c>
+      <c r="L10" s="98">
+        <f>IF(J10&gt;0,(J10-K10)/J10,"")</f>
+        <v/>
       </c>
       <c r="M10" s="99" t="inlineStr"/>
     </row>
@@ -2775,10 +2802,11 @@
         <v>1499</v>
       </c>
       <c r="K11" s="143" t="n">
-        <v>584.61</v>
-      </c>
-      <c r="L11" s="101" t="n">
-        <v>39</v>
+        <v>1467.88</v>
+      </c>
+      <c r="L11" s="101">
+        <f>IF(J11&gt;0,(J11-K11)/J11,"")</f>
+        <v/>
       </c>
       <c r="M11" s="102" t="inlineStr"/>
     </row>
@@ -2828,10 +2856,11 @@
         <v>1499</v>
       </c>
       <c r="K12" s="143" t="n">
-        <v>584.61</v>
-      </c>
-      <c r="L12" s="98" t="n">
-        <v>39</v>
+        <v>1375.98</v>
+      </c>
+      <c r="L12" s="98">
+        <f>IF(J12&gt;0,(J12-K12)/J12,"")</f>
+        <v/>
       </c>
       <c r="M12" s="99" t="inlineStr"/>
     </row>
@@ -2884,10 +2913,11 @@
         <v>1790</v>
       </c>
       <c r="K14" s="143" t="n">
-        <v>698.1</v>
-      </c>
-      <c r="L14" s="101" t="n">
-        <v>39</v>
+        <v>2229.49</v>
+      </c>
+      <c r="L14" s="101">
+        <f>IF(J14&gt;0,(J14-K14)/J14,"")</f>
+        <v/>
       </c>
       <c r="M14" s="102" t="inlineStr"/>
     </row>
@@ -2941,13 +2971,14 @@
         </is>
       </c>
       <c r="J16" s="142" t="n">
-        <v>567.4400000000001</v>
+        <v>2205</v>
       </c>
       <c r="K16" s="143" t="n">
-        <v>221.3</v>
-      </c>
-      <c r="L16" s="98" t="n">
-        <v>39</v>
+        <v>3581.65</v>
+      </c>
+      <c r="L16" s="98">
+        <f>IF(J16&gt;0,(J16-K16)/J16,"")</f>
+        <v/>
       </c>
       <c r="M16" s="99" t="inlineStr"/>
     </row>
@@ -2994,13 +3025,14 @@
         </is>
       </c>
       <c r="J17" s="141" t="n">
-        <v>567.4400000000001</v>
+        <v>2250</v>
       </c>
       <c r="K17" s="143" t="n">
-        <v>221.3</v>
-      </c>
-      <c r="L17" s="101" t="n">
-        <v>39</v>
+        <v>2250</v>
+      </c>
+      <c r="L17" s="101">
+        <f>IF(J17&gt;0,(J17-K17)/J17,"")</f>
+        <v/>
       </c>
       <c r="M17" s="102" t="inlineStr"/>
     </row>
@@ -3053,10 +3085,11 @@
         <v>2770</v>
       </c>
       <c r="K19" s="143" t="n">
-        <v>720.2</v>
-      </c>
-      <c r="L19" s="98" t="n">
-        <v>26</v>
+        <v>1845</v>
+      </c>
+      <c r="L19" s="98">
+        <f>IF(J19&gt;0,(J19-K19)/J19,"")</f>
+        <v/>
       </c>
       <c r="M19" s="99" t="inlineStr"/>
     </row>
@@ -3102,10 +3135,11 @@
         <v>950</v>
       </c>
       <c r="K20" s="143" t="n">
-        <v>370.5</v>
-      </c>
-      <c r="L20" s="101" t="n">
-        <v>39</v>
+        <v>1190</v>
+      </c>
+      <c r="L20" s="101">
+        <f>IF(J20&gt;0,(J20-K20)/J20,"")</f>
+        <v/>
       </c>
       <c r="M20" s="102" t="inlineStr"/>
     </row>
@@ -3151,10 +3185,11 @@
         <v>4590</v>
       </c>
       <c r="K21" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L21" s="98" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L21" s="98">
+        <f>IF(J21&gt;0,(J21-K21)/J21,"")</f>
+        <v/>
       </c>
       <c r="M21" s="99" t="inlineStr"/>
     </row>
@@ -3200,10 +3235,11 @@
         <v>4590</v>
       </c>
       <c r="K22" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L22" s="101" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L22" s="101">
+        <f>IF(J22&gt;0,(J22-K22)/J22,"")</f>
+        <v/>
       </c>
       <c r="M22" s="102" t="inlineStr"/>
     </row>
@@ -3249,13 +3285,14 @@
         </is>
       </c>
       <c r="J24" s="142" t="n">
-        <v>567.4400000000001</v>
+        <v>950</v>
       </c>
       <c r="K24" s="143" t="n">
-        <v>221.3</v>
-      </c>
-      <c r="L24" s="98" t="n">
-        <v>39</v>
+        <v>1282.99</v>
+      </c>
+      <c r="L24" s="98">
+        <f>IF(J24&gt;0,(J24-K24)/J24,"")</f>
+        <v/>
       </c>
       <c r="M24" s="99" t="inlineStr"/>
     </row>
@@ -3308,10 +3345,11 @@
         <v>640</v>
       </c>
       <c r="K26" s="143" t="n">
-        <v>249.6</v>
-      </c>
-      <c r="L26" s="101" t="n">
-        <v>39</v>
+        <v>640</v>
+      </c>
+      <c r="L26" s="101">
+        <f>IF(J26&gt;0,(J26-K26)/J26,"")</f>
+        <v/>
       </c>
       <c r="M26" s="102" t="inlineStr"/>
     </row>
@@ -3365,13 +3403,14 @@
         </is>
       </c>
       <c r="J28" s="142" t="n">
-        <v>567.4400000000001</v>
+        <v>950</v>
       </c>
       <c r="K28" s="143" t="n">
-        <v>221.3</v>
-      </c>
-      <c r="L28" s="98" t="n">
-        <v>39</v>
+        <v>1282.99</v>
+      </c>
+      <c r="L28" s="98">
+        <f>IF(J28&gt;0,(J28-K28)/J28,"")</f>
+        <v/>
       </c>
       <c r="M28" s="99" t="inlineStr"/>
     </row>
@@ -3421,13 +3460,14 @@
         </is>
       </c>
       <c r="J30" s="141" t="n">
-        <v>567.4400000000001</v>
+        <v>950</v>
       </c>
       <c r="K30" s="143" t="n">
-        <v>221.3</v>
-      </c>
-      <c r="L30" s="101" t="n">
-        <v>39</v>
+        <v>1282.99</v>
+      </c>
+      <c r="L30" s="101">
+        <f>IF(J30&gt;0,(J30-K30)/J30,"")</f>
+        <v/>
       </c>
       <c r="M30" s="102" t="inlineStr"/>
     </row>
@@ -3481,13 +3521,14 @@
         </is>
       </c>
       <c r="J32" s="142" t="n">
-        <v>567.4400000000001</v>
+        <v>950</v>
       </c>
       <c r="K32" s="143" t="n">
-        <v>221.3</v>
-      </c>
-      <c r="L32" s="98" t="n">
-        <v>39</v>
+        <v>1282.99</v>
+      </c>
+      <c r="L32" s="98">
+        <f>IF(J32&gt;0,(J32-K32)/J32,"")</f>
+        <v/>
       </c>
       <c r="M32" s="99" t="inlineStr"/>
     </row>
@@ -3540,10 +3581,11 @@
         <v>640</v>
       </c>
       <c r="K34" s="143" t="n">
-        <v>249.6</v>
-      </c>
-      <c r="L34" s="101" t="n">
-        <v>39</v>
+        <v>640</v>
+      </c>
+      <c r="L34" s="101">
+        <f>IF(J34&gt;0,(J34-K34)/J34,"")</f>
+        <v/>
       </c>
       <c r="M34" s="102" t="inlineStr"/>
     </row>
@@ -3589,10 +3631,11 @@
         <v>640</v>
       </c>
       <c r="K35" s="143" t="n">
-        <v>249.6</v>
-      </c>
-      <c r="L35" s="98" t="n">
-        <v>39</v>
+        <v>640</v>
+      </c>
+      <c r="L35" s="98">
+        <f>IF(J35&gt;0,(J35-K35)/J35,"")</f>
+        <v/>
       </c>
       <c r="M35" s="99" t="inlineStr"/>
     </row>
@@ -3638,10 +3681,11 @@
         <v>640</v>
       </c>
       <c r="K36" s="143" t="n">
-        <v>249.6</v>
-      </c>
-      <c r="L36" s="101" t="n">
-        <v>39</v>
+        <v>640</v>
+      </c>
+      <c r="L36" s="101">
+        <f>IF(J36&gt;0,(J36-K36)/J36,"")</f>
+        <v/>
       </c>
       <c r="M36" s="102" t="inlineStr"/>
     </row>
@@ -3694,10 +3738,11 @@
         <v>249</v>
       </c>
       <c r="K38" s="143" t="n">
-        <v>97.11</v>
-      </c>
-      <c r="L38" s="98" t="n">
-        <v>39</v>
+        <v>289.98</v>
+      </c>
+      <c r="L38" s="98">
+        <f>IF(J38&gt;0,(J38-K38)/J38,"")</f>
+        <v/>
       </c>
       <c r="M38" s="99" t="inlineStr"/>
     </row>
@@ -3747,10 +3792,11 @@
         <v>70.2</v>
       </c>
       <c r="K39" s="143" t="n">
-        <v>27.38</v>
-      </c>
-      <c r="L39" s="101" t="n">
-        <v>39</v>
+        <v>70.2</v>
+      </c>
+      <c r="L39" s="101">
+        <f>IF(J39&gt;0,(J39-K39)/J39,"")</f>
+        <v/>
       </c>
       <c r="M39" s="102" t="inlineStr"/>
     </row>
@@ -3800,10 +3846,11 @@
         <v>79.33</v>
       </c>
       <c r="K40" s="143" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="L40" s="98" t="n">
-        <v>39</v>
+        <v>66.2</v>
+      </c>
+      <c r="L40" s="98">
+        <f>IF(J40&gt;0,(J40-K40)/J40,"")</f>
+        <v/>
       </c>
       <c r="M40" s="99" t="inlineStr"/>
     </row>
@@ -3860,10 +3907,11 @@
         <v>494.88</v>
       </c>
       <c r="K42" s="143" t="n">
-        <v>193</v>
-      </c>
-      <c r="L42" s="101" t="n">
-        <v>39</v>
+        <v>350</v>
+      </c>
+      <c r="L42" s="101">
+        <f>IF(J42&gt;0,(J42-K42)/J42,"")</f>
+        <v/>
       </c>
       <c r="M42" s="102" t="inlineStr">
         <is>
@@ -3907,8 +3955,8 @@
     <mergeCell ref="A46:M46"/>
     <mergeCell ref="A13:M13"/>
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A5:M5"/>
     <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A5:M5"/>
     <mergeCell ref="A27:M27"/>
     <mergeCell ref="A31:M31"/>
     <mergeCell ref="A37:M37"/>
@@ -8933,7 +8981,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="137" t="inlineStr">
         <is>
-          <t>MMD-AUD-0004</t>
+          <t>8 itens   |   Valor: R$ 24.090,78   |   Desgaste medio: 2,6/5</t>
         </is>
       </c>
       <c r="B2" s="58" t="inlineStr">
@@ -9034,10 +9082,11 @@
         <v>10710</v>
       </c>
       <c r="K3" s="143" t="n">
-        <v>2784.6</v>
-      </c>
-      <c r="L3" s="57" t="n">
-        <v>26</v>
+        <v>10710</v>
+      </c>
+      <c r="L3" s="57">
+        <f>IF(J3&gt;0,(J3-K3)/J3,"")</f>
+        <v/>
       </c>
       <c r="M3" s="102" t="inlineStr">
         <is>
@@ -9092,10 +9141,11 @@
         <v>850</v>
       </c>
       <c r="K4" s="143" t="n">
-        <v>331.5</v>
-      </c>
-      <c r="L4" s="62" t="n">
-        <v>39</v>
+        <v>850</v>
+      </c>
+      <c r="L4" s="62">
+        <f>IF(J4&gt;0,(J4-K4)/J4,"")</f>
+        <v/>
       </c>
       <c r="M4" s="99" t="inlineStr"/>
       <c r="N4" s="58" t="inlineStr">
@@ -9146,10 +9196,11 @@
         <v>850</v>
       </c>
       <c r="K5" s="143" t="n">
-        <v>331.5</v>
-      </c>
-      <c r="L5" s="57" t="n">
-        <v>39</v>
+        <v>850</v>
+      </c>
+      <c r="L5" s="57">
+        <f>IF(J5&gt;0,(J5-K5)/J5,"")</f>
+        <v/>
       </c>
       <c r="M5" s="102" t="inlineStr"/>
       <c r="N5" s="53" t="inlineStr">
@@ -9204,10 +9255,11 @@
         <v>1998</v>
       </c>
       <c r="K6" s="143" t="n">
-        <v>779.22</v>
-      </c>
-      <c r="L6" s="62" t="n">
-        <v>39</v>
+        <v>1593</v>
+      </c>
+      <c r="L6" s="62">
+        <f>IF(J6&gt;0,(J6-K6)/J6,"")</f>
+        <v/>
       </c>
       <c r="M6" s="99" t="inlineStr">
         <is>
@@ -9263,13 +9315,14 @@
         </is>
       </c>
       <c r="J7" s="141" t="n">
-        <v>2235.94</v>
+        <v>1117</v>
       </c>
       <c r="K7" s="143" t="n">
-        <v>872.02</v>
-      </c>
-      <c r="L7" s="57" t="n">
-        <v>39</v>
+        <v>1117</v>
+      </c>
+      <c r="L7" s="57">
+        <f>IF(J7&gt;0,(J7-K7)/J7,"")</f>
+        <v/>
       </c>
       <c r="M7" s="102" t="inlineStr"/>
       <c r="N7" s="53" t="inlineStr">
@@ -9324,10 +9377,11 @@
         <v>5325.88</v>
       </c>
       <c r="K8" s="143" t="n">
-        <v>2077.09</v>
-      </c>
-      <c r="L8" s="62" t="n">
-        <v>39</v>
+        <v>5325.88</v>
+      </c>
+      <c r="L8" s="62">
+        <f>IF(J8&gt;0,(J8-K8)/J8,"")</f>
+        <v/>
       </c>
       <c r="M8" s="99" t="inlineStr">
         <is>
@@ -9383,13 +9437,14 @@
         </is>
       </c>
       <c r="J9" s="141" t="n">
-        <v>10300</v>
+        <v>3000</v>
       </c>
       <c r="K9" s="143" t="n">
-        <v>4017</v>
-      </c>
-      <c r="L9" s="57" t="n">
-        <v>39</v>
+        <v>3000</v>
+      </c>
+      <c r="L9" s="57">
+        <f>IF(J9&gt;0,(J9-K9)/J9,"")</f>
+        <v/>
       </c>
       <c r="M9" s="102" t="inlineStr"/>
       <c r="N9" s="53" t="inlineStr">
@@ -9436,10 +9491,11 @@
         <v>239.9</v>
       </c>
       <c r="K10" s="143" t="n">
-        <v>31.19</v>
-      </c>
-      <c r="L10" s="62" t="n">
-        <v>13</v>
+        <v>331.55</v>
+      </c>
+      <c r="L10" s="62">
+        <f>IF(J10&gt;0,(J10-K10)/J10,"")</f>
+        <v/>
       </c>
       <c r="M10" s="99" t="inlineStr"/>
       <c r="N10" s="58" t="inlineStr">
@@ -9483,7 +9539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -9500,6 +9556,7 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -9520,11 +9577,11 @@
     <row r="4"/>
     <row r="5" ht="36" customHeight="1">
       <c r="B5" s="37" t="n">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E5" s="38" t="n"/>
       <c r="F5" s="40" t="n">
@@ -9566,11 +9623,11 @@
       </c>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="139" t="n">
-        <v>974094.53</v>
+        <v>796323.5</v>
       </c>
       <c r="E8" s="38" t="n"/>
       <c r="F8" s="140" t="n">
-        <v>394569.04</v>
+        <v>707348.99</v>
       </c>
       <c r="G8" s="38" t="n"/>
     </row>
@@ -9616,11 +9673,11 @@
         </is>
       </c>
       <c r="C12" s="48" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D12" s="49" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="E12" s="50" t="n">
@@ -9694,17 +9751,23 @@
         <v>270</v>
       </c>
       <c r="D17" s="141" t="n">
-        <v>273897.84</v>
-      </c>
-      <c r="E17" s="56" t="n">
-        <v>0.2811819916492089</v>
-      </c>
-      <c r="F17" s="57" t="n">
-        <v>0.1675842844284658</v>
+        <v>246366.48</v>
+      </c>
+      <c r="E17" s="146" t="n">
+        <v>198692.34</v>
+      </c>
+      <c r="F17" s="147" t="n">
+        <v>0.30937989397525</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>ILUMINACAO R$ 70.942</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>ILUMINACAO
+R$ 246.366,48</t>
         </is>
       </c>
     </row>
@@ -9719,17 +9782,23 @@
         <v>125</v>
       </c>
       <c r="D18" s="142" t="n">
-        <v>623704.25</v>
-      </c>
-      <c r="E18" s="61" t="n">
-        <v>0.6402912969853142</v>
-      </c>
-      <c r="F18" s="62" t="n">
-        <v>0.6901398509187291</v>
+        <v>446936.35</v>
+      </c>
+      <c r="E18" s="148" t="n">
+        <v>408059.94</v>
+      </c>
+      <c r="F18" s="149" t="n">
+        <v>0.5612497307940805</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>AUDIO R$ 292.151</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>AUDIO
+R$ 446.936,35</t>
         </is>
       </c>
     </row>
@@ -9744,17 +9813,23 @@
         <v>27</v>
       </c>
       <c r="D19" s="141" t="n">
-        <v>6233.08</v>
-      </c>
-      <c r="E19" s="56" t="n">
-        <v>0.006398845089500707</v>
-      </c>
-      <c r="F19" s="57" t="n">
-        <v>0</v>
+        <v>5785.73</v>
+      </c>
+      <c r="E19" s="146" t="n">
+        <v>4877.84</v>
+      </c>
+      <c r="F19" s="147" t="n">
+        <v>0.007265552253575337</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>CABO R$ 0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>ENERGIA
+R$ 5.785,73</t>
         </is>
       </c>
     </row>
@@ -9766,20 +9841,26 @@
         </is>
       </c>
       <c r="C20" s="58" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D20" s="142" t="n">
-        <v>17860.75</v>
-      </c>
-      <c r="E20" s="61" t="n">
-        <v>0.01833574612106691</v>
-      </c>
-      <c r="F20" s="62" t="n">
-        <v>0.03100591943537474</v>
+        <v>17629.93</v>
+      </c>
+      <c r="E20" s="148" t="n">
+        <v>14934.46</v>
+      </c>
+      <c r="F20" s="149" t="n">
+        <v>0.02213915575767888</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>ENERGIA R$ 13.125</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>ESTRUTURA
+R$ 17.629,93</t>
         </is>
       </c>
     </row>
@@ -9796,15 +9877,21 @@
       <c r="D21" s="141" t="n">
         <v>8441</v>
       </c>
-      <c r="E21" s="56" t="n">
-        <v>0.008665483420792847</v>
-      </c>
-      <c r="F21" s="57" t="n">
-        <v>0.05260360712743656</v>
+      <c r="E21" s="146" t="n">
+        <v>8349.15</v>
+      </c>
+      <c r="F21" s="147" t="n">
+        <v>0.01059996345706236</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>ESTRUTURA R$ 22.268</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>EFEITO
+R$ 8.441,00</t>
         </is>
       </c>
     </row>
@@ -9819,17 +9906,23 @@
         <v>9</v>
       </c>
       <c r="D22" s="142" t="n">
-        <v>13146.12</v>
-      </c>
-      <c r="E22" s="61" t="n">
-        <v>0.01349573331450696</v>
-      </c>
-      <c r="F22" s="62" t="n">
-        <v>0.005184389956004522</v>
+        <v>13022.82</v>
+      </c>
+      <c r="E22" s="148" t="n">
+        <v>15008.87</v>
+      </c>
+      <c r="F22" s="149" t="n">
+        <v>0.0163536803824074</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>EFEITO R$ 2.195</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>VIDEO
+R$ 13.022,82</t>
         </is>
       </c>
     </row>
@@ -9844,32 +9937,54 @@
         <v>24</v>
       </c>
       <c r="D23" s="141" t="n">
-        <v>30811.49</v>
-      </c>
-      <c r="E23" s="56" t="n">
-        <v>0.03163090341960959</v>
-      </c>
-      <c r="F23" s="57" t="n">
-        <v>0.0116911340851257</v>
+        <v>34050.41</v>
+      </c>
+      <c r="E23" s="146" t="n">
+        <v>33648.96</v>
+      </c>
+      <c r="F23" s="147" t="n">
+        <v>0.04275951921549472</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>VIDEO R$ 4.949</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>ACESSORIO
+R$ 34.050,41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="58" t="n"/>
-      <c r="B24" s="68" t="n"/>
-      <c r="C24" s="58" t="n"/>
-      <c r="D24" s="60" t="n"/>
-      <c r="E24" s="61" t="n"/>
-      <c r="F24" s="62" t="n">
-        <v>0.04179081404886384</v>
+      <c r="B24" s="68" t="inlineStr">
+        <is>
+          <t>FORA DE OPERACAO</t>
+        </is>
+      </c>
+      <c r="C24" s="58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="142" t="n">
+        <v>24090.78</v>
+      </c>
+      <c r="E24" s="148" t="n">
+        <v>23777.43</v>
+      </c>
+      <c r="F24" s="149" t="n">
+        <v>0.03025250416445075</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>ACESSORIO R$ 17.691</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>FORA DE OPERACAO
+R$ 24.090,78</t>
         </is>
       </c>
     </row>
@@ -9904,10 +10019,10 @@
         </is>
       </c>
       <c r="C28" s="70" t="n">
-        <v>1041</v>
-      </c>
-      <c r="D28" s="71" t="n">
-        <v>1</v>
+        <v>511</v>
+      </c>
+      <c r="D28" s="150" t="n">
+        <v>0.9845857418111753</v>
       </c>
     </row>
     <row r="29">
@@ -9919,7 +10034,7 @@
       <c r="C29" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="71" t="n">
+      <c r="D29" s="150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9932,7 +10047,7 @@
       <c r="C30" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="71" t="n">
+      <c r="D30" s="150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9945,7 +10060,7 @@
       <c r="C31" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="71" t="n">
+      <c r="D31" s="150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9987,7 +10102,7 @@
       <c r="A35" s="58" t="n"/>
       <c r="B35" s="75" t="inlineStr">
         <is>
-          <t>Pioneer XDJ-XZ PIONEER</t>
+          <t>XDJ-XZ PIONEER</t>
         </is>
       </c>
       <c r="C35" s="76" t="inlineStr">
@@ -9995,7 +10110,7 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D35" s="60" t="n">
+      <c r="D35" s="142" t="n">
         <v>22499.99</v>
       </c>
       <c r="E35" s="77" t="inlineStr">
@@ -10003,15 +10118,15 @@
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="F35" s="78" t="n">
-        <v>15299.99</v>
+      <c r="F35" s="151" t="n">
+        <v>15900</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="53" t="n"/>
       <c r="B36" s="79" t="inlineStr">
         <is>
-          <t>RCF 8003-AS II 2200W</t>
+          <t>8003-AS II 2200W</t>
         </is>
       </c>
       <c r="C36" s="80" t="inlineStr">
@@ -10019,7 +10134,7 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D36" s="55" t="n">
+      <c r="D36" s="141" t="n">
         <v>19990</v>
       </c>
       <c r="E36" s="77" t="inlineStr">
@@ -10027,15 +10142,15 @@
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="F36" s="81" t="n">
-        <v>13593.2</v>
+      <c r="F36" s="152" t="n">
+        <v>26246</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="58" t="n"/>
       <c r="B37" s="75" t="inlineStr">
         <is>
-          <t>Pioneer XDJ-RR PIONEER</t>
+          <t>XDJ-RR PIONEER</t>
         </is>
       </c>
       <c r="C37" s="76" t="inlineStr">
@@ -10043,7 +10158,7 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D37" s="60" t="n">
+      <c r="D37" s="142" t="n">
         <v>13997</v>
       </c>
       <c r="E37" s="77" t="inlineStr">
@@ -10051,15 +10166,15 @@
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="F37" s="78" t="n">
-        <v>9517.959999999999</v>
+      <c r="F37" s="151" t="n">
+        <v>11319</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="53" t="n"/>
       <c r="B38" s="79" t="inlineStr">
         <is>
-          <t>QSC KW181</t>
+          <t>KW181</t>
         </is>
       </c>
       <c r="C38" s="80" t="inlineStr">
@@ -10067,7 +10182,7 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D38" s="55" t="n">
+      <c r="D38" s="141" t="n">
         <v>13500</v>
       </c>
       <c r="E38" s="77" t="inlineStr">
@@ -10075,15 +10190,15 @@
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="F38" s="81" t="n">
-        <v>9180</v>
+      <c r="F38" s="152" t="n">
+        <v>13500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="58" t="n"/>
       <c r="B39" s="75" t="inlineStr">
         <is>
-          <t>QSC K12.2</t>
+          <t>X32 RACK</t>
         </is>
       </c>
       <c r="C39" s="76" t="inlineStr">
@@ -10091,23 +10206,23 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D39" s="60" t="n">
-        <v>12530</v>
+      <c r="D39" s="142" t="n">
+        <v>12900</v>
       </c>
       <c r="E39" s="82" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="F39" s="78" t="n">
-        <v>4886.7</v>
+      <c r="F39" s="151" t="n">
+        <v>10490</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="53" t="n"/>
       <c r="B40" s="79" t="inlineStr">
         <is>
-          <t>QSC K12.2</t>
+          <t>K12.2</t>
         </is>
       </c>
       <c r="C40" s="80" t="inlineStr">
@@ -10115,23 +10230,23 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D40" s="55" t="n">
+      <c r="D40" s="141" t="n">
         <v>12530</v>
       </c>
       <c r="E40" s="77" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="F40" s="81" t="n">
-        <v>8520.4</v>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="F40" s="152" t="n">
+        <v>8990</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="58" t="n"/>
       <c r="B41" s="75" t="inlineStr">
         <is>
-          <t>QSC K12.2</t>
+          <t>K12.2</t>
         </is>
       </c>
       <c r="C41" s="76" t="inlineStr">
@@ -10139,7 +10254,7 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D41" s="60" t="n">
+      <c r="D41" s="142" t="n">
         <v>12530</v>
       </c>
       <c r="E41" s="77" t="inlineStr">
@@ -10147,15 +10262,15 @@
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="F41" s="78" t="n">
-        <v>8520.4</v>
+      <c r="F41" s="151" t="n">
+        <v>8990</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="53" t="n"/>
       <c r="B42" s="79" t="inlineStr">
         <is>
-          <t>QSC K12.2</t>
+          <t>K12.2</t>
         </is>
       </c>
       <c r="C42" s="80" t="inlineStr">
@@ -10163,7 +10278,7 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D42" s="55" t="n">
+      <c r="D42" s="141" t="n">
         <v>12530</v>
       </c>
       <c r="E42" s="77" t="inlineStr">
@@ -10171,15 +10286,15 @@
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="F42" s="81" t="n">
-        <v>8520.4</v>
+      <c r="F42" s="152" t="n">
+        <v>8990</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="58" t="n"/>
       <c r="B43" s="75" t="inlineStr">
         <is>
-          <t>QSC K12.2</t>
+          <t>K12.2</t>
         </is>
       </c>
       <c r="C43" s="76" t="inlineStr">
@@ -10187,7 +10302,7 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D43" s="60" t="n">
+      <c r="D43" s="142" t="n">
         <v>12530</v>
       </c>
       <c r="E43" s="77" t="inlineStr">
@@ -10195,15 +10310,15 @@
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="F43" s="78" t="n">
-        <v>8520.4</v>
+      <c r="F43" s="151" t="n">
+        <v>8990</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="53" t="n"/>
       <c r="B44" s="79" t="inlineStr">
         <is>
-          <t>QSC K12.2</t>
+          <t>K12.2</t>
         </is>
       </c>
       <c r="C44" s="80" t="inlineStr">
@@ -10211,7 +10326,7 @@
           <t>AUDIO</t>
         </is>
       </c>
-      <c r="D44" s="55" t="n">
+      <c r="D44" s="141" t="n">
         <v>12530</v>
       </c>
       <c r="E44" s="77" t="inlineStr">
@@ -10219,8 +10334,8 @@
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="F44" s="81" t="n">
-        <v>8520.4</v>
+      <c r="F44" s="152" t="n">
+        <v>8990</v>
       </c>
     </row>
     <row r="46">
@@ -10426,7 +10541,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="90" t="inlineStr">
         <is>
-          <t>270 itens   |   Valor: R$ 273.897,84   |   Desgaste medio: 2,0/5</t>
+          <t>270 itens   |   Valor: R$ 246.366,48   |   Desgaste medio: 2,0/5</t>
         </is>
       </c>
     </row>
@@ -10547,10 +10662,11 @@
         <v>950</v>
       </c>
       <c r="K6" s="143" t="n">
-        <v>247</v>
-      </c>
-      <c r="L6" s="98" t="n">
-        <v>26</v>
+        <v>875</v>
+      </c>
+      <c r="L6" s="98">
+        <f>IF(J6&gt;0,(J6-K6)/J6,"")</f>
+        <v/>
       </c>
       <c r="M6" s="99" t="inlineStr"/>
     </row>
@@ -10596,10 +10712,11 @@
         <v>950</v>
       </c>
       <c r="K7" s="143" t="n">
-        <v>247</v>
-      </c>
-      <c r="L7" s="101" t="n">
-        <v>26</v>
+        <v>875</v>
+      </c>
+      <c r="L7" s="101">
+        <f>IF(J7&gt;0,(J7-K7)/J7,"")</f>
+        <v/>
       </c>
       <c r="M7" s="102" t="inlineStr"/>
     </row>
@@ -10645,10 +10762,11 @@
         <v>950</v>
       </c>
       <c r="K8" s="143" t="n">
-        <v>247</v>
-      </c>
-      <c r="L8" s="98" t="n">
-        <v>26</v>
+        <v>875</v>
+      </c>
+      <c r="L8" s="98">
+        <f>IF(J8&gt;0,(J8-K8)/J8,"")</f>
+        <v/>
       </c>
       <c r="M8" s="99" t="inlineStr"/>
     </row>
@@ -10694,10 +10812,11 @@
         <v>950</v>
       </c>
       <c r="K9" s="143" t="n">
-        <v>247</v>
-      </c>
-      <c r="L9" s="101" t="n">
-        <v>26</v>
+        <v>875</v>
+      </c>
+      <c r="L9" s="101">
+        <f>IF(J9&gt;0,(J9-K9)/J9,"")</f>
+        <v/>
       </c>
       <c r="M9" s="102" t="inlineStr"/>
     </row>
@@ -10743,10 +10862,11 @@
         <v>950</v>
       </c>
       <c r="K10" s="143" t="n">
-        <v>247</v>
-      </c>
-      <c r="L10" s="98" t="n">
-        <v>26</v>
+        <v>875</v>
+      </c>
+      <c r="L10" s="98">
+        <f>IF(J10&gt;0,(J10-K10)/J10,"")</f>
+        <v/>
       </c>
       <c r="M10" s="99" t="inlineStr"/>
     </row>
@@ -10792,10 +10912,11 @@
         <v>950</v>
       </c>
       <c r="K11" s="143" t="n">
-        <v>247</v>
-      </c>
-      <c r="L11" s="101" t="n">
-        <v>26</v>
+        <v>875</v>
+      </c>
+      <c r="L11" s="101">
+        <f>IF(J11&gt;0,(J11-K11)/J11,"")</f>
+        <v/>
       </c>
       <c r="M11" s="102" t="inlineStr"/>
     </row>
@@ -10848,10 +10969,11 @@
         <v>4590</v>
       </c>
       <c r="K13" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L13" s="98" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L13" s="98">
+        <f>IF(J13&gt;0,(J13-K13)/J13,"")</f>
+        <v/>
       </c>
       <c r="M13" s="99" t="inlineStr"/>
     </row>
@@ -10897,10 +11019,11 @@
         <v>4590</v>
       </c>
       <c r="K14" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L14" s="101" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L14" s="101">
+        <f>IF(J14&gt;0,(J14-K14)/J14,"")</f>
+        <v/>
       </c>
       <c r="M14" s="102" t="inlineStr"/>
     </row>
@@ -10946,10 +11069,11 @@
         <v>4590</v>
       </c>
       <c r="K15" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L15" s="98" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L15" s="98">
+        <f>IF(J15&gt;0,(J15-K15)/J15,"")</f>
+        <v/>
       </c>
       <c r="M15" s="99" t="inlineStr"/>
     </row>
@@ -10995,10 +11119,11 @@
         <v>4590</v>
       </c>
       <c r="K16" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L16" s="101" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L16" s="101">
+        <f>IF(J16&gt;0,(J16-K16)/J16,"")</f>
+        <v/>
       </c>
       <c r="M16" s="102" t="inlineStr"/>
     </row>
@@ -11044,10 +11169,11 @@
         <v>4590</v>
       </c>
       <c r="K17" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L17" s="98" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L17" s="98">
+        <f>IF(J17&gt;0,(J17-K17)/J17,"")</f>
+        <v/>
       </c>
       <c r="M17" s="99" t="inlineStr"/>
     </row>
@@ -11093,10 +11219,11 @@
         <v>4590</v>
       </c>
       <c r="K18" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L18" s="101" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L18" s="101">
+        <f>IF(J18&gt;0,(J18-K18)/J18,"")</f>
+        <v/>
       </c>
       <c r="M18" s="102" t="inlineStr"/>
     </row>
@@ -11142,10 +11269,11 @@
         <v>4590</v>
       </c>
       <c r="K19" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L19" s="98" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L19" s="98">
+        <f>IF(J19&gt;0,(J19-K19)/J19,"")</f>
+        <v/>
       </c>
       <c r="M19" s="99" t="inlineStr"/>
     </row>
@@ -11191,10 +11319,11 @@
         <v>4590</v>
       </c>
       <c r="K20" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L20" s="101" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L20" s="101">
+        <f>IF(J20&gt;0,(J20-K20)/J20,"")</f>
+        <v/>
       </c>
       <c r="M20" s="102" t="inlineStr"/>
     </row>
@@ -11240,10 +11369,11 @@
         <v>4590</v>
       </c>
       <c r="K21" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L21" s="98" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L21" s="98">
+        <f>IF(J21&gt;0,(J21-K21)/J21,"")</f>
+        <v/>
       </c>
       <c r="M21" s="99" t="inlineStr"/>
     </row>
@@ -11289,10 +11419,11 @@
         <v>4590</v>
       </c>
       <c r="K22" s="143" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="L22" s="101" t="n">
-        <v>26</v>
+        <v>2500</v>
+      </c>
+      <c r="L22" s="101">
+        <f>IF(J22&gt;0,(J22-K22)/J22,"")</f>
+        <v/>
       </c>
       <c r="M22" s="102" t="inlineStr"/>
     </row>
@@ -11345,10 +11476,11 @@
         <v>799</v>
       </c>
       <c r="K24" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L24" s="98" t="n">
-        <v>26</v>
+        <v>639</v>
+      </c>
+      <c r="L24" s="98">
+        <f>IF(J24&gt;0,(J24-K24)/J24,"")</f>
+        <v/>
       </c>
       <c r="M24" s="99" t="inlineStr"/>
     </row>
@@ -11397,10 +11529,11 @@
         <v>2224</v>
       </c>
       <c r="K26" s="143" t="n">
-        <v>578.24</v>
-      </c>
-      <c r="L26" s="101" t="n">
-        <v>26</v>
+        <v>2224</v>
+      </c>
+      <c r="L26" s="101">
+        <f>IF(J26&gt;0,(J26-K26)/J26,"")</f>
+        <v/>
       </c>
       <c r="M26" s="102" t="inlineStr"/>
     </row>
@@ -11449,10 +11582,11 @@
         <v>799</v>
       </c>
       <c r="K28" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L28" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L28" s="98">
+        <f>IF(J28&gt;0,(J28-K28)/J28,"")</f>
+        <v/>
       </c>
       <c r="M28" s="99" t="inlineStr"/>
     </row>
@@ -11494,10 +11628,11 @@
         <v>799</v>
       </c>
       <c r="K29" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L29" s="101" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L29" s="101">
+        <f>IF(J29&gt;0,(J29-K29)/J29,"")</f>
+        <v/>
       </c>
       <c r="M29" s="102" t="inlineStr"/>
     </row>
@@ -11550,10 +11685,11 @@
         <v>949</v>
       </c>
       <c r="K31" s="143" t="n">
-        <v>370.11</v>
-      </c>
-      <c r="L31" s="98" t="n">
-        <v>39</v>
+        <v>947.15</v>
+      </c>
+      <c r="L31" s="98">
+        <f>IF(J31&gt;0,(J31-K31)/J31,"")</f>
+        <v/>
       </c>
       <c r="M31" s="99" t="inlineStr"/>
     </row>
@@ -11606,10 +11742,11 @@
         <v>1200</v>
       </c>
       <c r="K33" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L33" s="101" t="n">
-        <v>26</v>
+        <v>120</v>
+      </c>
+      <c r="L33" s="101">
+        <f>IF(J33&gt;0,(J33-K33)/J33,"")</f>
+        <v/>
       </c>
       <c r="M33" s="102" t="inlineStr"/>
     </row>
@@ -11655,10 +11792,11 @@
         <v>1200</v>
       </c>
       <c r="K34" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L34" s="98" t="n">
-        <v>26</v>
+        <v>120</v>
+      </c>
+      <c r="L34" s="98">
+        <f>IF(J34&gt;0,(J34-K34)/J34,"")</f>
+        <v/>
       </c>
       <c r="M34" s="99" t="inlineStr"/>
     </row>
@@ -11704,10 +11842,11 @@
         <v>1200</v>
       </c>
       <c r="K35" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L35" s="101" t="n">
-        <v>26</v>
+        <v>120</v>
+      </c>
+      <c r="L35" s="101">
+        <f>IF(J35&gt;0,(J35-K35)/J35,"")</f>
+        <v/>
       </c>
       <c r="M35" s="102" t="inlineStr"/>
     </row>
@@ -11753,10 +11892,11 @@
         <v>1015</v>
       </c>
       <c r="K36" s="143" t="n">
-        <v>263.9</v>
-      </c>
-      <c r="L36" s="98" t="n">
-        <v>26</v>
+        <v>508.94</v>
+      </c>
+      <c r="L36" s="98">
+        <f>IF(J36&gt;0,(J36-K36)/J36,"")</f>
+        <v/>
       </c>
       <c r="M36" s="99" t="inlineStr"/>
     </row>
@@ -11802,10 +11942,11 @@
         <v>1200</v>
       </c>
       <c r="K37" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L37" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L37" s="101">
+        <f>IF(J37&gt;0,(J37-K37)/J37,"")</f>
+        <v/>
       </c>
       <c r="M37" s="102" t="inlineStr"/>
     </row>
@@ -11851,10 +11992,11 @@
         <v>1200</v>
       </c>
       <c r="K38" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L38" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L38" s="98">
+        <f>IF(J38&gt;0,(J38-K38)/J38,"")</f>
+        <v/>
       </c>
       <c r="M38" s="99" t="inlineStr"/>
     </row>
@@ -11900,10 +12042,11 @@
         <v>1200</v>
       </c>
       <c r="K39" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L39" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L39" s="101">
+        <f>IF(J39&gt;0,(J39-K39)/J39,"")</f>
+        <v/>
       </c>
       <c r="M39" s="102" t="inlineStr"/>
     </row>
@@ -11949,10 +12092,11 @@
         <v>1200</v>
       </c>
       <c r="K40" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L40" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L40" s="98">
+        <f>IF(J40&gt;0,(J40-K40)/J40,"")</f>
+        <v/>
       </c>
       <c r="M40" s="99" t="inlineStr"/>
     </row>
@@ -11998,10 +12142,11 @@
         <v>1200</v>
       </c>
       <c r="K41" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L41" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L41" s="101">
+        <f>IF(J41&gt;0,(J41-K41)/J41,"")</f>
+        <v/>
       </c>
       <c r="M41" s="102" t="inlineStr"/>
     </row>
@@ -12047,10 +12192,11 @@
         <v>1200</v>
       </c>
       <c r="K42" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L42" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L42" s="98">
+        <f>IF(J42&gt;0,(J42-K42)/J42,"")</f>
+        <v/>
       </c>
       <c r="M42" s="99" t="inlineStr"/>
     </row>
@@ -12096,10 +12242,11 @@
         <v>1200</v>
       </c>
       <c r="K43" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L43" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L43" s="101">
+        <f>IF(J43&gt;0,(J43-K43)/J43,"")</f>
+        <v/>
       </c>
       <c r="M43" s="102" t="inlineStr"/>
     </row>
@@ -12145,10 +12292,11 @@
         <v>1200</v>
       </c>
       <c r="K44" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L44" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L44" s="98">
+        <f>IF(J44&gt;0,(J44-K44)/J44,"")</f>
+        <v/>
       </c>
       <c r="M44" s="99" t="inlineStr"/>
     </row>
@@ -12194,10 +12342,11 @@
         <v>1200</v>
       </c>
       <c r="K45" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L45" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L45" s="101">
+        <f>IF(J45&gt;0,(J45-K45)/J45,"")</f>
+        <v/>
       </c>
       <c r="M45" s="102" t="inlineStr"/>
     </row>
@@ -12243,10 +12392,11 @@
         <v>1200</v>
       </c>
       <c r="K46" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L46" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L46" s="98">
+        <f>IF(J46&gt;0,(J46-K46)/J46,"")</f>
+        <v/>
       </c>
       <c r="M46" s="99" t="inlineStr"/>
     </row>
@@ -12292,10 +12442,11 @@
         <v>1200</v>
       </c>
       <c r="K47" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L47" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L47" s="101">
+        <f>IF(J47&gt;0,(J47-K47)/J47,"")</f>
+        <v/>
       </c>
       <c r="M47" s="102" t="inlineStr"/>
     </row>
@@ -12341,10 +12492,11 @@
         <v>1200</v>
       </c>
       <c r="K48" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L48" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L48" s="98">
+        <f>IF(J48&gt;0,(J48-K48)/J48,"")</f>
+        <v/>
       </c>
       <c r="M48" s="99" t="inlineStr"/>
     </row>
@@ -12390,10 +12542,11 @@
         <v>1200</v>
       </c>
       <c r="K49" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L49" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L49" s="101">
+        <f>IF(J49&gt;0,(J49-K49)/J49,"")</f>
+        <v/>
       </c>
       <c r="M49" s="102" t="inlineStr"/>
     </row>
@@ -12439,10 +12592,11 @@
         <v>1200</v>
       </c>
       <c r="K50" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L50" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L50" s="98">
+        <f>IF(J50&gt;0,(J50-K50)/J50,"")</f>
+        <v/>
       </c>
       <c r="M50" s="99" t="inlineStr"/>
     </row>
@@ -12488,10 +12642,11 @@
         <v>1200</v>
       </c>
       <c r="K51" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L51" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L51" s="101">
+        <f>IF(J51&gt;0,(J51-K51)/J51,"")</f>
+        <v/>
       </c>
       <c r="M51" s="102" t="inlineStr"/>
     </row>
@@ -12537,10 +12692,11 @@
         <v>1200</v>
       </c>
       <c r="K52" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L52" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L52" s="98">
+        <f>IF(J52&gt;0,(J52-K52)/J52,"")</f>
+        <v/>
       </c>
       <c r="M52" s="99" t="inlineStr"/>
     </row>
@@ -12586,10 +12742,11 @@
         <v>1200</v>
       </c>
       <c r="K53" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L53" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L53" s="101">
+        <f>IF(J53&gt;0,(J53-K53)/J53,"")</f>
+        <v/>
       </c>
       <c r="M53" s="102" t="inlineStr"/>
     </row>
@@ -12635,10 +12792,11 @@
         <v>1200</v>
       </c>
       <c r="K54" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L54" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L54" s="98">
+        <f>IF(J54&gt;0,(J54-K54)/J54,"")</f>
+        <v/>
       </c>
       <c r="M54" s="99" t="inlineStr"/>
     </row>
@@ -12684,10 +12842,11 @@
         <v>1200</v>
       </c>
       <c r="K55" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L55" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L55" s="101">
+        <f>IF(J55&gt;0,(J55-K55)/J55,"")</f>
+        <v/>
       </c>
       <c r="M55" s="102" t="inlineStr"/>
     </row>
@@ -12733,10 +12892,11 @@
         <v>1200</v>
       </c>
       <c r="K56" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L56" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L56" s="98">
+        <f>IF(J56&gt;0,(J56-K56)/J56,"")</f>
+        <v/>
       </c>
       <c r="M56" s="99" t="inlineStr"/>
     </row>
@@ -12782,10 +12942,11 @@
         <v>1200</v>
       </c>
       <c r="K57" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L57" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L57" s="101">
+        <f>IF(J57&gt;0,(J57-K57)/J57,"")</f>
+        <v/>
       </c>
       <c r="M57" s="102" t="inlineStr"/>
     </row>
@@ -12831,10 +12992,11 @@
         <v>1200</v>
       </c>
       <c r="K58" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L58" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L58" s="98">
+        <f>IF(J58&gt;0,(J58-K58)/J58,"")</f>
+        <v/>
       </c>
       <c r="M58" s="99" t="inlineStr"/>
     </row>
@@ -12880,10 +13042,11 @@
         <v>1200</v>
       </c>
       <c r="K59" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L59" s="101" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L59" s="101">
+        <f>IF(J59&gt;0,(J59-K59)/J59,"")</f>
+        <v/>
       </c>
       <c r="M59" s="102" t="inlineStr"/>
     </row>
@@ -12929,10 +13092,11 @@
         <v>1200</v>
       </c>
       <c r="K60" s="143" t="n">
-        <v>312</v>
-      </c>
-      <c r="L60" s="98" t="n">
-        <v>26</v>
+        <v>819.99</v>
+      </c>
+      <c r="L60" s="98">
+        <f>IF(J60&gt;0,(J60-K60)/J60,"")</f>
+        <v/>
       </c>
       <c r="M60" s="99" t="inlineStr"/>
     </row>
@@ -12978,10 +13142,11 @@
         <v>830</v>
       </c>
       <c r="K61" s="143" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="L61" s="101" t="n">
-        <v>26</v>
+        <v>830</v>
+      </c>
+      <c r="L61" s="101">
+        <f>IF(J61&gt;0,(J61-K61)/J61,"")</f>
+        <v/>
       </c>
       <c r="M61" s="102" t="inlineStr"/>
     </row>
@@ -13027,10 +13192,11 @@
         <v>830</v>
       </c>
       <c r="K62" s="143" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="L62" s="98" t="n">
-        <v>26</v>
+        <v>197.88</v>
+      </c>
+      <c r="L62" s="98">
+        <f>IF(J62&gt;0,(J62-K62)/J62,"")</f>
+        <v/>
       </c>
       <c r="M62" s="99" t="inlineStr"/>
     </row>
@@ -13076,10 +13242,11 @@
         <v>830</v>
       </c>
       <c r="K63" s="143" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="L63" s="101" t="n">
-        <v>26</v>
+        <v>197.88</v>
+      </c>
+      <c r="L63" s="101">
+        <f>IF(J63&gt;0,(J63-K63)/J63,"")</f>
+        <v/>
       </c>
       <c r="M63" s="102" t="inlineStr"/>
     </row>
@@ -13121,10 +13288,11 @@
         <v>1015</v>
       </c>
       <c r="K64" s="143" t="n">
-        <v>263.9</v>
-      </c>
-      <c r="L64" s="98" t="n">
-        <v>26</v>
+        <v>508.94</v>
+      </c>
+      <c r="L64" s="98">
+        <f>IF(J64&gt;0,(J64-K64)/J64,"")</f>
+        <v/>
       </c>
       <c r="M64" s="99" t="inlineStr"/>
     </row>
@@ -13166,10 +13334,11 @@
         <v>1015</v>
       </c>
       <c r="K65" s="143" t="n">
-        <v>263.9</v>
-      </c>
-      <c r="L65" s="101" t="n">
-        <v>26</v>
+        <v>508.94</v>
+      </c>
+      <c r="L65" s="101">
+        <f>IF(J65&gt;0,(J65-K65)/J65,"")</f>
+        <v/>
       </c>
       <c r="M65" s="102" t="inlineStr"/>
     </row>
@@ -13211,10 +13380,11 @@
         <v>1015</v>
       </c>
       <c r="K66" s="143" t="n">
-        <v>263.9</v>
-      </c>
-      <c r="L66" s="98" t="n">
-        <v>26</v>
+        <v>508.94</v>
+      </c>
+      <c r="L66" s="98">
+        <f>IF(J66&gt;0,(J66-K66)/J66,"")</f>
+        <v/>
       </c>
       <c r="M66" s="99" t="inlineStr"/>
     </row>
@@ -13260,10 +13430,11 @@
         <v>830</v>
       </c>
       <c r="K67" s="143" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="L67" s="101" t="n">
-        <v>26</v>
+        <v>830</v>
+      </c>
+      <c r="L67" s="101">
+        <f>IF(J67&gt;0,(J67-K67)/J67,"")</f>
+        <v/>
       </c>
       <c r="M67" s="102" t="inlineStr"/>
     </row>
@@ -13309,10 +13480,11 @@
         <v>830</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="L68" s="98" t="n">
-        <v>26</v>
+        <v>830</v>
+      </c>
+      <c r="L68" s="98">
+        <f>IF(J68&gt;0,(J68-K68)/J68,"")</f>
+        <v/>
       </c>
       <c r="M68" s="99" t="inlineStr"/>
     </row>
@@ -13358,10 +13530,11 @@
         <v>830</v>
       </c>
       <c r="K69" s="143" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="L69" s="101" t="n">
-        <v>26</v>
+        <v>197.88</v>
+      </c>
+      <c r="L69" s="101">
+        <f>IF(J69&gt;0,(J69-K69)/J69,"")</f>
+        <v/>
       </c>
       <c r="M69" s="102" t="inlineStr"/>
     </row>
@@ -13411,13 +13584,14 @@
         </is>
       </c>
       <c r="J71" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K71" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L71" s="98" t="n">
-        <v>26</v>
+        <v>560</v>
+      </c>
+      <c r="L71" s="98">
+        <f>IF(J71&gt;0,(J71-K71)/J71,"")</f>
+        <v/>
       </c>
       <c r="M71" s="99" t="inlineStr"/>
     </row>
@@ -13463,10 +13637,11 @@
         <v>320</v>
       </c>
       <c r="K72" s="143" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="L72" s="101" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L72" s="101">
+        <f>IF(J72&gt;0,(J72-K72)/J72,"")</f>
+        <v/>
       </c>
       <c r="M72" s="102" t="inlineStr"/>
     </row>
@@ -13512,10 +13687,11 @@
         <v>320</v>
       </c>
       <c r="K73" s="143" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="L73" s="98" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L73" s="98">
+        <f>IF(J73&gt;0,(J73-K73)/J73,"")</f>
+        <v/>
       </c>
       <c r="M73" s="99" t="inlineStr"/>
     </row>
@@ -13558,13 +13734,14 @@
         </is>
       </c>
       <c r="J74" s="141" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K74" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L74" s="101" t="n">
-        <v>26</v>
+        <v>560</v>
+      </c>
+      <c r="L74" s="101">
+        <f>IF(J74&gt;0,(J74-K74)/J74,"")</f>
+        <v/>
       </c>
       <c r="M74" s="102" t="inlineStr"/>
     </row>
@@ -13614,10 +13791,11 @@
         <v>289</v>
       </c>
       <c r="K75" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L75" s="98" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L75" s="98">
+        <f>IF(J75&gt;0,(J75-K75)/J75,"")</f>
+        <v/>
       </c>
       <c r="M75" s="99" t="inlineStr"/>
     </row>
@@ -13663,10 +13841,11 @@
         <v>660</v>
       </c>
       <c r="K76" s="143" t="n">
-        <v>171.6</v>
-      </c>
-      <c r="L76" s="101" t="n">
-        <v>26</v>
+        <v>290</v>
+      </c>
+      <c r="L76" s="101">
+        <f>IF(J76&gt;0,(J76-K76)/J76,"")</f>
+        <v/>
       </c>
       <c r="M76" s="102" t="inlineStr"/>
     </row>
@@ -13712,10 +13891,11 @@
         <v>660</v>
       </c>
       <c r="K77" s="143" t="n">
-        <v>171.6</v>
-      </c>
-      <c r="L77" s="98" t="n">
-        <v>26</v>
+        <v>290</v>
+      </c>
+      <c r="L77" s="98">
+        <f>IF(J77&gt;0,(J77-K77)/J77,"")</f>
+        <v/>
       </c>
       <c r="M77" s="99" t="inlineStr"/>
     </row>
@@ -13761,10 +13941,11 @@
         <v>660</v>
       </c>
       <c r="K78" s="143" t="n">
-        <v>171.6</v>
-      </c>
-      <c r="L78" s="101" t="n">
-        <v>26</v>
+        <v>290</v>
+      </c>
+      <c r="L78" s="101">
+        <f>IF(J78&gt;0,(J78-K78)/J78,"")</f>
+        <v/>
       </c>
       <c r="M78" s="102" t="inlineStr"/>
     </row>
@@ -13810,10 +13991,11 @@
         <v>450</v>
       </c>
       <c r="K79" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L79" s="98" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L79" s="98">
+        <f>IF(J79&gt;0,(J79-K79)/J79,"")</f>
+        <v/>
       </c>
       <c r="M79" s="99" t="inlineStr"/>
     </row>
@@ -13859,10 +14041,11 @@
         <v>450</v>
       </c>
       <c r="K80" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L80" s="101" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L80" s="101">
+        <f>IF(J80&gt;0,(J80-K80)/J80,"")</f>
+        <v/>
       </c>
       <c r="M80" s="102" t="inlineStr"/>
     </row>
@@ -13908,10 +14091,11 @@
         <v>450</v>
       </c>
       <c r="K81" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L81" s="98" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L81" s="98">
+        <f>IF(J81&gt;0,(J81-K81)/J81,"")</f>
+        <v/>
       </c>
       <c r="M81" s="99" t="inlineStr"/>
     </row>
@@ -13957,10 +14141,11 @@
         <v>450</v>
       </c>
       <c r="K82" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L82" s="101" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L82" s="101">
+        <f>IF(J82&gt;0,(J82-K82)/J82,"")</f>
+        <v/>
       </c>
       <c r="M82" s="102" t="inlineStr"/>
     </row>
@@ -14006,10 +14191,11 @@
         <v>450</v>
       </c>
       <c r="K83" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L83" s="98" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L83" s="98">
+        <f>IF(J83&gt;0,(J83-K83)/J83,"")</f>
+        <v/>
       </c>
       <c r="M83" s="99" t="inlineStr"/>
     </row>
@@ -14052,13 +14238,14 @@
         </is>
       </c>
       <c r="J84" s="141" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K84" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L84" s="101" t="n">
-        <v>26</v>
+        <v>560</v>
+      </c>
+      <c r="L84" s="101">
+        <f>IF(J84&gt;0,(J84-K84)/J84,"")</f>
+        <v/>
       </c>
       <c r="M84" s="102" t="inlineStr"/>
     </row>
@@ -14104,10 +14291,11 @@
         <v>320</v>
       </c>
       <c r="K85" s="143" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="L85" s="98" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L85" s="98">
+        <f>IF(J85&gt;0,(J85-K85)/J85,"")</f>
+        <v/>
       </c>
       <c r="M85" s="99" t="inlineStr"/>
     </row>
@@ -14153,10 +14341,11 @@
         <v>450</v>
       </c>
       <c r="K86" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L86" s="101" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L86" s="101">
+        <f>IF(J86&gt;0,(J86-K86)/J86,"")</f>
+        <v/>
       </c>
       <c r="M86" s="102" t="inlineStr"/>
     </row>
@@ -14199,13 +14388,14 @@
         </is>
       </c>
       <c r="J87" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K87" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L87" s="98" t="n">
-        <v>26</v>
+        <v>560</v>
+      </c>
+      <c r="L87" s="98">
+        <f>IF(J87&gt;0,(J87-K87)/J87,"")</f>
+        <v/>
       </c>
       <c r="M87" s="99" t="inlineStr"/>
     </row>
@@ -14252,13 +14442,14 @@
         </is>
       </c>
       <c r="J88" s="141" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K88" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L88" s="101" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L88" s="101">
+        <f>IF(J88&gt;0,(J88-K88)/J88,"")</f>
+        <v/>
       </c>
       <c r="M88" s="102" t="inlineStr"/>
     </row>
@@ -14305,13 +14496,14 @@
         </is>
       </c>
       <c r="J89" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K89" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L89" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L89" s="98">
+        <f>IF(J89&gt;0,(J89-K89)/J89,"")</f>
+        <v/>
       </c>
       <c r="M89" s="99" t="inlineStr"/>
     </row>
@@ -14350,13 +14542,14 @@
         </is>
       </c>
       <c r="J90" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K90" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L90" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L90" s="101">
+        <f>IF(J90&gt;0,(J90-K90)/J90,"")</f>
+        <v/>
       </c>
       <c r="M90" s="102" t="inlineStr"/>
     </row>
@@ -14399,13 +14592,14 @@
         </is>
       </c>
       <c r="J91" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K91" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L91" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L91" s="98">
+        <f>IF(J91&gt;0,(J91-K91)/J91,"")</f>
+        <v/>
       </c>
       <c r="M91" s="99" t="inlineStr"/>
     </row>
@@ -14448,13 +14642,14 @@
         </is>
       </c>
       <c r="J92" s="141" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K92" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L92" s="101" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L92" s="101">
+        <f>IF(J92&gt;0,(J92-K92)/J92,"")</f>
+        <v/>
       </c>
       <c r="M92" s="102" t="inlineStr"/>
     </row>
@@ -14497,13 +14692,14 @@
         </is>
       </c>
       <c r="J93" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K93" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L93" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L93" s="98">
+        <f>IF(J93&gt;0,(J93-K93)/J93,"")</f>
+        <v/>
       </c>
       <c r="M93" s="99" t="inlineStr"/>
     </row>
@@ -14546,13 +14742,14 @@
         </is>
       </c>
       <c r="J94" s="141" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K94" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L94" s="101" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L94" s="101">
+        <f>IF(J94&gt;0,(J94-K94)/J94,"")</f>
+        <v/>
       </c>
       <c r="M94" s="102" t="inlineStr"/>
     </row>
@@ -14595,13 +14792,14 @@
         </is>
       </c>
       <c r="J95" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K95" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L95" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L95" s="98">
+        <f>IF(J95&gt;0,(J95-K95)/J95,"")</f>
+        <v/>
       </c>
       <c r="M95" s="99" t="inlineStr"/>
     </row>
@@ -14644,13 +14842,14 @@
         </is>
       </c>
       <c r="J96" s="141" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K96" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L96" s="101" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L96" s="101">
+        <f>IF(J96&gt;0,(J96-K96)/J96,"")</f>
+        <v/>
       </c>
       <c r="M96" s="102" t="inlineStr"/>
     </row>
@@ -14693,13 +14892,14 @@
         </is>
       </c>
       <c r="J97" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K97" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L97" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L97" s="98">
+        <f>IF(J97&gt;0,(J97-K97)/J97,"")</f>
+        <v/>
       </c>
       <c r="M97" s="99" t="inlineStr"/>
     </row>
@@ -14742,13 +14942,14 @@
         </is>
       </c>
       <c r="J98" s="141" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K98" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L98" s="101" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L98" s="101">
+        <f>IF(J98&gt;0,(J98-K98)/J98,"")</f>
+        <v/>
       </c>
       <c r="M98" s="102" t="inlineStr"/>
     </row>
@@ -14791,13 +14992,14 @@
         </is>
       </c>
       <c r="J99" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K99" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L99" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L99" s="98">
+        <f>IF(J99&gt;0,(J99-K99)/J99,"")</f>
+        <v/>
       </c>
       <c r="M99" s="99" t="inlineStr"/>
     </row>
@@ -14843,10 +15045,11 @@
         <v>799</v>
       </c>
       <c r="K100" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L100" s="101" t="n">
-        <v>26</v>
+        <v>637.1799999999999</v>
+      </c>
+      <c r="L100" s="101">
+        <f>IF(J100&gt;0,(J100-K100)/J100,"")</f>
+        <v/>
       </c>
       <c r="M100" s="102" t="inlineStr"/>
     </row>
@@ -14889,13 +15092,14 @@
         </is>
       </c>
       <c r="J101" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K101" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L101" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L101" s="98">
+        <f>IF(J101&gt;0,(J101-K101)/J101,"")</f>
+        <v/>
       </c>
       <c r="M101" s="99" t="inlineStr"/>
     </row>
@@ -14945,10 +15149,11 @@
         <v>799</v>
       </c>
       <c r="K102" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L102" s="101" t="n">
-        <v>26</v>
+        <v>844.7</v>
+      </c>
+      <c r="L102" s="101">
+        <f>IF(J102&gt;0,(J102-K102)/J102,"")</f>
+        <v/>
       </c>
       <c r="M102" s="102" t="inlineStr"/>
     </row>
@@ -14998,10 +15203,11 @@
         <v>799</v>
       </c>
       <c r="K103" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L103" s="98" t="n">
-        <v>26</v>
+        <v>844.7</v>
+      </c>
+      <c r="L103" s="98">
+        <f>IF(J103&gt;0,(J103-K103)/J103,"")</f>
+        <v/>
       </c>
       <c r="M103" s="99" t="inlineStr"/>
     </row>
@@ -15051,10 +15257,11 @@
         <v>799</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L104" s="101" t="n">
-        <v>26</v>
+        <v>844.7</v>
+      </c>
+      <c r="L104" s="101">
+        <f>IF(J104&gt;0,(J104-K104)/J104,"")</f>
+        <v/>
       </c>
       <c r="M104" s="102" t="inlineStr"/>
     </row>
@@ -15104,10 +15311,11 @@
         <v>799</v>
       </c>
       <c r="K105" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L105" s="98" t="n">
-        <v>26</v>
+        <v>844.7</v>
+      </c>
+      <c r="L105" s="98">
+        <f>IF(J105&gt;0,(J105-K105)/J105,"")</f>
+        <v/>
       </c>
       <c r="M105" s="99" t="inlineStr"/>
     </row>
@@ -15157,10 +15365,11 @@
         <v>799</v>
       </c>
       <c r="K106" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L106" s="101" t="n">
-        <v>26</v>
+        <v>844.7</v>
+      </c>
+      <c r="L106" s="101">
+        <f>IF(J106&gt;0,(J106-K106)/J106,"")</f>
+        <v/>
       </c>
       <c r="M106" s="102" t="inlineStr"/>
     </row>
@@ -15210,10 +15419,11 @@
         <v>799</v>
       </c>
       <c r="K107" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L107" s="98" t="n">
-        <v>26</v>
+        <v>844.7</v>
+      </c>
+      <c r="L107" s="98">
+        <f>IF(J107&gt;0,(J107-K107)/J107,"")</f>
+        <v/>
       </c>
       <c r="M107" s="99" t="inlineStr"/>
     </row>
@@ -15263,10 +15473,11 @@
         <v>799</v>
       </c>
       <c r="K108" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L108" s="101" t="n">
-        <v>26</v>
+        <v>844.7</v>
+      </c>
+      <c r="L108" s="101">
+        <f>IF(J108&gt;0,(J108-K108)/J108,"")</f>
+        <v/>
       </c>
       <c r="M108" s="102" t="inlineStr"/>
     </row>
@@ -15309,13 +15520,14 @@
         </is>
       </c>
       <c r="J109" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K109" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L109" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L109" s="98">
+        <f>IF(J109&gt;0,(J109-K109)/J109,"")</f>
+        <v/>
       </c>
       <c r="M109" s="99" t="inlineStr"/>
     </row>
@@ -15358,13 +15570,14 @@
         </is>
       </c>
       <c r="J110" s="141" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K110" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L110" s="101" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L110" s="101">
+        <f>IF(J110&gt;0,(J110-K110)/J110,"")</f>
+        <v/>
       </c>
       <c r="M110" s="102" t="inlineStr"/>
     </row>
@@ -15410,10 +15623,11 @@
         <v>450</v>
       </c>
       <c r="K111" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L111" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L111" s="98">
+        <f>IF(J111&gt;0,(J111-K111)/J111,"")</f>
+        <v/>
       </c>
       <c r="M111" s="99" t="inlineStr"/>
     </row>
@@ -15459,10 +15673,11 @@
         <v>450</v>
       </c>
       <c r="K112" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L112" s="101" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L112" s="101">
+        <f>IF(J112&gt;0,(J112-K112)/J112,"")</f>
+        <v/>
       </c>
       <c r="M112" s="102" t="inlineStr"/>
     </row>
@@ -15508,10 +15723,11 @@
         <v>450</v>
       </c>
       <c r="K113" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L113" s="98" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L113" s="98">
+        <f>IF(J113&gt;0,(J113-K113)/J113,"")</f>
+        <v/>
       </c>
       <c r="M113" s="99" t="inlineStr"/>
     </row>
@@ -15557,10 +15773,11 @@
         <v>450</v>
       </c>
       <c r="K114" s="143" t="n">
-        <v>117</v>
-      </c>
-      <c r="L114" s="101" t="n">
-        <v>26</v>
+        <v>320</v>
+      </c>
+      <c r="L114" s="101">
+        <f>IF(J114&gt;0,(J114-K114)/J114,"")</f>
+        <v/>
       </c>
       <c r="M114" s="102" t="inlineStr"/>
     </row>
@@ -15603,13 +15820,14 @@
         </is>
       </c>
       <c r="J115" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K115" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L115" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L115" s="98">
+        <f>IF(J115&gt;0,(J115-K115)/J115,"")</f>
+        <v/>
       </c>
       <c r="M115" s="99" t="inlineStr"/>
     </row>
@@ -15648,13 +15866,14 @@
         </is>
       </c>
       <c r="J116" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K116" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L116" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L116" s="101">
+        <f>IF(J116&gt;0,(J116-K116)/J116,"")</f>
+        <v/>
       </c>
       <c r="M116" s="102" t="inlineStr"/>
     </row>
@@ -15693,13 +15912,14 @@
         </is>
       </c>
       <c r="J117" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K117" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L117" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L117" s="98">
+        <f>IF(J117&gt;0,(J117-K117)/J117,"")</f>
+        <v/>
       </c>
       <c r="M117" s="99" t="inlineStr"/>
     </row>
@@ -15742,13 +15962,14 @@
         </is>
       </c>
       <c r="J118" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K118" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L118" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L118" s="101">
+        <f>IF(J118&gt;0,(J118-K118)/J118,"")</f>
+        <v/>
       </c>
       <c r="M118" s="102" t="inlineStr"/>
     </row>
@@ -15791,13 +16012,14 @@
         </is>
       </c>
       <c r="J119" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K119" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L119" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L119" s="98">
+        <f>IF(J119&gt;0,(J119-K119)/J119,"")</f>
+        <v/>
       </c>
       <c r="M119" s="99" t="inlineStr"/>
     </row>
@@ -15840,13 +16062,14 @@
         </is>
       </c>
       <c r="J120" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K120" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L120" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L120" s="101">
+        <f>IF(J120&gt;0,(J120-K120)/J120,"")</f>
+        <v/>
       </c>
       <c r="M120" s="102" t="inlineStr"/>
     </row>
@@ -15889,13 +16112,14 @@
         </is>
       </c>
       <c r="J121" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K121" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L121" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L121" s="98">
+        <f>IF(J121&gt;0,(J121-K121)/J121,"")</f>
+        <v/>
       </c>
       <c r="M121" s="99" t="inlineStr"/>
     </row>
@@ -15938,13 +16162,14 @@
         </is>
       </c>
       <c r="J122" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K122" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L122" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L122" s="101">
+        <f>IF(J122&gt;0,(J122-K122)/J122,"")</f>
+        <v/>
       </c>
       <c r="M122" s="102" t="inlineStr"/>
     </row>
@@ -15987,13 +16212,14 @@
         </is>
       </c>
       <c r="J123" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K123" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L123" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L123" s="98">
+        <f>IF(J123&gt;0,(J123-K123)/J123,"")</f>
+        <v/>
       </c>
       <c r="M123" s="99" t="inlineStr"/>
     </row>
@@ -16036,13 +16262,14 @@
         </is>
       </c>
       <c r="J124" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K124" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L124" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L124" s="101">
+        <f>IF(J124&gt;0,(J124-K124)/J124,"")</f>
+        <v/>
       </c>
       <c r="M124" s="102" t="inlineStr"/>
     </row>
@@ -16085,13 +16312,14 @@
         </is>
       </c>
       <c r="J125" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K125" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L125" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L125" s="98">
+        <f>IF(J125&gt;0,(J125-K125)/J125,"")</f>
+        <v/>
       </c>
       <c r="M125" s="99" t="inlineStr"/>
     </row>
@@ -16130,13 +16358,14 @@
         </is>
       </c>
       <c r="J126" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K126" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L126" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L126" s="101">
+        <f>IF(J126&gt;0,(J126-K126)/J126,"")</f>
+        <v/>
       </c>
       <c r="M126" s="102" t="inlineStr"/>
     </row>
@@ -16175,13 +16404,14 @@
         </is>
       </c>
       <c r="J127" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K127" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L127" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L127" s="98">
+        <f>IF(J127&gt;0,(J127-K127)/J127,"")</f>
+        <v/>
       </c>
       <c r="M127" s="99" t="inlineStr"/>
     </row>
@@ -16220,13 +16450,14 @@
         </is>
       </c>
       <c r="J128" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K128" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L128" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L128" s="101">
+        <f>IF(J128&gt;0,(J128-K128)/J128,"")</f>
+        <v/>
       </c>
       <c r="M128" s="102" t="inlineStr"/>
     </row>
@@ -16269,13 +16500,14 @@
         </is>
       </c>
       <c r="J129" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K129" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L129" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L129" s="98">
+        <f>IF(J129&gt;0,(J129-K129)/J129,"")</f>
+        <v/>
       </c>
       <c r="M129" s="99" t="inlineStr"/>
     </row>
@@ -16314,13 +16546,14 @@
         </is>
       </c>
       <c r="J130" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K130" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L130" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L130" s="101">
+        <f>IF(J130&gt;0,(J130-K130)/J130,"")</f>
+        <v/>
       </c>
       <c r="M130" s="102" t="inlineStr"/>
     </row>
@@ -16359,13 +16592,14 @@
         </is>
       </c>
       <c r="J131" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K131" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L131" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L131" s="98">
+        <f>IF(J131&gt;0,(J131-K131)/J131,"")</f>
+        <v/>
       </c>
       <c r="M131" s="99" t="inlineStr"/>
     </row>
@@ -16404,13 +16638,14 @@
         </is>
       </c>
       <c r="J132" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K132" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L132" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L132" s="101">
+        <f>IF(J132&gt;0,(J132-K132)/J132,"")</f>
+        <v/>
       </c>
       <c r="M132" s="102" t="inlineStr"/>
     </row>
@@ -16449,13 +16684,14 @@
         </is>
       </c>
       <c r="J133" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K133" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L133" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L133" s="98">
+        <f>IF(J133&gt;0,(J133-K133)/J133,"")</f>
+        <v/>
       </c>
       <c r="M133" s="99" t="inlineStr"/>
     </row>
@@ -16494,13 +16730,14 @@
         </is>
       </c>
       <c r="J134" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K134" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L134" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L134" s="101">
+        <f>IF(J134&gt;0,(J134-K134)/J134,"")</f>
+        <v/>
       </c>
       <c r="M134" s="102" t="inlineStr"/>
     </row>
@@ -16546,10 +16783,11 @@
         <v>289</v>
       </c>
       <c r="K135" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L135" s="98" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L135" s="98">
+        <f>IF(J135&gt;0,(J135-K135)/J135,"")</f>
+        <v/>
       </c>
       <c r="M135" s="99" t="inlineStr"/>
     </row>
@@ -16595,10 +16833,11 @@
         <v>289</v>
       </c>
       <c r="K136" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L136" s="101" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L136" s="101">
+        <f>IF(J136&gt;0,(J136-K136)/J136,"")</f>
+        <v/>
       </c>
       <c r="M136" s="102" t="inlineStr"/>
     </row>
@@ -16644,10 +16883,11 @@
         <v>289</v>
       </c>
       <c r="K137" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L137" s="98" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L137" s="98">
+        <f>IF(J137&gt;0,(J137-K137)/J137,"")</f>
+        <v/>
       </c>
       <c r="M137" s="99" t="inlineStr"/>
     </row>
@@ -16693,10 +16933,11 @@
         <v>289</v>
       </c>
       <c r="K138" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L138" s="101" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L138" s="101">
+        <f>IF(J138&gt;0,(J138-K138)/J138,"")</f>
+        <v/>
       </c>
       <c r="M138" s="102" t="inlineStr"/>
     </row>
@@ -16742,10 +16983,11 @@
         <v>289</v>
       </c>
       <c r="K139" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L139" s="98" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L139" s="98">
+        <f>IF(J139&gt;0,(J139-K139)/J139,"")</f>
+        <v/>
       </c>
       <c r="M139" s="99" t="inlineStr"/>
     </row>
@@ -16791,10 +17033,11 @@
         <v>289</v>
       </c>
       <c r="K140" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L140" s="101" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L140" s="101">
+        <f>IF(J140&gt;0,(J140-K140)/J140,"")</f>
+        <v/>
       </c>
       <c r="M140" s="102" t="inlineStr"/>
     </row>
@@ -16840,10 +17083,11 @@
         <v>289</v>
       </c>
       <c r="K141" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L141" s="98" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L141" s="98">
+        <f>IF(J141&gt;0,(J141-K141)/J141,"")</f>
+        <v/>
       </c>
       <c r="M141" s="99" t="inlineStr"/>
     </row>
@@ -16889,10 +17133,11 @@
         <v>289</v>
       </c>
       <c r="K142" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L142" s="101" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L142" s="101">
+        <f>IF(J142&gt;0,(J142-K142)/J142,"")</f>
+        <v/>
       </c>
       <c r="M142" s="102" t="inlineStr"/>
     </row>
@@ -16938,10 +17183,11 @@
         <v>289</v>
       </c>
       <c r="K143" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L143" s="98" t="n">
-        <v>26</v>
+        <v>289</v>
+      </c>
+      <c r="L143" s="98">
+        <f>IF(J143&gt;0,(J143-K143)/J143,"")</f>
+        <v/>
       </c>
       <c r="M143" s="99" t="inlineStr"/>
     </row>
@@ -16991,10 +17237,11 @@
         <v>799</v>
       </c>
       <c r="K144" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L144" s="101" t="n">
-        <v>26</v>
+        <v>844.7</v>
+      </c>
+      <c r="L144" s="101">
+        <f>IF(J144&gt;0,(J144-K144)/J144,"")</f>
+        <v/>
       </c>
       <c r="M144" s="102" t="inlineStr"/>
     </row>
@@ -17037,13 +17284,14 @@
         </is>
       </c>
       <c r="J145" s="142" t="n">
-        <v>729.5</v>
+        <v>450</v>
       </c>
       <c r="K145" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L145" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L145" s="98">
+        <f>IF(J145&gt;0,(J145-K145)/J145,"")</f>
+        <v/>
       </c>
       <c r="M145" s="99" t="inlineStr"/>
     </row>
@@ -17092,10 +17340,11 @@
         <v>3011</v>
       </c>
       <c r="K147" s="143" t="n">
-        <v>782.86</v>
-      </c>
-      <c r="L147" s="101" t="n">
-        <v>26</v>
+        <v>3011</v>
+      </c>
+      <c r="L147" s="101">
+        <f>IF(J147&gt;0,(J147-K147)/J147,"")</f>
+        <v/>
       </c>
       <c r="M147" s="102" t="inlineStr"/>
     </row>
@@ -17138,13 +17387,14 @@
         </is>
       </c>
       <c r="J148" s="142" t="n">
-        <v>3011</v>
+        <v>2700</v>
       </c>
       <c r="K148" s="143" t="n">
-        <v>782.86</v>
-      </c>
-      <c r="L148" s="98" t="n">
-        <v>26</v>
+        <v>2700</v>
+      </c>
+      <c r="L148" s="98">
+        <f>IF(J148&gt;0,(J148-K148)/J148,"")</f>
+        <v/>
       </c>
       <c r="M148" s="99" t="inlineStr"/>
     </row>
@@ -17187,13 +17437,14 @@
         </is>
       </c>
       <c r="J149" s="141" t="n">
-        <v>3011</v>
+        <v>2700</v>
       </c>
       <c r="K149" s="143" t="n">
-        <v>782.86</v>
-      </c>
-      <c r="L149" s="101" t="n">
-        <v>26</v>
+        <v>2700</v>
+      </c>
+      <c r="L149" s="101">
+        <f>IF(J149&gt;0,(J149-K149)/J149,"")</f>
+        <v/>
       </c>
       <c r="M149" s="102" t="inlineStr"/>
     </row>
@@ -17236,13 +17487,14 @@
         </is>
       </c>
       <c r="J150" s="142" t="n">
-        <v>3011</v>
+        <v>2700</v>
       </c>
       <c r="K150" s="143" t="n">
-        <v>782.86</v>
-      </c>
-      <c r="L150" s="98" t="n">
-        <v>26</v>
+        <v>2700</v>
+      </c>
+      <c r="L150" s="98">
+        <f>IF(J150&gt;0,(J150-K150)/J150,"")</f>
+        <v/>
       </c>
       <c r="M150" s="99" t="inlineStr"/>
     </row>
@@ -17285,13 +17537,14 @@
         </is>
       </c>
       <c r="J151" s="141" t="n">
-        <v>3011</v>
+        <v>2700</v>
       </c>
       <c r="K151" s="143" t="n">
-        <v>782.86</v>
-      </c>
-      <c r="L151" s="101" t="n">
-        <v>26</v>
+        <v>2700</v>
+      </c>
+      <c r="L151" s="101">
+        <f>IF(J151&gt;0,(J151-K151)/J151,"")</f>
+        <v/>
       </c>
       <c r="M151" s="102" t="inlineStr"/>
     </row>
@@ -17334,13 +17587,14 @@
         </is>
       </c>
       <c r="J152" s="142" t="n">
-        <v>3011</v>
+        <v>2700</v>
       </c>
       <c r="K152" s="143" t="n">
-        <v>782.86</v>
-      </c>
-      <c r="L152" s="98" t="n">
-        <v>26</v>
+        <v>2700</v>
+      </c>
+      <c r="L152" s="98">
+        <f>IF(J152&gt;0,(J152-K152)/J152,"")</f>
+        <v/>
       </c>
       <c r="M152" s="99" t="inlineStr"/>
     </row>
@@ -17383,13 +17637,14 @@
         </is>
       </c>
       <c r="J153" s="141" t="n">
-        <v>3011</v>
+        <v>2700</v>
       </c>
       <c r="K153" s="143" t="n">
-        <v>782.86</v>
-      </c>
-      <c r="L153" s="101" t="n">
-        <v>26</v>
+        <v>2700</v>
+      </c>
+      <c r="L153" s="101">
+        <f>IF(J153&gt;0,(J153-K153)/J153,"")</f>
+        <v/>
       </c>
       <c r="M153" s="102" t="inlineStr"/>
     </row>
@@ -17431,10 +17686,11 @@
         <v>3011</v>
       </c>
       <c r="K154" s="143" t="n">
-        <v>782.86</v>
-      </c>
-      <c r="L154" s="98" t="n">
-        <v>26</v>
+        <v>3011</v>
+      </c>
+      <c r="L154" s="98">
+        <f>IF(J154&gt;0,(J154-K154)/J154,"")</f>
+        <v/>
       </c>
       <c r="M154" s="99" t="inlineStr"/>
     </row>
@@ -17476,10 +17732,11 @@
         <v>3011</v>
       </c>
       <c r="K155" s="143" t="n">
-        <v>782.86</v>
-      </c>
-      <c r="L155" s="101" t="n">
-        <v>26</v>
+        <v>3011</v>
+      </c>
+      <c r="L155" s="101">
+        <f>IF(J155&gt;0,(J155-K155)/J155,"")</f>
+        <v/>
       </c>
       <c r="M155" s="102" t="inlineStr"/>
     </row>
@@ -17528,10 +17785,11 @@
         <v>799</v>
       </c>
       <c r="K157" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L157" s="98" t="n">
-        <v>26</v>
+        <v>639</v>
+      </c>
+      <c r="L157" s="98">
+        <f>IF(J157&gt;0,(J157-K157)/J157,"")</f>
+        <v/>
       </c>
       <c r="M157" s="99" t="inlineStr"/>
     </row>
@@ -17581,13 +17839,14 @@
         </is>
       </c>
       <c r="J159" s="141" t="n">
-        <v>1724</v>
+        <v>1068.47</v>
       </c>
       <c r="K159" s="143" t="n">
-        <v>448.24</v>
-      </c>
-      <c r="L159" s="101" t="n">
-        <v>26</v>
+        <v>1068.47</v>
+      </c>
+      <c r="L159" s="101">
+        <f>IF(J159&gt;0,(J159-K159)/J159,"")</f>
+        <v/>
       </c>
       <c r="M159" s="102" t="inlineStr"/>
     </row>
@@ -17633,10 +17892,11 @@
         <v>412.95</v>
       </c>
       <c r="K160" s="143" t="n">
-        <v>107.37</v>
-      </c>
-      <c r="L160" s="98" t="n">
-        <v>26</v>
+        <v>412.95</v>
+      </c>
+      <c r="L160" s="98">
+        <f>IF(J160&gt;0,(J160-K160)/J160,"")</f>
+        <v/>
       </c>
       <c r="M160" s="99" t="inlineStr"/>
     </row>
@@ -17682,10 +17942,11 @@
         <v>1724</v>
       </c>
       <c r="K161" s="143" t="n">
-        <v>672.36</v>
-      </c>
-      <c r="L161" s="101" t="n">
-        <v>39</v>
+        <v>1724</v>
+      </c>
+      <c r="L161" s="101">
+        <f>IF(J161&gt;0,(J161-K161)/J161,"")</f>
+        <v/>
       </c>
       <c r="M161" s="102" t="inlineStr"/>
     </row>
@@ -17731,10 +17992,11 @@
         <v>4860</v>
       </c>
       <c r="K162" s="143" t="n">
-        <v>1895.4</v>
-      </c>
-      <c r="L162" s="98" t="n">
-        <v>39</v>
+        <v>4860</v>
+      </c>
+      <c r="L162" s="98">
+        <f>IF(J162&gt;0,(J162-K162)/J162,"")</f>
+        <v/>
       </c>
       <c r="M162" s="99" t="inlineStr"/>
     </row>
@@ -17777,13 +18039,14 @@
         </is>
       </c>
       <c r="J163" s="141" t="n">
-        <v>4860</v>
+        <v>247.99</v>
       </c>
       <c r="K163" s="143" t="n">
-        <v>1263.6</v>
-      </c>
-      <c r="L163" s="101" t="n">
-        <v>26</v>
+        <v>407</v>
+      </c>
+      <c r="L163" s="101">
+        <f>IF(J163&gt;0,(J163-K163)/J163,"")</f>
+        <v/>
       </c>
       <c r="M163" s="102" t="inlineStr"/>
     </row>
@@ -17832,10 +18095,11 @@
         <v>1245</v>
       </c>
       <c r="K165" s="143" t="n">
-        <v>323.7</v>
-      </c>
-      <c r="L165" s="98" t="n">
-        <v>26</v>
+        <v>995</v>
+      </c>
+      <c r="L165" s="98">
+        <f>IF(J165&gt;0,(J165-K165)/J165,"")</f>
+        <v/>
       </c>
       <c r="M165" s="99" t="inlineStr"/>
     </row>
@@ -17877,10 +18141,11 @@
         <v>1245</v>
       </c>
       <c r="K166" s="143" t="n">
-        <v>323.7</v>
-      </c>
-      <c r="L166" s="101" t="n">
-        <v>26</v>
+        <v>995</v>
+      </c>
+      <c r="L166" s="101">
+        <f>IF(J166&gt;0,(J166-K166)/J166,"")</f>
+        <v/>
       </c>
       <c r="M166" s="102" t="inlineStr"/>
     </row>
@@ -17922,10 +18187,11 @@
         <v>1245</v>
       </c>
       <c r="K167" s="143" t="n">
-        <v>323.7</v>
-      </c>
-      <c r="L167" s="98" t="n">
-        <v>26</v>
+        <v>995</v>
+      </c>
+      <c r="L167" s="98">
+        <f>IF(J167&gt;0,(J167-K167)/J167,"")</f>
+        <v/>
       </c>
       <c r="M167" s="99" t="inlineStr"/>
     </row>
@@ -17967,10 +18233,11 @@
         <v>1245</v>
       </c>
       <c r="K168" s="143" t="n">
-        <v>323.7</v>
-      </c>
-      <c r="L168" s="101" t="n">
-        <v>26</v>
+        <v>995</v>
+      </c>
+      <c r="L168" s="101">
+        <f>IF(J168&gt;0,(J168-K168)/J168,"")</f>
+        <v/>
       </c>
       <c r="M168" s="102" t="inlineStr"/>
     </row>
@@ -18012,10 +18279,11 @@
         <v>1245</v>
       </c>
       <c r="K169" s="143" t="n">
-        <v>323.7</v>
-      </c>
-      <c r="L169" s="98" t="n">
-        <v>26</v>
+        <v>995</v>
+      </c>
+      <c r="L169" s="98">
+        <f>IF(J169&gt;0,(J169-K169)/J169,"")</f>
+        <v/>
       </c>
       <c r="M169" s="99" t="inlineStr"/>
     </row>
@@ -18057,10 +18325,11 @@
         <v>1245</v>
       </c>
       <c r="K170" s="143" t="n">
-        <v>323.7</v>
-      </c>
-      <c r="L170" s="101" t="n">
-        <v>26</v>
+        <v>995</v>
+      </c>
+      <c r="L170" s="101">
+        <f>IF(J170&gt;0,(J170-K170)/J170,"")</f>
+        <v/>
       </c>
       <c r="M170" s="102" t="inlineStr"/>
     </row>
@@ -18113,10 +18382,11 @@
         <v>675</v>
       </c>
       <c r="K172" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L172" s="98" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L172" s="98">
+        <f>IF(J172&gt;0,(J172-K172)/J172,"")</f>
+        <v/>
       </c>
       <c r="M172" s="99" t="inlineStr"/>
     </row>
@@ -18162,10 +18432,11 @@
         <v>675</v>
       </c>
       <c r="K173" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L173" s="101" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L173" s="101">
+        <f>IF(J173&gt;0,(J173-K173)/J173,"")</f>
+        <v/>
       </c>
       <c r="M173" s="102" t="inlineStr"/>
     </row>
@@ -18211,10 +18482,11 @@
         <v>936</v>
       </c>
       <c r="K174" s="143" t="n">
-        <v>243.36</v>
-      </c>
-      <c r="L174" s="98" t="n">
-        <v>26</v>
+        <v>936</v>
+      </c>
+      <c r="L174" s="98">
+        <f>IF(J174&gt;0,(J174-K174)/J174,"")</f>
+        <v/>
       </c>
       <c r="M174" s="99" t="inlineStr"/>
     </row>
@@ -18260,10 +18532,11 @@
         <v>936</v>
       </c>
       <c r="K175" s="143" t="n">
-        <v>243.36</v>
-      </c>
-      <c r="L175" s="101" t="n">
-        <v>26</v>
+        <v>936</v>
+      </c>
+      <c r="L175" s="101">
+        <f>IF(J175&gt;0,(J175-K175)/J175,"")</f>
+        <v/>
       </c>
       <c r="M175" s="102" t="inlineStr"/>
     </row>
@@ -18309,10 +18582,11 @@
         <v>675</v>
       </c>
       <c r="K176" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L176" s="98" t="n">
-        <v>26</v>
+        <v>639</v>
+      </c>
+      <c r="L176" s="98">
+        <f>IF(J176&gt;0,(J176-K176)/J176,"")</f>
+        <v/>
       </c>
       <c r="M176" s="99" t="inlineStr"/>
     </row>
@@ -18358,10 +18632,11 @@
         <v>675</v>
       </c>
       <c r="K177" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L177" s="101" t="n">
-        <v>26</v>
+        <v>639</v>
+      </c>
+      <c r="L177" s="101">
+        <f>IF(J177&gt;0,(J177-K177)/J177,"")</f>
+        <v/>
       </c>
       <c r="M177" s="102" t="inlineStr"/>
     </row>
@@ -18407,10 +18682,11 @@
         <v>321</v>
       </c>
       <c r="K178" s="143" t="n">
-        <v>83.45999999999999</v>
-      </c>
-      <c r="L178" s="98" t="n">
-        <v>26</v>
+        <v>321</v>
+      </c>
+      <c r="L178" s="98">
+        <f>IF(J178&gt;0,(J178-K178)/J178,"")</f>
+        <v/>
       </c>
       <c r="M178" s="99" t="inlineStr"/>
     </row>
@@ -18456,10 +18732,11 @@
         <v>535</v>
       </c>
       <c r="K179" s="143" t="n">
-        <v>139.1</v>
-      </c>
-      <c r="L179" s="101" t="n">
-        <v>26</v>
+        <v>700</v>
+      </c>
+      <c r="L179" s="101">
+        <f>IF(J179&gt;0,(J179-K179)/J179,"")</f>
+        <v/>
       </c>
       <c r="M179" s="102" t="inlineStr"/>
     </row>
@@ -18505,10 +18782,11 @@
         <v>535</v>
       </c>
       <c r="K180" s="143" t="n">
-        <v>139.1</v>
-      </c>
-      <c r="L180" s="98" t="n">
-        <v>26</v>
+        <v>700</v>
+      </c>
+      <c r="L180" s="98">
+        <f>IF(J180&gt;0,(J180-K180)/J180,"")</f>
+        <v/>
       </c>
       <c r="M180" s="99" t="inlineStr"/>
     </row>
@@ -18554,10 +18832,11 @@
         <v>535</v>
       </c>
       <c r="K181" s="143" t="n">
-        <v>139.1</v>
-      </c>
-      <c r="L181" s="101" t="n">
-        <v>26</v>
+        <v>700</v>
+      </c>
+      <c r="L181" s="101">
+        <f>IF(J181&gt;0,(J181-K181)/J181,"")</f>
+        <v/>
       </c>
       <c r="M181" s="102" t="inlineStr"/>
     </row>
@@ -18603,10 +18882,11 @@
         <v>535</v>
       </c>
       <c r="K182" s="143" t="n">
-        <v>139.1</v>
-      </c>
-      <c r="L182" s="98" t="n">
-        <v>26</v>
+        <v>700</v>
+      </c>
+      <c r="L182" s="98">
+        <f>IF(J182&gt;0,(J182-K182)/J182,"")</f>
+        <v/>
       </c>
       <c r="M182" s="99" t="inlineStr"/>
     </row>
@@ -18652,10 +18932,11 @@
         <v>535</v>
       </c>
       <c r="K183" s="143" t="n">
-        <v>139.1</v>
-      </c>
-      <c r="L183" s="101" t="n">
-        <v>26</v>
+        <v>700</v>
+      </c>
+      <c r="L183" s="101">
+        <f>IF(J183&gt;0,(J183-K183)/J183,"")</f>
+        <v/>
       </c>
       <c r="M183" s="102" t="inlineStr"/>
     </row>
@@ -18701,10 +18982,11 @@
         <v>675</v>
       </c>
       <c r="K184" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L184" s="98" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L184" s="98">
+        <f>IF(J184&gt;0,(J184-K184)/J184,"")</f>
+        <v/>
       </c>
       <c r="M184" s="99" t="inlineStr"/>
     </row>
@@ -18750,10 +19032,11 @@
         <v>675</v>
       </c>
       <c r="K185" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L185" s="101" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L185" s="101">
+        <f>IF(J185&gt;0,(J185-K185)/J185,"")</f>
+        <v/>
       </c>
       <c r="M185" s="102" t="inlineStr"/>
     </row>
@@ -18799,10 +19082,11 @@
         <v>675</v>
       </c>
       <c r="K186" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L186" s="98" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L186" s="98">
+        <f>IF(J186&gt;0,(J186-K186)/J186,"")</f>
+        <v/>
       </c>
       <c r="M186" s="99" t="inlineStr"/>
     </row>
@@ -18848,10 +19132,11 @@
         <v>675</v>
       </c>
       <c r="K187" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L187" s="101" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L187" s="101">
+        <f>IF(J187&gt;0,(J187-K187)/J187,"")</f>
+        <v/>
       </c>
       <c r="M187" s="102" t="inlineStr"/>
     </row>
@@ -18897,10 +19182,11 @@
         <v>675</v>
       </c>
       <c r="K188" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L188" s="98" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L188" s="98">
+        <f>IF(J188&gt;0,(J188-K188)/J188,"")</f>
+        <v/>
       </c>
       <c r="M188" s="99" t="inlineStr"/>
     </row>
@@ -18942,10 +19228,11 @@
         <v>675</v>
       </c>
       <c r="K189" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L189" s="101" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L189" s="101">
+        <f>IF(J189&gt;0,(J189-K189)/J189,"")</f>
+        <v/>
       </c>
       <c r="M189" s="102" t="inlineStr"/>
     </row>
@@ -18987,10 +19274,11 @@
         <v>675</v>
       </c>
       <c r="K190" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L190" s="98" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L190" s="98">
+        <f>IF(J190&gt;0,(J190-K190)/J190,"")</f>
+        <v/>
       </c>
       <c r="M190" s="99" t="inlineStr"/>
     </row>
@@ -19036,10 +19324,11 @@
         <v>675</v>
       </c>
       <c r="K191" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L191" s="101" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L191" s="101">
+        <f>IF(J191&gt;0,(J191-K191)/J191,"")</f>
+        <v/>
       </c>
       <c r="M191" s="102" t="inlineStr"/>
     </row>
@@ -19081,10 +19370,11 @@
         <v>675</v>
       </c>
       <c r="K192" s="143" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="L192" s="98" t="n">
-        <v>26</v>
+        <v>315</v>
+      </c>
+      <c r="L192" s="98">
+        <f>IF(J192&gt;0,(J192-K192)/J192,"")</f>
+        <v/>
       </c>
       <c r="M192" s="99" t="inlineStr"/>
     </row>
@@ -19130,10 +19420,11 @@
         <v>321</v>
       </c>
       <c r="K193" s="143" t="n">
-        <v>83.45999999999999</v>
-      </c>
-      <c r="L193" s="101" t="n">
-        <v>26</v>
+        <v>321</v>
+      </c>
+      <c r="L193" s="101">
+        <f>IF(J193&gt;0,(J193-K193)/J193,"")</f>
+        <v/>
       </c>
       <c r="M193" s="102" t="inlineStr"/>
     </row>
@@ -19179,10 +19470,11 @@
         <v>936</v>
       </c>
       <c r="K194" s="143" t="n">
-        <v>243.36</v>
-      </c>
-      <c r="L194" s="98" t="n">
-        <v>26</v>
+        <v>936</v>
+      </c>
+      <c r="L194" s="98">
+        <f>IF(J194&gt;0,(J194-K194)/J194,"")</f>
+        <v/>
       </c>
       <c r="M194" s="99" t="inlineStr"/>
     </row>
@@ -19228,10 +19520,11 @@
         <v>936</v>
       </c>
       <c r="K195" s="143" t="n">
-        <v>243.36</v>
-      </c>
-      <c r="L195" s="101" t="n">
-        <v>26</v>
+        <v>936</v>
+      </c>
+      <c r="L195" s="101">
+        <f>IF(J195&gt;0,(J195-K195)/J195,"")</f>
+        <v/>
       </c>
       <c r="M195" s="102" t="inlineStr"/>
     </row>
@@ -19284,10 +19577,11 @@
         <v>640</v>
       </c>
       <c r="K197" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L197" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L197" s="98">
+        <f>IF(J197&gt;0,(J197-K197)/J197,"")</f>
+        <v/>
       </c>
       <c r="M197" s="99" t="inlineStr"/>
     </row>
@@ -19333,10 +19627,11 @@
         <v>640</v>
       </c>
       <c r="K198" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L198" s="101" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L198" s="101">
+        <f>IF(J198&gt;0,(J198-K198)/J198,"")</f>
+        <v/>
       </c>
       <c r="M198" s="102" t="inlineStr"/>
     </row>
@@ -19379,13 +19674,14 @@
         </is>
       </c>
       <c r="J199" s="142" t="n">
-        <v>640</v>
+        <v>450</v>
       </c>
       <c r="K199" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L199" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L199" s="98">
+        <f>IF(J199&gt;0,(J199-K199)/J199,"")</f>
+        <v/>
       </c>
       <c r="M199" s="99" t="inlineStr"/>
     </row>
@@ -19431,10 +19727,11 @@
         <v>1350</v>
       </c>
       <c r="K200" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L200" s="101" t="n">
-        <v>26</v>
+        <v>1290</v>
+      </c>
+      <c r="L200" s="101">
+        <f>IF(J200&gt;0,(J200-K200)/J200,"")</f>
+        <v/>
       </c>
       <c r="M200" s="102" t="inlineStr"/>
     </row>
@@ -19480,10 +19777,11 @@
         <v>640</v>
       </c>
       <c r="K201" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L201" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L201" s="98">
+        <f>IF(J201&gt;0,(J201-K201)/J201,"")</f>
+        <v/>
       </c>
       <c r="M201" s="99" t="inlineStr"/>
     </row>
@@ -19526,13 +19824,14 @@
         </is>
       </c>
       <c r="J202" s="141" t="n">
-        <v>640</v>
+        <v>450</v>
       </c>
       <c r="K202" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L202" s="101" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L202" s="101">
+        <f>IF(J202&gt;0,(J202-K202)/J202,"")</f>
+        <v/>
       </c>
       <c r="M202" s="102" t="inlineStr"/>
     </row>
@@ -19578,10 +19877,11 @@
         <v>640</v>
       </c>
       <c r="K203" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L203" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L203" s="98">
+        <f>IF(J203&gt;0,(J203-K203)/J203,"")</f>
+        <v/>
       </c>
       <c r="M203" s="99" t="inlineStr"/>
     </row>
@@ -19627,10 +19927,11 @@
         <v>640</v>
       </c>
       <c r="K204" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L204" s="101" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L204" s="101">
+        <f>IF(J204&gt;0,(J204-K204)/J204,"")</f>
+        <v/>
       </c>
       <c r="M204" s="102" t="inlineStr"/>
     </row>
@@ -19673,13 +19974,14 @@
         </is>
       </c>
       <c r="J205" s="142" t="n">
-        <v>640</v>
+        <v>450</v>
       </c>
       <c r="K205" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L205" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L205" s="98">
+        <f>IF(J205&gt;0,(J205-K205)/J205,"")</f>
+        <v/>
       </c>
       <c r="M205" s="99" t="inlineStr"/>
     </row>
@@ -19725,10 +20027,11 @@
         <v>1350</v>
       </c>
       <c r="K206" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L206" s="101" t="n">
-        <v>26</v>
+        <v>1290</v>
+      </c>
+      <c r="L206" s="101">
+        <f>IF(J206&gt;0,(J206-K206)/J206,"")</f>
+        <v/>
       </c>
       <c r="M206" s="102" t="inlineStr"/>
     </row>
@@ -19771,13 +20074,14 @@
         </is>
       </c>
       <c r="J207" s="142" t="n">
-        <v>640</v>
+        <v>450</v>
       </c>
       <c r="K207" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L207" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L207" s="98">
+        <f>IF(J207&gt;0,(J207-K207)/J207,"")</f>
+        <v/>
       </c>
       <c r="M207" s="99" t="inlineStr"/>
     </row>
@@ -19823,10 +20127,11 @@
         <v>1350</v>
       </c>
       <c r="K208" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L208" s="101" t="n">
-        <v>26</v>
+        <v>1290</v>
+      </c>
+      <c r="L208" s="101">
+        <f>IF(J208&gt;0,(J208-K208)/J208,"")</f>
+        <v/>
       </c>
       <c r="M208" s="102" t="inlineStr"/>
     </row>
@@ -19869,13 +20174,14 @@
         </is>
       </c>
       <c r="J209" s="142" t="n">
-        <v>640</v>
+        <v>450</v>
       </c>
       <c r="K209" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L209" s="98" t="n">
-        <v>26</v>
+        <v>450</v>
+      </c>
+      <c r="L209" s="98">
+        <f>IF(J209&gt;0,(J209-K209)/J209,"")</f>
+        <v/>
       </c>
       <c r="M209" s="99" t="inlineStr"/>
     </row>
@@ -19917,10 +20223,11 @@
         <v>1350</v>
       </c>
       <c r="K210" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L210" s="101" t="n">
-        <v>26</v>
+        <v>1290</v>
+      </c>
+      <c r="L210" s="101">
+        <f>IF(J210&gt;0,(J210-K210)/J210,"")</f>
+        <v/>
       </c>
       <c r="M210" s="102" t="inlineStr"/>
     </row>
@@ -19962,10 +20269,11 @@
         <v>1350</v>
       </c>
       <c r="K211" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L211" s="98" t="n">
-        <v>26</v>
+        <v>1290</v>
+      </c>
+      <c r="L211" s="98">
+        <f>IF(J211&gt;0,(J211-K211)/J211,"")</f>
+        <v/>
       </c>
       <c r="M211" s="99" t="inlineStr"/>
     </row>
@@ -20007,10 +20315,11 @@
         <v>1350</v>
       </c>
       <c r="K212" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L212" s="101" t="n">
-        <v>26</v>
+        <v>1290</v>
+      </c>
+      <c r="L212" s="101">
+        <f>IF(J212&gt;0,(J212-K212)/J212,"")</f>
+        <v/>
       </c>
       <c r="M212" s="102" t="inlineStr"/>
     </row>
@@ -20056,10 +20365,11 @@
         <v>640</v>
       </c>
       <c r="K213" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L213" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L213" s="98">
+        <f>IF(J213&gt;0,(J213-K213)/J213,"")</f>
+        <v/>
       </c>
       <c r="M213" s="99" t="inlineStr"/>
     </row>
@@ -20101,10 +20411,11 @@
         <v>1350</v>
       </c>
       <c r="K214" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L214" s="101" t="n">
-        <v>26</v>
+        <v>1290</v>
+      </c>
+      <c r="L214" s="101">
+        <f>IF(J214&gt;0,(J214-K214)/J214,"")</f>
+        <v/>
       </c>
       <c r="M214" s="102" t="inlineStr"/>
     </row>
@@ -20150,10 +20461,11 @@
         <v>640</v>
       </c>
       <c r="K215" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L215" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L215" s="98">
+        <f>IF(J215&gt;0,(J215-K215)/J215,"")</f>
+        <v/>
       </c>
       <c r="M215" s="99" t="inlineStr"/>
     </row>
@@ -20203,10 +20515,11 @@
         <v>640</v>
       </c>
       <c r="K216" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L216" s="101" t="n">
-        <v>26</v>
+        <v>129.99</v>
+      </c>
+      <c r="L216" s="101">
+        <f>IF(J216&gt;0,(J216-K216)/J216,"")</f>
+        <v/>
       </c>
       <c r="M216" s="102" t="inlineStr"/>
     </row>
@@ -20252,10 +20565,11 @@
         <v>192.14</v>
       </c>
       <c r="K217" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L217" s="98" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L217" s="98">
+        <f>IF(J217&gt;0,(J217-K217)/J217,"")</f>
+        <v/>
       </c>
       <c r="M217" s="99" t="inlineStr"/>
     </row>
@@ -20301,10 +20615,11 @@
         <v>192.14</v>
       </c>
       <c r="K218" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L218" s="101" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L218" s="101">
+        <f>IF(J218&gt;0,(J218-K218)/J218,"")</f>
+        <v/>
       </c>
       <c r="M218" s="102" t="inlineStr"/>
     </row>
@@ -20350,10 +20665,11 @@
         <v>192.14</v>
       </c>
       <c r="K219" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L219" s="98" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L219" s="98">
+        <f>IF(J219&gt;0,(J219-K219)/J219,"")</f>
+        <v/>
       </c>
       <c r="M219" s="99" t="inlineStr"/>
     </row>
@@ -20399,10 +20715,11 @@
         <v>192.14</v>
       </c>
       <c r="K220" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L220" s="101" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L220" s="101">
+        <f>IF(J220&gt;0,(J220-K220)/J220,"")</f>
+        <v/>
       </c>
       <c r="M220" s="102" t="inlineStr"/>
     </row>
@@ -20448,10 +20765,11 @@
         <v>192.14</v>
       </c>
       <c r="K221" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L221" s="98" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L221" s="98">
+        <f>IF(J221&gt;0,(J221-K221)/J221,"")</f>
+        <v/>
       </c>
       <c r="M221" s="99" t="inlineStr"/>
     </row>
@@ -20497,10 +20815,11 @@
         <v>192.14</v>
       </c>
       <c r="K222" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L222" s="101" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L222" s="101">
+        <f>IF(J222&gt;0,(J222-K222)/J222,"")</f>
+        <v/>
       </c>
       <c r="M222" s="102" t="inlineStr"/>
     </row>
@@ -20546,10 +20865,11 @@
         <v>192.14</v>
       </c>
       <c r="K223" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L223" s="98" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L223" s="98">
+        <f>IF(J223&gt;0,(J223-K223)/J223,"")</f>
+        <v/>
       </c>
       <c r="M223" s="99" t="inlineStr"/>
     </row>
@@ -20595,10 +20915,11 @@
         <v>192.14</v>
       </c>
       <c r="K224" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L224" s="101" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L224" s="101">
+        <f>IF(J224&gt;0,(J224-K224)/J224,"")</f>
+        <v/>
       </c>
       <c r="M224" s="102" t="inlineStr"/>
     </row>
@@ -20644,10 +20965,11 @@
         <v>192.14</v>
       </c>
       <c r="K225" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L225" s="98" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L225" s="98">
+        <f>IF(J225&gt;0,(J225-K225)/J225,"")</f>
+        <v/>
       </c>
       <c r="M225" s="99" t="inlineStr"/>
     </row>
@@ -20693,10 +21015,11 @@
         <v>192.14</v>
       </c>
       <c r="K226" s="143" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="L226" s="101" t="n">
-        <v>26</v>
+        <v>192.14</v>
+      </c>
+      <c r="L226" s="101">
+        <f>IF(J226&gt;0,(J226-K226)/J226,"")</f>
+        <v/>
       </c>
       <c r="M226" s="102" t="inlineStr"/>
     </row>
@@ -20742,10 +21065,11 @@
         <v>640</v>
       </c>
       <c r="K227" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L227" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L227" s="98">
+        <f>IF(J227&gt;0,(J227-K227)/J227,"")</f>
+        <v/>
       </c>
       <c r="M227" s="99" t="inlineStr"/>
     </row>
@@ -20791,10 +21115,11 @@
         <v>640</v>
       </c>
       <c r="K228" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L228" s="101" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L228" s="101">
+        <f>IF(J228&gt;0,(J228-K228)/J228,"")</f>
+        <v/>
       </c>
       <c r="M228" s="102" t="inlineStr"/>
     </row>
@@ -20840,10 +21165,11 @@
         <v>640</v>
       </c>
       <c r="K229" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L229" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L229" s="98">
+        <f>IF(J229&gt;0,(J229-K229)/J229,"")</f>
+        <v/>
       </c>
       <c r="M229" s="99" t="inlineStr"/>
     </row>
@@ -20889,10 +21215,11 @@
         <v>640</v>
       </c>
       <c r="K230" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L230" s="101" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L230" s="101">
+        <f>IF(J230&gt;0,(J230-K230)/J230,"")</f>
+        <v/>
       </c>
       <c r="M230" s="102" t="inlineStr"/>
     </row>
@@ -20938,10 +21265,11 @@
         <v>640</v>
       </c>
       <c r="K231" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L231" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L231" s="98">
+        <f>IF(J231&gt;0,(J231-K231)/J231,"")</f>
+        <v/>
       </c>
       <c r="M231" s="99" t="inlineStr"/>
     </row>
@@ -20987,10 +21315,11 @@
         <v>640</v>
       </c>
       <c r="K232" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L232" s="101" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L232" s="101">
+        <f>IF(J232&gt;0,(J232-K232)/J232,"")</f>
+        <v/>
       </c>
       <c r="M232" s="102" t="inlineStr"/>
     </row>
@@ -21036,10 +21365,11 @@
         <v>640</v>
       </c>
       <c r="K233" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L233" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L233" s="98">
+        <f>IF(J233&gt;0,(J233-K233)/J233,"")</f>
+        <v/>
       </c>
       <c r="M233" s="99" t="inlineStr"/>
     </row>
@@ -21085,10 +21415,11 @@
         <v>640</v>
       </c>
       <c r="K234" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L234" s="101" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L234" s="101">
+        <f>IF(J234&gt;0,(J234-K234)/J234,"")</f>
+        <v/>
       </c>
       <c r="M234" s="102" t="inlineStr"/>
     </row>
@@ -21134,10 +21465,11 @@
         <v>640</v>
       </c>
       <c r="K235" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L235" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L235" s="98">
+        <f>IF(J235&gt;0,(J235-K235)/J235,"")</f>
+        <v/>
       </c>
       <c r="M235" s="99" t="inlineStr"/>
     </row>
@@ -21183,10 +21515,11 @@
         <v>640</v>
       </c>
       <c r="K236" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L236" s="101" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L236" s="101">
+        <f>IF(J236&gt;0,(J236-K236)/J236,"")</f>
+        <v/>
       </c>
       <c r="M236" s="102" t="inlineStr"/>
     </row>
@@ -21232,10 +21565,11 @@
         <v>640</v>
       </c>
       <c r="K237" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L237" s="98" t="n">
-        <v>26</v>
+        <v>640</v>
+      </c>
+      <c r="L237" s="98">
+        <f>IF(J237&gt;0,(J237-K237)/J237,"")</f>
+        <v/>
       </c>
       <c r="M237" s="99" t="inlineStr"/>
     </row>
@@ -21278,13 +21612,14 @@
         </is>
       </c>
       <c r="J238" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K238" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L238" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L238" s="101">
+        <f>IF(J238&gt;0,(J238-K238)/J238,"")</f>
+        <v/>
       </c>
       <c r="M238" s="102" t="inlineStr"/>
     </row>
@@ -21327,13 +21662,14 @@
         </is>
       </c>
       <c r="J239" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K239" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L239" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L239" s="98">
+        <f>IF(J239&gt;0,(J239-K239)/J239,"")</f>
+        <v/>
       </c>
       <c r="M239" s="99" t="inlineStr"/>
     </row>
@@ -21376,13 +21712,14 @@
         </is>
       </c>
       <c r="J240" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K240" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L240" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L240" s="101">
+        <f>IF(J240&gt;0,(J240-K240)/J240,"")</f>
+        <v/>
       </c>
       <c r="M240" s="102" t="inlineStr"/>
     </row>
@@ -21425,13 +21762,14 @@
         </is>
       </c>
       <c r="J241" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K241" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L241" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L241" s="98">
+        <f>IF(J241&gt;0,(J241-K241)/J241,"")</f>
+        <v/>
       </c>
       <c r="M241" s="99" t="inlineStr"/>
     </row>
@@ -21474,13 +21812,14 @@
         </is>
       </c>
       <c r="J242" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K242" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L242" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L242" s="101">
+        <f>IF(J242&gt;0,(J242-K242)/J242,"")</f>
+        <v/>
       </c>
       <c r="M242" s="102" t="inlineStr"/>
     </row>
@@ -21523,13 +21862,14 @@
         </is>
       </c>
       <c r="J243" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K243" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L243" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L243" s="98">
+        <f>IF(J243&gt;0,(J243-K243)/J243,"")</f>
+        <v/>
       </c>
       <c r="M243" s="99" t="inlineStr"/>
     </row>
@@ -21572,13 +21912,14 @@
         </is>
       </c>
       <c r="J244" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K244" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L244" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L244" s="101">
+        <f>IF(J244&gt;0,(J244-K244)/J244,"")</f>
+        <v/>
       </c>
       <c r="M244" s="102" t="inlineStr"/>
     </row>
@@ -21621,13 +21962,14 @@
         </is>
       </c>
       <c r="J245" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K245" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L245" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L245" s="98">
+        <f>IF(J245&gt;0,(J245-K245)/J245,"")</f>
+        <v/>
       </c>
       <c r="M245" s="99" t="inlineStr"/>
     </row>
@@ -21670,13 +22012,14 @@
         </is>
       </c>
       <c r="J246" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K246" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L246" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L246" s="101">
+        <f>IF(J246&gt;0,(J246-K246)/J246,"")</f>
+        <v/>
       </c>
       <c r="M246" s="102" t="inlineStr"/>
     </row>
@@ -21719,13 +22062,14 @@
         </is>
       </c>
       <c r="J247" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K247" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L247" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L247" s="98">
+        <f>IF(J247&gt;0,(J247-K247)/J247,"")</f>
+        <v/>
       </c>
       <c r="M247" s="99" t="inlineStr"/>
     </row>
@@ -21768,13 +22112,14 @@
         </is>
       </c>
       <c r="J248" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K248" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L248" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L248" s="101">
+        <f>IF(J248&gt;0,(J248-K248)/J248,"")</f>
+        <v/>
       </c>
       <c r="M248" s="102" t="inlineStr"/>
     </row>
@@ -21817,13 +22162,14 @@
         </is>
       </c>
       <c r="J249" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K249" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L249" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L249" s="98">
+        <f>IF(J249&gt;0,(J249-K249)/J249,"")</f>
+        <v/>
       </c>
       <c r="M249" s="99" t="inlineStr"/>
     </row>
@@ -21866,13 +22212,14 @@
         </is>
       </c>
       <c r="J250" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K250" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L250" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L250" s="101">
+        <f>IF(J250&gt;0,(J250-K250)/J250,"")</f>
+        <v/>
       </c>
       <c r="M250" s="102" t="inlineStr"/>
     </row>
@@ -21915,13 +22262,14 @@
         </is>
       </c>
       <c r="J251" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K251" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L251" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L251" s="98">
+        <f>IF(J251&gt;0,(J251-K251)/J251,"")</f>
+        <v/>
       </c>
       <c r="M251" s="99" t="inlineStr"/>
     </row>
@@ -21964,13 +22312,14 @@
         </is>
       </c>
       <c r="J252" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K252" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L252" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L252" s="101">
+        <f>IF(J252&gt;0,(J252-K252)/J252,"")</f>
+        <v/>
       </c>
       <c r="M252" s="102" t="inlineStr"/>
     </row>
@@ -22013,13 +22362,14 @@
         </is>
       </c>
       <c r="J253" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K253" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L253" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L253" s="98">
+        <f>IF(J253&gt;0,(J253-K253)/J253,"")</f>
+        <v/>
       </c>
       <c r="M253" s="99" t="inlineStr"/>
     </row>
@@ -22062,13 +22412,14 @@
         </is>
       </c>
       <c r="J254" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K254" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L254" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L254" s="101">
+        <f>IF(J254&gt;0,(J254-K254)/J254,"")</f>
+        <v/>
       </c>
       <c r="M254" s="102" t="inlineStr"/>
     </row>
@@ -22111,13 +22462,14 @@
         </is>
       </c>
       <c r="J255" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K255" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L255" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L255" s="98">
+        <f>IF(J255&gt;0,(J255-K255)/J255,"")</f>
+        <v/>
       </c>
       <c r="M255" s="99" t="inlineStr"/>
     </row>
@@ -22160,13 +22512,14 @@
         </is>
       </c>
       <c r="J256" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K256" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L256" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L256" s="101">
+        <f>IF(J256&gt;0,(J256-K256)/J256,"")</f>
+        <v/>
       </c>
       <c r="M256" s="102" t="inlineStr"/>
     </row>
@@ -22209,13 +22562,14 @@
         </is>
       </c>
       <c r="J257" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K257" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L257" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L257" s="98">
+        <f>IF(J257&gt;0,(J257-K257)/J257,"")</f>
+        <v/>
       </c>
       <c r="M257" s="99" t="inlineStr"/>
     </row>
@@ -22258,13 +22612,14 @@
         </is>
       </c>
       <c r="J258" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K258" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L258" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L258" s="101">
+        <f>IF(J258&gt;0,(J258-K258)/J258,"")</f>
+        <v/>
       </c>
       <c r="M258" s="102" t="inlineStr"/>
     </row>
@@ -22307,13 +22662,14 @@
         </is>
       </c>
       <c r="J259" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K259" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L259" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L259" s="98">
+        <f>IF(J259&gt;0,(J259-K259)/J259,"")</f>
+        <v/>
       </c>
       <c r="M259" s="99" t="inlineStr"/>
     </row>
@@ -22356,13 +22712,14 @@
         </is>
       </c>
       <c r="J260" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K260" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L260" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L260" s="101">
+        <f>IF(J260&gt;0,(J260-K260)/J260,"")</f>
+        <v/>
       </c>
       <c r="M260" s="102" t="inlineStr"/>
     </row>
@@ -22405,13 +22762,14 @@
         </is>
       </c>
       <c r="J261" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K261" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L261" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L261" s="98">
+        <f>IF(J261&gt;0,(J261-K261)/J261,"")</f>
+        <v/>
       </c>
       <c r="M261" s="99" t="inlineStr"/>
     </row>
@@ -22454,13 +22812,14 @@
         </is>
       </c>
       <c r="J262" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K262" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L262" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L262" s="101">
+        <f>IF(J262&gt;0,(J262-K262)/J262,"")</f>
+        <v/>
       </c>
       <c r="M262" s="102" t="inlineStr"/>
     </row>
@@ -22503,13 +22862,14 @@
         </is>
       </c>
       <c r="J263" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K263" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L263" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L263" s="98">
+        <f>IF(J263&gt;0,(J263-K263)/J263,"")</f>
+        <v/>
       </c>
       <c r="M263" s="99" t="inlineStr"/>
     </row>
@@ -22552,13 +22912,14 @@
         </is>
       </c>
       <c r="J264" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K264" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L264" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L264" s="101">
+        <f>IF(J264&gt;0,(J264-K264)/J264,"")</f>
+        <v/>
       </c>
       <c r="M264" s="102" t="inlineStr"/>
     </row>
@@ -22601,13 +22962,14 @@
         </is>
       </c>
       <c r="J265" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K265" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L265" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L265" s="98">
+        <f>IF(J265&gt;0,(J265-K265)/J265,"")</f>
+        <v/>
       </c>
       <c r="M265" s="99" t="inlineStr"/>
     </row>
@@ -22650,13 +23012,14 @@
         </is>
       </c>
       <c r="J266" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K266" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L266" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L266" s="101">
+        <f>IF(J266&gt;0,(J266-K266)/J266,"")</f>
+        <v/>
       </c>
       <c r="M266" s="102" t="inlineStr"/>
     </row>
@@ -22699,13 +23062,14 @@
         </is>
       </c>
       <c r="J267" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K267" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L267" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L267" s="98">
+        <f>IF(J267&gt;0,(J267-K267)/J267,"")</f>
+        <v/>
       </c>
       <c r="M267" s="99" t="inlineStr"/>
     </row>
@@ -22748,13 +23112,14 @@
         </is>
       </c>
       <c r="J268" s="141" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K268" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L268" s="101" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L268" s="101">
+        <f>IF(J268&gt;0,(J268-K268)/J268,"")</f>
+        <v/>
       </c>
       <c r="M268" s="102" t="inlineStr"/>
     </row>
@@ -22797,13 +23162,14 @@
         </is>
       </c>
       <c r="J269" s="142" t="n">
-        <v>640</v>
+        <v>664.99</v>
       </c>
       <c r="K269" s="143" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="L269" s="98" t="n">
-        <v>26</v>
+        <v>664.99</v>
+      </c>
+      <c r="L269" s="98">
+        <f>IF(J269&gt;0,(J269-K269)/J269,"")</f>
+        <v/>
       </c>
       <c r="M269" s="99" t="inlineStr"/>
     </row>
@@ -22845,10 +23211,11 @@
         <v>1350</v>
       </c>
       <c r="K270" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L270" s="101" t="n">
-        <v>26</v>
+        <v>1290</v>
+      </c>
+      <c r="L270" s="101">
+        <f>IF(J270&gt;0,(J270-K270)/J270,"")</f>
+        <v/>
       </c>
       <c r="M270" s="102" t="inlineStr"/>
     </row>
@@ -22894,10 +23261,11 @@
         <v>1350</v>
       </c>
       <c r="K271" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L271" s="98" t="n">
-        <v>26</v>
+        <v>1290</v>
+      </c>
+      <c r="L271" s="98">
+        <f>IF(J271&gt;0,(J271-K271)/J271,"")</f>
+        <v/>
       </c>
       <c r="M271" s="99" t="inlineStr"/>
     </row>
@@ -22939,10 +23307,11 @@
         <v>1350</v>
       </c>
       <c r="K272" s="143" t="n">
-        <v>351</v>
-      </c>
-      <c r="L272" s="101" t="n">
-        <v>26</v>
+        <v>560</v>
+      </c>
+      <c r="L272" s="101">
+        <f>IF(J272&gt;0,(J272-K272)/J272,"")</f>
+        <v/>
       </c>
       <c r="M272" s="102" t="inlineStr"/>
     </row>
@@ -22995,10 +23364,11 @@
         <v>289</v>
       </c>
       <c r="K274" s="143" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="L274" s="98" t="n">
-        <v>26</v>
+        <v>1100</v>
+      </c>
+      <c r="L274" s="98">
+        <f>IF(J274&gt;0,(J274-K274)/J274,"")</f>
+        <v/>
       </c>
       <c r="M274" s="99" t="inlineStr"/>
     </row>
@@ -23041,13 +23411,14 @@
         </is>
       </c>
       <c r="J275" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K275" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L275" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L275" s="101">
+        <f>IF(J275&gt;0,(J275-K275)/J275,"")</f>
+        <v/>
       </c>
       <c r="M275" s="102" t="inlineStr"/>
     </row>
@@ -23086,13 +23457,14 @@
         </is>
       </c>
       <c r="J276" s="142" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K276" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L276" s="98" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L276" s="98">
+        <f>IF(J276&gt;0,(J276-K276)/J276,"")</f>
+        <v/>
       </c>
       <c r="M276" s="99" t="inlineStr"/>
     </row>
@@ -23131,13 +23503,14 @@
         </is>
       </c>
       <c r="J277" s="141" t="n">
-        <v>729.5</v>
+        <v>171</v>
       </c>
       <c r="K277" s="143" t="n">
-        <v>189.67</v>
-      </c>
-      <c r="L277" s="101" t="n">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="L277" s="101">
+        <f>IF(J277&gt;0,(J277-K277)/J277,"")</f>
+        <v/>
       </c>
       <c r="M277" s="102" t="inlineStr"/>
     </row>
@@ -23186,10 +23559,11 @@
         <v>799</v>
       </c>
       <c r="K279" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L279" s="98" t="n">
-        <v>26</v>
+        <v>639</v>
+      </c>
+      <c r="L279" s="98">
+        <f>IF(J279&gt;0,(J279-K279)/J279,"")</f>
+        <v/>
       </c>
       <c r="M279" s="99" t="inlineStr"/>
     </row>
@@ -23231,10 +23605,11 @@
         <v>799</v>
       </c>
       <c r="K280" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L280" s="101" t="n">
-        <v>26</v>
+        <v>639</v>
+      </c>
+      <c r="L280" s="101">
+        <f>IF(J280&gt;0,(J280-K280)/J280,"")</f>
+        <v/>
       </c>
       <c r="M280" s="102" t="inlineStr"/>
     </row>
@@ -23287,10 +23662,11 @@
         <v>479.99</v>
       </c>
       <c r="K282" s="143" t="n">
-        <v>187.2</v>
-      </c>
-      <c r="L282" s="98" t="n">
-        <v>39</v>
+        <v>365.76</v>
+      </c>
+      <c r="L282" s="98">
+        <f>IF(J282&gt;0,(J282-K282)/J282,"")</f>
+        <v/>
       </c>
       <c r="M282" s="99" t="inlineStr"/>
     </row>
@@ -23332,10 +23708,11 @@
         <v>1196</v>
       </c>
       <c r="K283" s="143" t="n">
-        <v>466.44</v>
-      </c>
-      <c r="L283" s="101" t="n">
-        <v>39</v>
+        <v>1196</v>
+      </c>
+      <c r="L283" s="101">
+        <f>IF(J283&gt;0,(J283-K283)/J283,"")</f>
+        <v/>
       </c>
       <c r="M283" s="102" t="inlineStr"/>
     </row>
@@ -23377,10 +23754,11 @@
         <v>1196</v>
       </c>
       <c r="K284" s="143" t="n">
-        <v>466.44</v>
-      </c>
-      <c r="L284" s="98" t="n">
-        <v>39</v>
+        <v>1196</v>
+      </c>
+      <c r="L284" s="98">
+        <f>IF(J284&gt;0,(J284-K284)/J284,"")</f>
+        <v/>
       </c>
       <c r="M284" s="99" t="inlineStr"/>
     </row>
@@ -23430,13 +23808,14 @@
         </is>
       </c>
       <c r="J286" s="141" t="n">
-        <v>799</v>
+        <v>590</v>
       </c>
       <c r="K286" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L286" s="101" t="n">
-        <v>26</v>
+        <v>419</v>
+      </c>
+      <c r="L286" s="101">
+        <f>IF(J286&gt;0,(J286-K286)/J286,"")</f>
+        <v/>
       </c>
       <c r="M286" s="102" t="inlineStr"/>
     </row>
@@ -23479,13 +23858,14 @@
         </is>
       </c>
       <c r="J287" s="142" t="n">
-        <v>799</v>
+        <v>590</v>
       </c>
       <c r="K287" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L287" s="98" t="n">
-        <v>26</v>
+        <v>419</v>
+      </c>
+      <c r="L287" s="98">
+        <f>IF(J287&gt;0,(J287-K287)/J287,"")</f>
+        <v/>
       </c>
       <c r="M287" s="99" t="inlineStr"/>
     </row>
@@ -23528,13 +23908,14 @@
         </is>
       </c>
       <c r="J288" s="141" t="n">
-        <v>799</v>
+        <v>590</v>
       </c>
       <c r="K288" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L288" s="101" t="n">
-        <v>26</v>
+        <v>419</v>
+      </c>
+      <c r="L288" s="101">
+        <f>IF(J288&gt;0,(J288-K288)/J288,"")</f>
+        <v/>
       </c>
       <c r="M288" s="102" t="inlineStr"/>
     </row>
@@ -23577,13 +23958,14 @@
         </is>
       </c>
       <c r="J289" s="142" t="n">
-        <v>799</v>
+        <v>590</v>
       </c>
       <c r="K289" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L289" s="98" t="n">
-        <v>26</v>
+        <v>419</v>
+      </c>
+      <c r="L289" s="98">
+        <f>IF(J289&gt;0,(J289-K289)/J289,"")</f>
+        <v/>
       </c>
       <c r="M289" s="99" t="inlineStr"/>
     </row>
@@ -23626,13 +24008,14 @@
         </is>
       </c>
       <c r="J290" s="141" t="n">
-        <v>799</v>
+        <v>590</v>
       </c>
       <c r="K290" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L290" s="101" t="n">
-        <v>26</v>
+        <v>419</v>
+      </c>
+      <c r="L290" s="101">
+        <f>IF(J290&gt;0,(J290-K290)/J290,"")</f>
+        <v/>
       </c>
       <c r="M290" s="102" t="inlineStr"/>
     </row>
@@ -23675,13 +24058,14 @@
         </is>
       </c>
       <c r="J291" s="142" t="n">
-        <v>799</v>
+        <v>590</v>
       </c>
       <c r="K291" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L291" s="98" t="n">
-        <v>26</v>
+        <v>419</v>
+      </c>
+      <c r="L291" s="98">
+        <f>IF(J291&gt;0,(J291-K291)/J291,"")</f>
+        <v/>
       </c>
       <c r="M291" s="99" t="inlineStr"/>
     </row>
@@ -23730,10 +24114,11 @@
         <v>799</v>
       </c>
       <c r="K293" s="143" t="n">
-        <v>207.74</v>
-      </c>
-      <c r="L293" s="101" t="n">
-        <v>26</v>
+        <v>449</v>
+      </c>
+      <c r="L293" s="101">
+        <f>IF(J293&gt;0,(J293-K293)/J293,"")</f>
+        <v/>
       </c>
       <c r="M293" s="102" t="inlineStr"/>
     </row>
@@ -24188,7 +24573,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="90" t="inlineStr">
         <is>
-          <t>125 itens   |   Valor: R$ 623.704,25   |   Desgaste medio: 3,1/5</t>
+          <t>125 itens   |   Valor: R$ 446.936,35   |   Desgaste medio: 3,1/5</t>
         </is>
       </c>
     </row>
@@ -24306,13 +24691,14 @@
         </is>
       </c>
       <c r="J6" s="142" t="n">
-        <v>3558.61</v>
+        <v>131.61</v>
       </c>
       <c r="K6" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L6" s="98" t="n">
-        <v>39</v>
+        <v>131.61</v>
+      </c>
+      <c r="L6" s="98">
+        <f>IF(J6&gt;0,(J6-K6)/J6,"")</f>
+        <v/>
       </c>
       <c r="M6" s="99" t="inlineStr"/>
     </row>
@@ -24369,10 +24755,11 @@
         <v>1600</v>
       </c>
       <c r="K8" s="143" t="n">
-        <v>624</v>
-      </c>
-      <c r="L8" s="101" t="n">
-        <v>39</v>
+        <v>2999</v>
+      </c>
+      <c r="L8" s="101">
+        <f>IF(J8&gt;0,(J8-K8)/J8,"")</f>
+        <v/>
       </c>
       <c r="M8" s="102" t="inlineStr">
         <is>
@@ -24419,13 +24806,14 @@
         </is>
       </c>
       <c r="J9" s="142" t="n">
-        <v>2036.94</v>
+        <v>1600</v>
       </c>
       <c r="K9" s="143" t="n">
-        <v>794.41</v>
-      </c>
-      <c r="L9" s="98" t="n">
-        <v>39</v>
+        <v>2999</v>
+      </c>
+      <c r="L9" s="98">
+        <f>IF(J9&gt;0,(J9-K9)/J9,"")</f>
+        <v/>
       </c>
       <c r="M9" s="99" t="inlineStr"/>
     </row>
@@ -24471,10 +24859,11 @@
         <v>4800</v>
       </c>
       <c r="K10" s="143" t="n">
-        <v>624</v>
-      </c>
-      <c r="L10" s="101" t="n">
-        <v>13</v>
+        <v>4800</v>
+      </c>
+      <c r="L10" s="101">
+        <f>IF(J10&gt;0,(J10-K10)/J10,"")</f>
+        <v/>
       </c>
       <c r="M10" s="102" t="inlineStr">
         <is>
@@ -24528,10 +24917,11 @@
         <v>449.28</v>
       </c>
       <c r="K11" s="143" t="n">
-        <v>116.81</v>
-      </c>
-      <c r="L11" s="98" t="n">
-        <v>26</v>
+        <v>449.28</v>
+      </c>
+      <c r="L11" s="98">
+        <f>IF(J11&gt;0,(J11-K11)/J11,"")</f>
+        <v/>
       </c>
       <c r="M11" s="99" t="inlineStr">
         <is>
@@ -24589,13 +24979,14 @@
         </is>
       </c>
       <c r="J13" s="141" t="n">
-        <v>2579</v>
+        <v>550</v>
       </c>
       <c r="K13" s="143" t="n">
-        <v>1005.81</v>
-      </c>
-      <c r="L13" s="101" t="n">
-        <v>39</v>
+        <v>759</v>
+      </c>
+      <c r="L13" s="101">
+        <f>IF(J13&gt;0,(J13-K13)/J13,"")</f>
+        <v/>
       </c>
       <c r="M13" s="102" t="inlineStr"/>
     </row>
@@ -24645,10 +25036,11 @@
         <v>2579</v>
       </c>
       <c r="K14" s="143" t="n">
-        <v>670.54</v>
-      </c>
-      <c r="L14" s="98" t="n">
-        <v>26</v>
+        <v>2088</v>
+      </c>
+      <c r="L14" s="98">
+        <f>IF(J14&gt;0,(J14-K14)/J14,"")</f>
+        <v/>
       </c>
       <c r="M14" s="99" t="inlineStr">
         <is>
@@ -24702,13 +25094,14 @@
         </is>
       </c>
       <c r="J16" s="141" t="n">
-        <v>3558.61</v>
+        <v>710.53</v>
       </c>
       <c r="K16" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L16" s="101" t="n">
-        <v>39</v>
+        <v>971</v>
+      </c>
+      <c r="L16" s="101">
+        <f>IF(J16&gt;0,(J16-K16)/J16,"")</f>
+        <v/>
       </c>
       <c r="M16" s="102" t="inlineStr"/>
     </row>
@@ -24755,13 +25148,14 @@
         </is>
       </c>
       <c r="J17" s="142" t="n">
-        <v>3558.61</v>
+        <v>1848.27</v>
       </c>
       <c r="K17" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L17" s="98" t="n">
-        <v>39</v>
+        <v>1848.27</v>
+      </c>
+      <c r="L17" s="98">
+        <f>IF(J17&gt;0,(J17-K17)/J17,"")</f>
+        <v/>
       </c>
       <c r="M17" s="99" t="inlineStr"/>
     </row>
@@ -24814,10 +25208,11 @@
         <v>2828.79</v>
       </c>
       <c r="K19" s="143" t="n">
-        <v>1103.23</v>
-      </c>
-      <c r="L19" s="101" t="n">
-        <v>39</v>
+        <v>1356</v>
+      </c>
+      <c r="L19" s="101">
+        <f>IF(J19&gt;0,(J19-K19)/J19,"")</f>
+        <v/>
       </c>
       <c r="M19" s="102" t="inlineStr"/>
     </row>
@@ -24871,13 +25266,14 @@
         </is>
       </c>
       <c r="J21" s="142" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K21" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L21" s="98" t="n">
-        <v>39</v>
+        <v>4699.9</v>
+      </c>
+      <c r="L21" s="98">
+        <f>IF(J21&gt;0,(J21-K21)/J21,"")</f>
+        <v/>
       </c>
       <c r="M21" s="99" t="inlineStr"/>
     </row>
@@ -24924,13 +25320,14 @@
         </is>
       </c>
       <c r="J22" s="141" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K22" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L22" s="101" t="n">
-        <v>39</v>
+        <v>4699.9</v>
+      </c>
+      <c r="L22" s="101">
+        <f>IF(J22&gt;0,(J22-K22)/J22,"")</f>
+        <v/>
       </c>
       <c r="M22" s="102" t="inlineStr"/>
     </row>
@@ -24977,13 +25374,14 @@
         </is>
       </c>
       <c r="J23" s="142" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K23" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L23" s="98" t="n">
-        <v>39</v>
+        <v>4699.9</v>
+      </c>
+      <c r="L23" s="98">
+        <f>IF(J23&gt;0,(J23-K23)/J23,"")</f>
+        <v/>
       </c>
       <c r="M23" s="99" t="inlineStr"/>
     </row>
@@ -25030,13 +25428,14 @@
         </is>
       </c>
       <c r="J24" s="141" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K24" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L24" s="101" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L24" s="101">
+        <f>IF(J24&gt;0,(J24-K24)/J24,"")</f>
+        <v/>
       </c>
       <c r="M24" s="102" t="inlineStr"/>
     </row>
@@ -25093,10 +25492,11 @@
         <v>4199</v>
       </c>
       <c r="K26" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L26" s="98" t="n">
-        <v>39</v>
+        <v>4199</v>
+      </c>
+      <c r="L26" s="98">
+        <f>IF(J26&gt;0,(J26-K26)/J26,"")</f>
+        <v/>
       </c>
       <c r="M26" s="99" t="inlineStr"/>
     </row>
@@ -25150,13 +25550,14 @@
         </is>
       </c>
       <c r="J28" s="141" t="n">
-        <v>3558.61</v>
+        <v>2299</v>
       </c>
       <c r="K28" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L28" s="101" t="n">
-        <v>39</v>
+        <v>7839</v>
+      </c>
+      <c r="L28" s="101">
+        <f>IF(J28&gt;0,(J28-K28)/J28,"")</f>
+        <v/>
       </c>
       <c r="M28" s="102" t="inlineStr"/>
     </row>
@@ -25203,13 +25604,14 @@
         </is>
       </c>
       <c r="J29" s="142" t="n">
-        <v>3558.61</v>
+        <v>2299</v>
       </c>
       <c r="K29" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L29" s="98" t="n">
-        <v>39</v>
+        <v>6619</v>
+      </c>
+      <c r="L29" s="98">
+        <f>IF(J29&gt;0,(J29-K29)/J29,"")</f>
+        <v/>
       </c>
       <c r="M29" s="99" t="inlineStr"/>
     </row>
@@ -25255,13 +25657,14 @@
         </is>
       </c>
       <c r="J31" s="141" t="n">
-        <v>3558.61</v>
+        <v>2299</v>
       </c>
       <c r="K31" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L31" s="101" t="n">
-        <v>39</v>
+        <v>2088</v>
+      </c>
+      <c r="L31" s="101">
+        <f>IF(J31&gt;0,(J31-K31)/J31,"")</f>
+        <v/>
       </c>
       <c r="M31" s="102" t="inlineStr"/>
     </row>
@@ -25315,13 +25718,14 @@
         </is>
       </c>
       <c r="J33" s="142" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K33" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L33" s="98" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L33" s="98">
+        <f>IF(J33&gt;0,(J33-K33)/J33,"")</f>
+        <v/>
       </c>
       <c r="M33" s="99" t="inlineStr"/>
     </row>
@@ -25375,13 +25779,14 @@
         </is>
       </c>
       <c r="J35" s="141" t="n">
-        <v>10710</v>
+        <v>6349</v>
       </c>
       <c r="K35" s="143" t="n">
-        <v>4176.9</v>
-      </c>
-      <c r="L35" s="101" t="n">
-        <v>39</v>
+        <v>6149</v>
+      </c>
+      <c r="L35" s="101">
+        <f>IF(J35&gt;0,(J35-K35)/J35,"")</f>
+        <v/>
       </c>
       <c r="M35" s="102" t="inlineStr"/>
     </row>
@@ -25428,13 +25833,14 @@
         </is>
       </c>
       <c r="J36" s="142" t="n">
-        <v>10710</v>
+        <v>6349</v>
       </c>
       <c r="K36" s="143" t="n">
-        <v>4176.9</v>
-      </c>
-      <c r="L36" s="98" t="n">
-        <v>39</v>
+        <v>6149</v>
+      </c>
+      <c r="L36" s="98">
+        <f>IF(J36&gt;0,(J36-K36)/J36,"")</f>
+        <v/>
       </c>
       <c r="M36" s="99" t="inlineStr"/>
     </row>
@@ -25484,10 +25890,11 @@
         <v>11581.68</v>
       </c>
       <c r="K37" s="143" t="n">
-        <v>7875.54</v>
-      </c>
-      <c r="L37" s="101" t="n">
-        <v>68</v>
+        <v>8499</v>
+      </c>
+      <c r="L37" s="101">
+        <f>IF(J37&gt;0,(J37-K37)/J37,"")</f>
+        <v/>
       </c>
       <c r="M37" s="102" t="inlineStr">
         <is>
@@ -25541,10 +25948,11 @@
         <v>11581.68</v>
       </c>
       <c r="K38" s="143" t="n">
-        <v>9844.43</v>
-      </c>
-      <c r="L38" s="98" t="n">
-        <v>85</v>
+        <v>8499</v>
+      </c>
+      <c r="L38" s="98">
+        <f>IF(J38&gt;0,(J38-K38)/J38,"")</f>
+        <v/>
       </c>
       <c r="M38" s="99" t="inlineStr">
         <is>
@@ -25598,10 +26006,11 @@
         <v>10710</v>
       </c>
       <c r="K39" s="143" t="n">
-        <v>7282.8</v>
-      </c>
-      <c r="L39" s="101" t="n">
-        <v>68</v>
+        <v>8354</v>
+      </c>
+      <c r="L39" s="101">
+        <f>IF(J39&gt;0,(J39-K39)/J39,"")</f>
+        <v/>
       </c>
       <c r="M39" s="102" t="inlineStr"/>
     </row>
@@ -25651,10 +26060,11 @@
         <v>10710</v>
       </c>
       <c r="K40" s="143" t="n">
-        <v>7282.8</v>
-      </c>
-      <c r="L40" s="98" t="n">
-        <v>68</v>
+        <v>8354</v>
+      </c>
+      <c r="L40" s="98">
+        <f>IF(J40&gt;0,(J40-K40)/J40,"")</f>
+        <v/>
       </c>
       <c r="M40" s="99" t="inlineStr"/>
     </row>
@@ -25704,10 +26114,11 @@
         <v>12530</v>
       </c>
       <c r="K41" s="143" t="n">
-        <v>4886.7</v>
-      </c>
-      <c r="L41" s="101" t="n">
-        <v>39</v>
+        <v>8990</v>
+      </c>
+      <c r="L41" s="101">
+        <f>IF(J41&gt;0,(J41-K41)/J41,"")</f>
+        <v/>
       </c>
       <c r="M41" s="102" t="inlineStr">
         <is>
@@ -25761,10 +26172,11 @@
         <v>12530</v>
       </c>
       <c r="K42" s="143" t="n">
-        <v>8520.4</v>
-      </c>
-      <c r="L42" s="98" t="n">
-        <v>68</v>
+        <v>8990</v>
+      </c>
+      <c r="L42" s="98">
+        <f>IF(J42&gt;0,(J42-K42)/J42,"")</f>
+        <v/>
       </c>
       <c r="M42" s="99" t="inlineStr"/>
     </row>
@@ -25814,10 +26226,11 @@
         <v>12530</v>
       </c>
       <c r="K43" s="143" t="n">
-        <v>8520.4</v>
-      </c>
-      <c r="L43" s="101" t="n">
-        <v>68</v>
+        <v>8990</v>
+      </c>
+      <c r="L43" s="101">
+        <f>IF(J43&gt;0,(J43-K43)/J43,"")</f>
+        <v/>
       </c>
       <c r="M43" s="102" t="inlineStr"/>
     </row>
@@ -25867,10 +26280,11 @@
         <v>12530</v>
       </c>
       <c r="K44" s="143" t="n">
-        <v>8520.4</v>
-      </c>
-      <c r="L44" s="98" t="n">
-        <v>68</v>
+        <v>8990</v>
+      </c>
+      <c r="L44" s="98">
+        <f>IF(J44&gt;0,(J44-K44)/J44,"")</f>
+        <v/>
       </c>
       <c r="M44" s="99" t="inlineStr"/>
     </row>
@@ -25920,10 +26334,11 @@
         <v>12530</v>
       </c>
       <c r="K45" s="143" t="n">
-        <v>8520.4</v>
-      </c>
-      <c r="L45" s="101" t="n">
-        <v>68</v>
+        <v>8990</v>
+      </c>
+      <c r="L45" s="101">
+        <f>IF(J45&gt;0,(J45-K45)/J45,"")</f>
+        <v/>
       </c>
       <c r="M45" s="102" t="inlineStr"/>
     </row>
@@ -25973,10 +26388,11 @@
         <v>12530</v>
       </c>
       <c r="K46" s="143" t="n">
-        <v>8520.4</v>
-      </c>
-      <c r="L46" s="98" t="n">
-        <v>68</v>
+        <v>8990</v>
+      </c>
+      <c r="L46" s="98">
+        <f>IF(J46&gt;0,(J46-K46)/J46,"")</f>
+        <v/>
       </c>
       <c r="M46" s="99" t="inlineStr"/>
     </row>
@@ -26022,10 +26438,11 @@
         <v>10710</v>
       </c>
       <c r="K47" s="143" t="n">
-        <v>1392.3</v>
-      </c>
-      <c r="L47" s="101" t="n">
-        <v>13</v>
+        <v>10710</v>
+      </c>
+      <c r="L47" s="101">
+        <f>IF(J47&gt;0,(J47-K47)/J47,"")</f>
+        <v/>
       </c>
       <c r="M47" s="102" t="inlineStr"/>
     </row>
@@ -26068,13 +26485,14 @@
         </is>
       </c>
       <c r="J48" s="142" t="n">
-        <v>10710</v>
+        <v>2470</v>
       </c>
       <c r="K48" s="143" t="n">
-        <v>4176.9</v>
-      </c>
-      <c r="L48" s="98" t="n">
-        <v>39</v>
+        <v>2470</v>
+      </c>
+      <c r="L48" s="98">
+        <f>IF(J48&gt;0,(J48-K48)/J48,"")</f>
+        <v/>
       </c>
       <c r="M48" s="99" t="inlineStr"/>
     </row>
@@ -26117,13 +26535,14 @@
         </is>
       </c>
       <c r="J49" s="141" t="n">
-        <v>10710</v>
+        <v>1699</v>
       </c>
       <c r="K49" s="143" t="n">
-        <v>4176.9</v>
-      </c>
-      <c r="L49" s="101" t="n">
-        <v>39</v>
+        <v>1699</v>
+      </c>
+      <c r="L49" s="101">
+        <f>IF(J49&gt;0,(J49-K49)/J49,"")</f>
+        <v/>
       </c>
       <c r="M49" s="102" t="inlineStr"/>
     </row>
@@ -26166,13 +26585,14 @@
         </is>
       </c>
       <c r="J50" s="142" t="n">
-        <v>10710</v>
+        <v>2499</v>
       </c>
       <c r="K50" s="143" t="n">
-        <v>4176.9</v>
-      </c>
-      <c r="L50" s="98" t="n">
-        <v>39</v>
+        <v>2499</v>
+      </c>
+      <c r="L50" s="98">
+        <f>IF(J50&gt;0,(J50-K50)/J50,"")</f>
+        <v/>
       </c>
       <c r="M50" s="99" t="inlineStr"/>
     </row>
@@ -26215,13 +26635,14 @@
         </is>
       </c>
       <c r="J51" s="141" t="n">
-        <v>10710</v>
+        <v>2299</v>
       </c>
       <c r="K51" s="143" t="n">
-        <v>4176.9</v>
-      </c>
-      <c r="L51" s="101" t="n">
-        <v>39</v>
+        <v>1351</v>
+      </c>
+      <c r="L51" s="101">
+        <f>IF(J51&gt;0,(J51-K51)/J51,"")</f>
+        <v/>
       </c>
       <c r="M51" s="102" t="inlineStr"/>
     </row>
@@ -26270,10 +26691,11 @@
         <v>1600</v>
       </c>
       <c r="K53" s="143" t="n">
-        <v>624</v>
-      </c>
-      <c r="L53" s="98" t="n">
-        <v>39</v>
+        <v>1119</v>
+      </c>
+      <c r="L53" s="98">
+        <f>IF(J53&gt;0,(J53-K53)/J53,"")</f>
+        <v/>
       </c>
       <c r="M53" s="99" t="inlineStr"/>
     </row>
@@ -26327,13 +26749,14 @@
         </is>
       </c>
       <c r="J55" s="141" t="n">
-        <v>3558.61</v>
+        <v>2299</v>
       </c>
       <c r="K55" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L55" s="101" t="n">
-        <v>39</v>
+        <v>4245</v>
+      </c>
+      <c r="L55" s="101">
+        <f>IF(J55&gt;0,(J55-K55)/J55,"")</f>
+        <v/>
       </c>
       <c r="M55" s="102" t="inlineStr"/>
     </row>
@@ -26390,10 +26813,11 @@
         <v>3500</v>
       </c>
       <c r="K57" s="143" t="n">
-        <v>2380</v>
-      </c>
-      <c r="L57" s="98" t="n">
-        <v>68</v>
+        <v>2500</v>
+      </c>
+      <c r="L57" s="98">
+        <f>IF(J57&gt;0,(J57-K57)/J57,"")</f>
+        <v/>
       </c>
       <c r="M57" s="99" t="inlineStr"/>
     </row>
@@ -26443,10 +26867,11 @@
         <v>3258</v>
       </c>
       <c r="K58" s="143" t="n">
-        <v>1270.62</v>
-      </c>
-      <c r="L58" s="101" t="n">
-        <v>39</v>
+        <v>3258</v>
+      </c>
+      <c r="L58" s="101">
+        <f>IF(J58&gt;0,(J58-K58)/J58,"")</f>
+        <v/>
       </c>
       <c r="M58" s="102" t="inlineStr"/>
     </row>
@@ -26496,10 +26921,11 @@
         <v>3500</v>
       </c>
       <c r="K59" s="143" t="n">
-        <v>2380</v>
-      </c>
-      <c r="L59" s="98" t="n">
-        <v>68</v>
+        <v>2500</v>
+      </c>
+      <c r="L59" s="98">
+        <f>IF(J59&gt;0,(J59-K59)/J59,"")</f>
+        <v/>
       </c>
       <c r="M59" s="99" t="inlineStr"/>
     </row>
@@ -26549,10 +26975,11 @@
         <v>13997</v>
       </c>
       <c r="K60" s="143" t="n">
-        <v>9517.959999999999</v>
-      </c>
-      <c r="L60" s="101" t="n">
-        <v>68</v>
+        <v>11319</v>
+      </c>
+      <c r="L60" s="101">
+        <f>IF(J60&gt;0,(J60-K60)/J60,"")</f>
+        <v/>
       </c>
       <c r="M60" s="102" t="inlineStr"/>
     </row>
@@ -26602,10 +27029,11 @@
         <v>8000</v>
       </c>
       <c r="K61" s="143" t="n">
-        <v>3120</v>
-      </c>
-      <c r="L61" s="98" t="n">
-        <v>39</v>
+        <v>8000</v>
+      </c>
+      <c r="L61" s="98">
+        <f>IF(J61&gt;0,(J61-K61)/J61,"")</f>
+        <v/>
       </c>
       <c r="M61" s="99" t="inlineStr"/>
     </row>
@@ -26655,10 +27083,11 @@
         <v>22499.99</v>
       </c>
       <c r="K62" s="143" t="n">
-        <v>15299.99</v>
-      </c>
-      <c r="L62" s="101" t="n">
-        <v>68</v>
+        <v>15900</v>
+      </c>
+      <c r="L62" s="101">
+        <f>IF(J62&gt;0,(J62-K62)/J62,"")</f>
+        <v/>
       </c>
       <c r="M62" s="102" t="inlineStr"/>
     </row>
@@ -26715,10 +27144,11 @@
         <v>610.9</v>
       </c>
       <c r="K64" s="143" t="n">
-        <v>238.25</v>
-      </c>
-      <c r="L64" s="98" t="n">
-        <v>39</v>
+        <v>497.94</v>
+      </c>
+      <c r="L64" s="98">
+        <f>IF(J64&gt;0,(J64-K64)/J64,"")</f>
+        <v/>
       </c>
       <c r="M64" s="99" t="inlineStr"/>
     </row>
@@ -26768,10 +27198,11 @@
         <v>478.8</v>
       </c>
       <c r="K65" s="143" t="n">
-        <v>186.73</v>
-      </c>
-      <c r="L65" s="101" t="n">
-        <v>39</v>
+        <v>425</v>
+      </c>
+      <c r="L65" s="101">
+        <f>IF(J65&gt;0,(J65-K65)/J65,"")</f>
+        <v/>
       </c>
       <c r="M65" s="102" t="inlineStr"/>
     </row>
@@ -26821,10 +27252,11 @@
         <v>478.8</v>
       </c>
       <c r="K66" s="143" t="n">
-        <v>186.73</v>
-      </c>
-      <c r="L66" s="98" t="n">
-        <v>39</v>
+        <v>425</v>
+      </c>
+      <c r="L66" s="98">
+        <f>IF(J66&gt;0,(J66-K66)/J66,"")</f>
+        <v/>
       </c>
       <c r="M66" s="99" t="inlineStr"/>
     </row>
@@ -26874,10 +27306,11 @@
         <v>478.8</v>
       </c>
       <c r="K67" s="143" t="n">
-        <v>186.73</v>
-      </c>
-      <c r="L67" s="101" t="n">
-        <v>39</v>
+        <v>425</v>
+      </c>
+      <c r="L67" s="101">
+        <f>IF(J67&gt;0,(J67-K67)/J67,"")</f>
+        <v/>
       </c>
       <c r="M67" s="102" t="inlineStr"/>
     </row>
@@ -26927,10 +27360,11 @@
         <v>478.8</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>186.73</v>
-      </c>
-      <c r="L68" s="98" t="n">
-        <v>39</v>
+        <v>425</v>
+      </c>
+      <c r="L68" s="98">
+        <f>IF(J68&gt;0,(J68-K68)/J68,"")</f>
+        <v/>
       </c>
       <c r="M68" s="99" t="inlineStr"/>
     </row>
@@ -26980,10 +27414,11 @@
         <v>478.8</v>
       </c>
       <c r="K69" s="143" t="n">
-        <v>186.73</v>
-      </c>
-      <c r="L69" s="101" t="n">
-        <v>39</v>
+        <v>425</v>
+      </c>
+      <c r="L69" s="101">
+        <f>IF(J69&gt;0,(J69-K69)/J69,"")</f>
+        <v/>
       </c>
       <c r="M69" s="102" t="inlineStr"/>
     </row>
@@ -27033,10 +27468,11 @@
         <v>478.8</v>
       </c>
       <c r="K70" s="143" t="n">
-        <v>186.73</v>
-      </c>
-      <c r="L70" s="98" t="n">
-        <v>39</v>
+        <v>435</v>
+      </c>
+      <c r="L70" s="98">
+        <f>IF(J70&gt;0,(J70-K70)/J70,"")</f>
+        <v/>
       </c>
       <c r="M70" s="99" t="inlineStr"/>
     </row>
@@ -27086,10 +27522,11 @@
         <v>478.8</v>
       </c>
       <c r="K71" s="143" t="n">
-        <v>186.73</v>
-      </c>
-      <c r="L71" s="101" t="n">
-        <v>39</v>
+        <v>435</v>
+      </c>
+      <c r="L71" s="101">
+        <f>IF(J71&gt;0,(J71-K71)/J71,"")</f>
+        <v/>
       </c>
       <c r="M71" s="102" t="inlineStr"/>
     </row>
@@ -27139,10 +27576,11 @@
         <v>478.8</v>
       </c>
       <c r="K72" s="143" t="n">
-        <v>186.73</v>
-      </c>
-      <c r="L72" s="98" t="n">
-        <v>39</v>
+        <v>435</v>
+      </c>
+      <c r="L72" s="98">
+        <f>IF(J72&gt;0,(J72-K72)/J72,"")</f>
+        <v/>
       </c>
       <c r="M72" s="99" t="inlineStr"/>
     </row>
@@ -27199,10 +27637,11 @@
         <v>1790</v>
       </c>
       <c r="K74" s="143" t="n">
-        <v>698.1</v>
-      </c>
-      <c r="L74" s="101" t="n">
-        <v>39</v>
+        <v>2229.49</v>
+      </c>
+      <c r="L74" s="101">
+        <f>IF(J74&gt;0,(J74-K74)/J74,"")</f>
+        <v/>
       </c>
       <c r="M74" s="102" t="inlineStr"/>
     </row>
@@ -27252,10 +27691,11 @@
         <v>1790</v>
       </c>
       <c r="K75" s="143" t="n">
-        <v>698.1</v>
-      </c>
-      <c r="L75" s="98" t="n">
-        <v>39</v>
+        <v>2229.49</v>
+      </c>
+      <c r="L75" s="98">
+        <f>IF(J75&gt;0,(J75-K75)/J75,"")</f>
+        <v/>
       </c>
       <c r="M75" s="99" t="inlineStr"/>
     </row>
@@ -27305,10 +27745,11 @@
         <v>1790</v>
       </c>
       <c r="K76" s="143" t="n">
-        <v>698.1</v>
-      </c>
-      <c r="L76" s="101" t="n">
-        <v>39</v>
+        <v>2229.49</v>
+      </c>
+      <c r="L76" s="101">
+        <f>IF(J76&gt;0,(J76-K76)/J76,"")</f>
+        <v/>
       </c>
       <c r="M76" s="102" t="inlineStr"/>
     </row>
@@ -27365,10 +27806,11 @@
         <v>1733.16</v>
       </c>
       <c r="K78" s="143" t="n">
-        <v>675.9299999999999</v>
-      </c>
-      <c r="L78" s="98" t="n">
-        <v>39</v>
+        <v>1200</v>
+      </c>
+      <c r="L78" s="98">
+        <f>IF(J78&gt;0,(J78-K78)/J78,"")</f>
+        <v/>
       </c>
       <c r="M78" s="99" t="inlineStr"/>
     </row>
@@ -27418,10 +27860,11 @@
         <v>1733.16</v>
       </c>
       <c r="K79" s="143" t="n">
-        <v>675.9299999999999</v>
-      </c>
-      <c r="L79" s="101" t="n">
-        <v>39</v>
+        <v>1200</v>
+      </c>
+      <c r="L79" s="101">
+        <f>IF(J79&gt;0,(J79-K79)/J79,"")</f>
+        <v/>
       </c>
       <c r="M79" s="102" t="inlineStr"/>
     </row>
@@ -27471,13 +27914,14 @@
         </is>
       </c>
       <c r="J81" s="142" t="n">
-        <v>3558.61</v>
+        <v>2299</v>
       </c>
       <c r="K81" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L81" s="98" t="n">
-        <v>39</v>
+        <v>219.97</v>
+      </c>
+      <c r="L81" s="98">
+        <f>IF(J81&gt;0,(J81-K81)/J81,"")</f>
+        <v/>
       </c>
       <c r="M81" s="99" t="inlineStr"/>
     </row>
@@ -27531,13 +27975,14 @@
         </is>
       </c>
       <c r="J83" s="141" t="n">
-        <v>3558.61</v>
+        <v>2299</v>
       </c>
       <c r="K83" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L83" s="101" t="n">
-        <v>39</v>
+        <v>2088</v>
+      </c>
+      <c r="L83" s="101">
+        <f>IF(J83&gt;0,(J83-K83)/J83,"")</f>
+        <v/>
       </c>
       <c r="M83" s="102" t="inlineStr"/>
     </row>
@@ -27590,10 +28035,11 @@
         <v>2490</v>
       </c>
       <c r="K85" s="143" t="n">
-        <v>971.1</v>
-      </c>
-      <c r="L85" s="98" t="n">
-        <v>39</v>
+        <v>2490</v>
+      </c>
+      <c r="L85" s="98">
+        <f>IF(J85&gt;0,(J85-K85)/J85,"")</f>
+        <v/>
       </c>
       <c r="M85" s="99" t="inlineStr"/>
     </row>
@@ -27643,10 +28089,11 @@
         <v>4500</v>
       </c>
       <c r="K86" s="143" t="n">
-        <v>1755</v>
-      </c>
-      <c r="L86" s="101" t="n">
-        <v>39</v>
+        <v>4500</v>
+      </c>
+      <c r="L86" s="101">
+        <f>IF(J86&gt;0,(J86-K86)/J86,"")</f>
+        <v/>
       </c>
       <c r="M86" s="102" t="inlineStr">
         <is>
@@ -27697,13 +28144,14 @@
         </is>
       </c>
       <c r="J87" s="142" t="n">
-        <v>4500</v>
+        <v>2632.15</v>
       </c>
       <c r="K87" s="143" t="n">
-        <v>1755</v>
-      </c>
-      <c r="L87" s="98" t="n">
-        <v>39</v>
+        <v>3666</v>
+      </c>
+      <c r="L87" s="98">
+        <f>IF(J87&gt;0,(J87-K87)/J87,"")</f>
+        <v/>
       </c>
       <c r="M87" s="99" t="inlineStr">
         <is>
@@ -27757,13 +28205,14 @@
         </is>
       </c>
       <c r="J89" s="141" t="n">
-        <v>3558.61</v>
+        <v>2299</v>
       </c>
       <c r="K89" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L89" s="101" t="n">
-        <v>39</v>
+        <v>2088</v>
+      </c>
+      <c r="L89" s="101">
+        <f>IF(J89&gt;0,(J89-K89)/J89,"")</f>
+        <v/>
       </c>
       <c r="M89" s="102" t="inlineStr"/>
     </row>
@@ -27806,13 +28255,14 @@
         </is>
       </c>
       <c r="J90" s="142" t="n">
-        <v>3558.61</v>
+        <v>2299</v>
       </c>
       <c r="K90" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L90" s="98" t="n">
-        <v>39</v>
+        <v>2088</v>
+      </c>
+      <c r="L90" s="98">
+        <f>IF(J90&gt;0,(J90-K90)/J90,"")</f>
+        <v/>
       </c>
       <c r="M90" s="99" t="inlineStr"/>
     </row>
@@ -27869,10 +28319,11 @@
         <v>10990</v>
       </c>
       <c r="K92" s="143" t="n">
-        <v>4286.1</v>
-      </c>
-      <c r="L92" s="101" t="n">
-        <v>39</v>
+        <v>9998</v>
+      </c>
+      <c r="L92" s="101">
+        <f>IF(J92&gt;0,(J92-K92)/J92,"")</f>
+        <v/>
       </c>
       <c r="M92" s="102" t="inlineStr"/>
     </row>
@@ -27922,10 +28373,11 @@
         <v>10990</v>
       </c>
       <c r="K93" s="143" t="n">
-        <v>4286.1</v>
-      </c>
-      <c r="L93" s="98" t="n">
-        <v>39</v>
+        <v>9998</v>
+      </c>
+      <c r="L93" s="98">
+        <f>IF(J93&gt;0,(J93-K93)/J93,"")</f>
+        <v/>
       </c>
       <c r="M93" s="99" t="inlineStr"/>
     </row>
@@ -27982,10 +28434,11 @@
         <v>1400</v>
       </c>
       <c r="K95" s="143" t="n">
-        <v>364</v>
-      </c>
-      <c r="L95" s="101" t="n">
-        <v>26</v>
+        <v>1399.9</v>
+      </c>
+      <c r="L95" s="101">
+        <f>IF(J95&gt;0,(J95-K95)/J95,"")</f>
+        <v/>
       </c>
       <c r="M95" s="102" t="inlineStr"/>
     </row>
@@ -28032,13 +28485,14 @@
         </is>
       </c>
       <c r="J96" s="142" t="n">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="K96" s="143" t="n">
-        <v>546</v>
-      </c>
-      <c r="L96" s="98" t="n">
-        <v>39</v>
+        <v>300</v>
+      </c>
+      <c r="L96" s="98">
+        <f>IF(J96&gt;0,(J96-K96)/J96,"")</f>
+        <v/>
       </c>
       <c r="M96" s="99" t="inlineStr"/>
     </row>
@@ -28084,10 +28538,11 @@
         <v>1849</v>
       </c>
       <c r="K97" s="143" t="n">
-        <v>721.11</v>
-      </c>
-      <c r="L97" s="101" t="n">
-        <v>39</v>
+        <v>2249.9</v>
+      </c>
+      <c r="L97" s="101">
+        <f>IF(J97&gt;0,(J97-K97)/J97,"")</f>
+        <v/>
       </c>
       <c r="M97" s="102" t="inlineStr"/>
     </row>
@@ -28133,10 +28588,11 @@
         <v>1849</v>
       </c>
       <c r="K98" s="143" t="n">
-        <v>721.11</v>
-      </c>
-      <c r="L98" s="98" t="n">
-        <v>39</v>
+        <v>2249.9</v>
+      </c>
+      <c r="L98" s="98">
+        <f>IF(J98&gt;0,(J98-K98)/J98,"")</f>
+        <v/>
       </c>
       <c r="M98" s="99" t="inlineStr"/>
     </row>
@@ -28186,10 +28642,11 @@
         <v>1849</v>
       </c>
       <c r="K99" s="143" t="n">
-        <v>721.11</v>
-      </c>
-      <c r="L99" s="101" t="n">
-        <v>39</v>
+        <v>2249.9</v>
+      </c>
+      <c r="L99" s="101">
+        <f>IF(J99&gt;0,(J99-K99)/J99,"")</f>
+        <v/>
       </c>
       <c r="M99" s="102" t="inlineStr"/>
     </row>
@@ -28239,10 +28696,11 @@
         <v>4588.96</v>
       </c>
       <c r="K100" s="143" t="n">
-        <v>1789.69</v>
-      </c>
-      <c r="L100" s="98" t="n">
-        <v>39</v>
+        <v>2249.9</v>
+      </c>
+      <c r="L100" s="98">
+        <f>IF(J100&gt;0,(J100-K100)/J100,"")</f>
+        <v/>
       </c>
       <c r="M100" s="99" t="inlineStr"/>
     </row>
@@ -28289,13 +28747,14 @@
         </is>
       </c>
       <c r="J101" s="141" t="n">
-        <v>1400</v>
+        <v>12900</v>
       </c>
       <c r="K101" s="143" t="n">
-        <v>546</v>
-      </c>
-      <c r="L101" s="101" t="n">
-        <v>39</v>
+        <v>10490</v>
+      </c>
+      <c r="L101" s="101">
+        <f>IF(J101&gt;0,(J101-K101)/J101,"")</f>
+        <v/>
       </c>
       <c r="M101" s="102" t="inlineStr"/>
     </row>
@@ -28345,13 +28804,14 @@
         </is>
       </c>
       <c r="J103" s="142" t="n">
-        <v>3558.61</v>
+        <v>301.67</v>
       </c>
       <c r="K103" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L103" s="98" t="n">
-        <v>39</v>
+        <v>301.67</v>
+      </c>
+      <c r="L103" s="98">
+        <f>IF(J103&gt;0,(J103-K103)/J103,"")</f>
+        <v/>
       </c>
       <c r="M103" s="99" t="inlineStr"/>
     </row>
@@ -28401,13 +28861,14 @@
         </is>
       </c>
       <c r="J105" s="141" t="n">
-        <v>3563.22</v>
+        <v>1228</v>
       </c>
       <c r="K105" s="143" t="n">
-        <v>1389.66</v>
-      </c>
-      <c r="L105" s="101" t="n">
-        <v>39</v>
+        <v>1547</v>
+      </c>
+      <c r="L105" s="101">
+        <f>IF(J105&gt;0,(J105-K105)/J105,"")</f>
+        <v/>
       </c>
       <c r="M105" s="102" t="inlineStr"/>
     </row>
@@ -28453,10 +28914,11 @@
         <v>3563.22</v>
       </c>
       <c r="K106" s="143" t="n">
-        <v>926.4400000000001</v>
-      </c>
-      <c r="L106" s="98" t="n">
-        <v>26</v>
+        <v>1080</v>
+      </c>
+      <c r="L106" s="98">
+        <f>IF(J106&gt;0,(J106-K106)/J106,"")</f>
+        <v/>
       </c>
       <c r="M106" s="99" t="inlineStr"/>
     </row>
@@ -28499,13 +28961,14 @@
         </is>
       </c>
       <c r="J107" s="141" t="n">
-        <v>3563.22</v>
+        <v>1119</v>
       </c>
       <c r="K107" s="143" t="n">
-        <v>1389.66</v>
-      </c>
-      <c r="L107" s="101" t="n">
-        <v>39</v>
+        <v>1099</v>
+      </c>
+      <c r="L107" s="101">
+        <f>IF(J107&gt;0,(J107-K107)/J107,"")</f>
+        <v/>
       </c>
       <c r="M107" s="102" t="inlineStr"/>
     </row>
@@ -28552,13 +29015,14 @@
         </is>
       </c>
       <c r="J108" s="142" t="n">
-        <v>3563.22</v>
+        <v>2712</v>
       </c>
       <c r="K108" s="143" t="n">
-        <v>1389.66</v>
-      </c>
-      <c r="L108" s="98" t="n">
-        <v>39</v>
+        <v>2712</v>
+      </c>
+      <c r="L108" s="98">
+        <f>IF(J108&gt;0,(J108-K108)/J108,"")</f>
+        <v/>
       </c>
       <c r="M108" s="99" t="inlineStr">
         <is>
@@ -28605,13 +29069,14 @@
         </is>
       </c>
       <c r="J109" s="141" t="n">
-        <v>3563.22</v>
+        <v>1970</v>
       </c>
       <c r="K109" s="143" t="n">
-        <v>1389.66</v>
-      </c>
-      <c r="L109" s="101" t="n">
-        <v>39</v>
+        <v>148</v>
+      </c>
+      <c r="L109" s="101">
+        <f>IF(J109&gt;0,(J109-K109)/J109,"")</f>
+        <v/>
       </c>
       <c r="M109" s="102" t="inlineStr"/>
     </row>
@@ -28657,13 +29122,14 @@
         </is>
       </c>
       <c r="J111" s="142" t="n">
-        <v>3558.61</v>
+        <v>2299</v>
       </c>
       <c r="K111" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L111" s="98" t="n">
-        <v>39</v>
+        <v>2088</v>
+      </c>
+      <c r="L111" s="98">
+        <f>IF(J111&gt;0,(J111-K111)/J111,"")</f>
+        <v/>
       </c>
       <c r="M111" s="99" t="inlineStr"/>
     </row>
@@ -28717,13 +29183,14 @@
         </is>
       </c>
       <c r="J113" s="141" t="n">
-        <v>3558.61</v>
+        <v>1308.5</v>
       </c>
       <c r="K113" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L113" s="101" t="n">
-        <v>39</v>
+        <v>3581.65</v>
+      </c>
+      <c r="L113" s="101">
+        <f>IF(J113&gt;0,(J113-K113)/J113,"")</f>
+        <v/>
       </c>
       <c r="M113" s="102" t="inlineStr"/>
     </row>
@@ -28770,13 +29237,14 @@
         </is>
       </c>
       <c r="J114" s="142" t="n">
-        <v>3558.61</v>
+        <v>2233</v>
       </c>
       <c r="K114" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L114" s="98" t="n">
-        <v>39</v>
+        <v>2233</v>
+      </c>
+      <c r="L114" s="98">
+        <f>IF(J114&gt;0,(J114-K114)/J114,"")</f>
+        <v/>
       </c>
       <c r="M114" s="99" t="inlineStr"/>
     </row>
@@ -28823,13 +29291,14 @@
         </is>
       </c>
       <c r="J115" s="141" t="n">
-        <v>3558.61</v>
+        <v>995</v>
       </c>
       <c r="K115" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L115" s="101" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L115" s="101">
+        <f>IF(J115&gt;0,(J115-K115)/J115,"")</f>
+        <v/>
       </c>
       <c r="M115" s="102" t="inlineStr"/>
     </row>
@@ -28876,13 +29345,14 @@
         </is>
       </c>
       <c r="J116" s="142" t="n">
-        <v>3558.61</v>
+        <v>995</v>
       </c>
       <c r="K116" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L116" s="98" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L116" s="98">
+        <f>IF(J116&gt;0,(J116-K116)/J116,"")</f>
+        <v/>
       </c>
       <c r="M116" s="99" t="inlineStr"/>
     </row>
@@ -28929,13 +29399,14 @@
         </is>
       </c>
       <c r="J117" s="141" t="n">
-        <v>3558.61</v>
+        <v>1308.5</v>
       </c>
       <c r="K117" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L117" s="101" t="n">
-        <v>39</v>
+        <v>4129</v>
+      </c>
+      <c r="L117" s="101">
+        <f>IF(J117&gt;0,(J117-K117)/J117,"")</f>
+        <v/>
       </c>
       <c r="M117" s="102" t="inlineStr"/>
     </row>
@@ -28982,13 +29453,14 @@
         </is>
       </c>
       <c r="J118" s="142" t="n">
-        <v>3558.61</v>
+        <v>2250</v>
       </c>
       <c r="K118" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L118" s="98" t="n">
-        <v>39</v>
+        <v>979</v>
+      </c>
+      <c r="L118" s="98">
+        <f>IF(J118&gt;0,(J118-K118)/J118,"")</f>
+        <v/>
       </c>
       <c r="M118" s="99" t="inlineStr"/>
     </row>
@@ -29035,13 +29507,14 @@
         </is>
       </c>
       <c r="J119" s="141" t="n">
-        <v>3558.61</v>
+        <v>2750</v>
       </c>
       <c r="K119" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L119" s="101" t="n">
-        <v>39</v>
+        <v>979</v>
+      </c>
+      <c r="L119" s="101">
+        <f>IF(J119&gt;0,(J119-K119)/J119,"")</f>
+        <v/>
       </c>
       <c r="M119" s="102" t="inlineStr"/>
     </row>
@@ -29088,13 +29561,14 @@
         </is>
       </c>
       <c r="J120" s="142" t="n">
-        <v>3558.61</v>
+        <v>2750</v>
       </c>
       <c r="K120" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L120" s="98" t="n">
-        <v>39</v>
+        <v>2750</v>
+      </c>
+      <c r="L120" s="98">
+        <f>IF(J120&gt;0,(J120-K120)/J120,"")</f>
+        <v/>
       </c>
       <c r="M120" s="99" t="inlineStr"/>
     </row>
@@ -29141,13 +29615,14 @@
         </is>
       </c>
       <c r="J121" s="141" t="n">
-        <v>3558.61</v>
+        <v>2250</v>
       </c>
       <c r="K121" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L121" s="101" t="n">
-        <v>39</v>
+        <v>2250</v>
+      </c>
+      <c r="L121" s="101">
+        <f>IF(J121&gt;0,(J121-K121)/J121,"")</f>
+        <v/>
       </c>
       <c r="M121" s="102" t="inlineStr"/>
     </row>
@@ -29194,13 +29669,14 @@
         </is>
       </c>
       <c r="J122" s="142" t="n">
-        <v>3558.61</v>
+        <v>2250</v>
       </c>
       <c r="K122" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L122" s="98" t="n">
-        <v>39</v>
+        <v>1247.5</v>
+      </c>
+      <c r="L122" s="98">
+        <f>IF(J122&gt;0,(J122-K122)/J122,"")</f>
+        <v/>
       </c>
       <c r="M122" s="99" t="inlineStr"/>
     </row>
@@ -29247,13 +29723,14 @@
         </is>
       </c>
       <c r="J123" s="141" t="n">
-        <v>3558.61</v>
+        <v>1308.5</v>
       </c>
       <c r="K123" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L123" s="101" t="n">
-        <v>39</v>
+        <v>334.01</v>
+      </c>
+      <c r="L123" s="101">
+        <f>IF(J123&gt;0,(J123-K123)/J123,"")</f>
+        <v/>
       </c>
       <c r="M123" s="102" t="inlineStr"/>
     </row>
@@ -29296,13 +29773,14 @@
         </is>
       </c>
       <c r="J124" s="142" t="n">
-        <v>3558.61</v>
+        <v>1500</v>
       </c>
       <c r="K124" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L124" s="98" t="n">
-        <v>39</v>
+        <v>1500</v>
+      </c>
+      <c r="L124" s="98">
+        <f>IF(J124&gt;0,(J124-K124)/J124,"")</f>
+        <v/>
       </c>
       <c r="M124" s="99" t="inlineStr"/>
     </row>
@@ -29345,13 +29823,14 @@
         </is>
       </c>
       <c r="J125" s="141" t="n">
-        <v>3558.61</v>
+        <v>1500</v>
       </c>
       <c r="K125" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L125" s="101" t="n">
-        <v>39</v>
+        <v>1500</v>
+      </c>
+      <c r="L125" s="101">
+        <f>IF(J125&gt;0,(J125-K125)/J125,"")</f>
+        <v/>
       </c>
       <c r="M125" s="102" t="inlineStr"/>
     </row>
@@ -29398,13 +29877,14 @@
         </is>
       </c>
       <c r="J126" s="142" t="n">
-        <v>3558.61</v>
+        <v>1308.5</v>
       </c>
       <c r="K126" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L126" s="98" t="n">
-        <v>39</v>
+        <v>334.01</v>
+      </c>
+      <c r="L126" s="98">
+        <f>IF(J126&gt;0,(J126-K126)/J126,"")</f>
+        <v/>
       </c>
       <c r="M126" s="99" t="inlineStr"/>
     </row>
@@ -29451,13 +29931,14 @@
         </is>
       </c>
       <c r="J127" s="141" t="n">
-        <v>3558.61</v>
+        <v>357</v>
       </c>
       <c r="K127" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L127" s="101" t="n">
-        <v>39</v>
+        <v>357</v>
+      </c>
+      <c r="L127" s="101">
+        <f>IF(J127&gt;0,(J127-K127)/J127,"")</f>
+        <v/>
       </c>
       <c r="M127" s="102" t="inlineStr"/>
     </row>
@@ -29500,13 +29981,14 @@
         </is>
       </c>
       <c r="J128" s="142" t="n">
-        <v>3558.61</v>
+        <v>357</v>
       </c>
       <c r="K128" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L128" s="98" t="n">
-        <v>39</v>
+        <v>357</v>
+      </c>
+      <c r="L128" s="98">
+        <f>IF(J128&gt;0,(J128-K128)/J128,"")</f>
+        <v/>
       </c>
       <c r="M128" s="99" t="inlineStr"/>
     </row>
@@ -29553,13 +30035,14 @@
         </is>
       </c>
       <c r="J129" s="141" t="n">
-        <v>3558.61</v>
+        <v>263.17</v>
       </c>
       <c r="K129" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L129" s="101" t="n">
-        <v>39</v>
+        <v>263.17</v>
+      </c>
+      <c r="L129" s="101">
+        <f>IF(J129&gt;0,(J129-K129)/J129,"")</f>
+        <v/>
       </c>
       <c r="M129" s="102" t="inlineStr">
         <is>
@@ -29606,13 +30089,14 @@
         </is>
       </c>
       <c r="J130" s="142" t="n">
-        <v>3558.61</v>
+        <v>357</v>
       </c>
       <c r="K130" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L130" s="98" t="n">
-        <v>39</v>
+        <v>357</v>
+      </c>
+      <c r="L130" s="98">
+        <f>IF(J130&gt;0,(J130-K130)/J130,"")</f>
+        <v/>
       </c>
       <c r="M130" s="99" t="inlineStr"/>
     </row>
@@ -29655,13 +30139,14 @@
         </is>
       </c>
       <c r="J131" s="141" t="n">
-        <v>3558.61</v>
+        <v>357</v>
       </c>
       <c r="K131" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L131" s="101" t="n">
-        <v>39</v>
+        <v>357</v>
+      </c>
+      <c r="L131" s="101">
+        <f>IF(J131&gt;0,(J131-K131)/J131,"")</f>
+        <v/>
       </c>
       <c r="M131" s="102" t="inlineStr"/>
     </row>
@@ -29704,13 +30189,14 @@
         </is>
       </c>
       <c r="J132" s="142" t="n">
-        <v>3558.61</v>
+        <v>357</v>
       </c>
       <c r="K132" s="143" t="n">
-        <v>1387.86</v>
-      </c>
-      <c r="L132" s="98" t="n">
-        <v>39</v>
+        <v>357</v>
+      </c>
+      <c r="L132" s="98">
+        <f>IF(J132&gt;0,(J132-K132)/J132,"")</f>
+        <v/>
       </c>
       <c r="M132" s="99" t="inlineStr"/>
     </row>
@@ -29767,10 +30253,11 @@
         <v>3500</v>
       </c>
       <c r="K134" s="143" t="n">
-        <v>1365</v>
-      </c>
-      <c r="L134" s="101" t="n">
-        <v>39</v>
+        <v>1700</v>
+      </c>
+      <c r="L134" s="101">
+        <f>IF(J134&gt;0,(J134-K134)/J134,"")</f>
+        <v/>
       </c>
       <c r="M134" s="102" t="inlineStr"/>
     </row>
@@ -29827,10 +30314,11 @@
         <v>3554</v>
       </c>
       <c r="K136" s="143" t="n">
-        <v>2416.72</v>
-      </c>
-      <c r="L136" s="98" t="n">
-        <v>68</v>
+        <v>1924.19</v>
+      </c>
+      <c r="L136" s="98">
+        <f>IF(J136&gt;0,(J136-K136)/J136,"")</f>
+        <v/>
       </c>
       <c r="M136" s="99" t="inlineStr"/>
     </row>
@@ -29883,10 +30371,11 @@
         <v>4598</v>
       </c>
       <c r="K138" s="143" t="n">
-        <v>1195.48</v>
-      </c>
-      <c r="L138" s="101" t="n">
-        <v>26</v>
+        <v>3267</v>
+      </c>
+      <c r="L138" s="101">
+        <f>IF(J138&gt;0,(J138-K138)/J138,"")</f>
+        <v/>
       </c>
       <c r="M138" s="102" t="inlineStr"/>
     </row>
@@ -29940,13 +30429,14 @@
         </is>
       </c>
       <c r="J140" s="142" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K140" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L140" s="98" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L140" s="98">
+        <f>IF(J140&gt;0,(J140-K140)/J140,"")</f>
+        <v/>
       </c>
       <c r="M140" s="99" t="inlineStr"/>
     </row>
@@ -30000,13 +30490,14 @@
         </is>
       </c>
       <c r="J142" s="141" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K142" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L142" s="101" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L142" s="101">
+        <f>IF(J142&gt;0,(J142-K142)/J142,"")</f>
+        <v/>
       </c>
       <c r="M142" s="102" t="inlineStr"/>
     </row>
@@ -30053,13 +30544,14 @@
         </is>
       </c>
       <c r="J143" s="142" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K143" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L143" s="98" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L143" s="98">
+        <f>IF(J143&gt;0,(J143-K143)/J143,"")</f>
+        <v/>
       </c>
       <c r="M143" s="99" t="inlineStr"/>
     </row>
@@ -30106,13 +30598,14 @@
         </is>
       </c>
       <c r="J144" s="141" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K144" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L144" s="101" t="n">
-        <v>39</v>
+        <v>790</v>
+      </c>
+      <c r="L144" s="101">
+        <f>IF(J144&gt;0,(J144-K144)/J144,"")</f>
+        <v/>
       </c>
       <c r="M144" s="102" t="inlineStr"/>
     </row>
@@ -30159,13 +30652,14 @@
         </is>
       </c>
       <c r="J145" s="142" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K145" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L145" s="98" t="n">
-        <v>39</v>
+        <v>790</v>
+      </c>
+      <c r="L145" s="98">
+        <f>IF(J145&gt;0,(J145-K145)/J145,"")</f>
+        <v/>
       </c>
       <c r="M145" s="99" t="inlineStr"/>
     </row>
@@ -30212,13 +30706,14 @@
         </is>
       </c>
       <c r="J146" s="141" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K146" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L146" s="101" t="n">
-        <v>39</v>
+        <v>790</v>
+      </c>
+      <c r="L146" s="101">
+        <f>IF(J146&gt;0,(J146-K146)/J146,"")</f>
+        <v/>
       </c>
       <c r="M146" s="102" t="inlineStr"/>
     </row>
@@ -30265,13 +30760,14 @@
         </is>
       </c>
       <c r="J147" s="142" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K147" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L147" s="98" t="n">
-        <v>39</v>
+        <v>790</v>
+      </c>
+      <c r="L147" s="98">
+        <f>IF(J147&gt;0,(J147-K147)/J147,"")</f>
+        <v/>
       </c>
       <c r="M147" s="99" t="inlineStr"/>
     </row>
@@ -30318,13 +30814,14 @@
         </is>
       </c>
       <c r="J148" s="141" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K148" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L148" s="101" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L148" s="101">
+        <f>IF(J148&gt;0,(J148-K148)/J148,"")</f>
+        <v/>
       </c>
       <c r="M148" s="102" t="inlineStr"/>
     </row>
@@ -30371,13 +30868,14 @@
         </is>
       </c>
       <c r="J149" s="142" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K149" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L149" s="98" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L149" s="98">
+        <f>IF(J149&gt;0,(J149-K149)/J149,"")</f>
+        <v/>
       </c>
       <c r="M149" s="99" t="inlineStr"/>
     </row>
@@ -30424,13 +30922,14 @@
         </is>
       </c>
       <c r="J150" s="141" t="n">
-        <v>4199</v>
+        <v>1185</v>
       </c>
       <c r="K150" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L150" s="101" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L150" s="101">
+        <f>IF(J150&gt;0,(J150-K150)/J150,"")</f>
+        <v/>
       </c>
       <c r="M150" s="102" t="inlineStr"/>
     </row>
@@ -30477,13 +30976,14 @@
         </is>
       </c>
       <c r="J151" s="142" t="n">
-        <v>4199</v>
+        <v>237</v>
       </c>
       <c r="K151" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L151" s="98" t="n">
-        <v>39</v>
+        <v>360.87</v>
+      </c>
+      <c r="L151" s="98">
+        <f>IF(J151&gt;0,(J151-K151)/J151,"")</f>
+        <v/>
       </c>
       <c r="M151" s="99" t="inlineStr"/>
     </row>
@@ -30530,13 +31030,14 @@
         </is>
       </c>
       <c r="J152" s="141" t="n">
-        <v>4199</v>
+        <v>237</v>
       </c>
       <c r="K152" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L152" s="101" t="n">
-        <v>39</v>
+        <v>360.87</v>
+      </c>
+      <c r="L152" s="101">
+        <f>IF(J152&gt;0,(J152-K152)/J152,"")</f>
+        <v/>
       </c>
       <c r="M152" s="102" t="inlineStr"/>
     </row>
@@ -30583,13 +31084,14 @@
         </is>
       </c>
       <c r="J153" s="142" t="n">
-        <v>4199</v>
+        <v>790</v>
       </c>
       <c r="K153" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L153" s="98" t="n">
-        <v>39</v>
+        <v>995</v>
+      </c>
+      <c r="L153" s="98">
+        <f>IF(J153&gt;0,(J153-K153)/J153,"")</f>
+        <v/>
       </c>
       <c r="M153" s="99" t="inlineStr"/>
     </row>
@@ -30636,13 +31138,14 @@
         </is>
       </c>
       <c r="J154" s="141" t="n">
-        <v>4199</v>
+        <v>252.65</v>
       </c>
       <c r="K154" s="143" t="n">
-        <v>1637.61</v>
-      </c>
-      <c r="L154" s="101" t="n">
-        <v>39</v>
+        <v>470.65</v>
+      </c>
+      <c r="L154" s="101">
+        <f>IF(J154&gt;0,(J154-K154)/J154,"")</f>
+        <v/>
       </c>
       <c r="M154" s="102" t="inlineStr"/>
     </row>
@@ -30699,10 +31202,11 @@
         <v>1670</v>
       </c>
       <c r="K156" s="143" t="n">
-        <v>651.3</v>
-      </c>
-      <c r="L156" s="98" t="n">
-        <v>39</v>
+        <v>1670</v>
+      </c>
+      <c r="L156" s="98">
+        <f>IF(J156&gt;0,(J156-K156)/J156,"")</f>
+        <v/>
       </c>
       <c r="M156" s="99" t="inlineStr"/>
     </row>
@@ -30752,10 +31256,11 @@
         <v>1670</v>
       </c>
       <c r="K157" s="143" t="n">
-        <v>651.3</v>
-      </c>
-      <c r="L157" s="101" t="n">
-        <v>39</v>
+        <v>1670</v>
+      </c>
+      <c r="L157" s="101">
+        <f>IF(J157&gt;0,(J157-K157)/J157,"")</f>
+        <v/>
       </c>
       <c r="M157" s="102" t="inlineStr"/>
     </row>
@@ -30812,10 +31317,11 @@
         <v>13500</v>
       </c>
       <c r="K159" s="143" t="n">
-        <v>9180</v>
-      </c>
-      <c r="L159" s="98" t="n">
-        <v>68</v>
+        <v>13500</v>
+      </c>
+      <c r="L159" s="98">
+        <f>IF(J159&gt;0,(J159-K159)/J159,"")</f>
+        <v/>
       </c>
       <c r="M159" s="99" t="inlineStr"/>
     </row>
@@ -30865,10 +31371,11 @@
         <v>19990</v>
       </c>
       <c r="K160" s="143" t="n">
-        <v>13593.2</v>
-      </c>
-      <c r="L160" s="101" t="n">
-        <v>68</v>
+        <v>26246</v>
+      </c>
+      <c r="L160" s="101">
+        <f>IF(J160&gt;0,(J160-K160)/J160,"")</f>
+        <v/>
       </c>
       <c r="M160" s="102" t="inlineStr">
         <is>
@@ -30922,10 +31429,11 @@
         <v>6347.08</v>
       </c>
       <c r="K161" s="143" t="n">
-        <v>1650.24</v>
-      </c>
-      <c r="L161" s="98" t="n">
-        <v>26</v>
+        <v>5095.75</v>
+      </c>
+      <c r="L161" s="98">
+        <f>IF(J161&gt;0,(J161-K161)/J161,"")</f>
+        <v/>
       </c>
       <c r="M161" s="99" t="inlineStr">
         <is>
@@ -30979,10 +31487,11 @@
         <v>10300</v>
       </c>
       <c r="K162" s="143" t="n">
-        <v>7004</v>
-      </c>
-      <c r="L162" s="101" t="n">
-        <v>68</v>
+        <v>6373.43</v>
+      </c>
+      <c r="L162" s="101">
+        <f>IF(J162&gt;0,(J162-K162)/J162,"")</f>
+        <v/>
       </c>
       <c r="M162" s="102" t="inlineStr"/>
     </row>
@@ -31028,10 +31537,11 @@
         <v>10300</v>
       </c>
       <c r="K163" s="143" t="n">
-        <v>2678</v>
-      </c>
-      <c r="L163" s="98" t="n">
-        <v>26</v>
+        <v>6373.43</v>
+      </c>
+      <c r="L163" s="98">
+        <f>IF(J163&gt;0,(J163-K163)/J163,"")</f>
+        <v/>
       </c>
       <c r="M163" s="99" t="inlineStr">
         <is>
@@ -31589,7 +32099,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="90" t="inlineStr">
         <is>
-          <t>27 itens   |   Valor: R$ 6.233,08   |   Desgaste medio: 3,0/5</t>
+          <t>27 itens   |   Valor: R$ 5.785,73   |   Desgaste medio: 3,0/5</t>
         </is>
       </c>
     </row>
@@ -31710,10 +32220,11 @@
         <v>400</v>
       </c>
       <c r="K6" s="143" t="n">
-        <v>156</v>
-      </c>
-      <c r="L6" s="98" t="n">
-        <v>39</v>
+        <v>332.34</v>
+      </c>
+      <c r="L6" s="98">
+        <f>IF(J6&gt;0,(J6-K6)/J6,"")</f>
+        <v/>
       </c>
       <c r="M6" s="99" t="inlineStr"/>
     </row>
@@ -31759,13 +32270,14 @@
         </is>
       </c>
       <c r="J8" s="141" t="n">
-        <v>275</v>
+        <v>245.07</v>
       </c>
       <c r="K8" s="143" t="n">
-        <v>107.25</v>
-      </c>
-      <c r="L8" s="101" t="n">
-        <v>39</v>
+        <v>66.75</v>
+      </c>
+      <c r="L8" s="101">
+        <f>IF(J8&gt;0,(J8-K8)/J8,"")</f>
+        <v/>
       </c>
       <c r="M8" s="102" t="inlineStr"/>
     </row>
@@ -31815,13 +32327,14 @@
         </is>
       </c>
       <c r="J10" s="142" t="n">
-        <v>215.14</v>
+        <v>76</v>
       </c>
       <c r="K10" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L10" s="98" t="n">
-        <v>39</v>
+        <v>66.75</v>
+      </c>
+      <c r="L10" s="98">
+        <f>IF(J10&gt;0,(J10-K10)/J10,"")</f>
+        <v/>
       </c>
       <c r="M10" s="99" t="inlineStr"/>
     </row>
@@ -31864,13 +32377,14 @@
         </is>
       </c>
       <c r="J11" s="141" t="n">
-        <v>215.14</v>
+        <v>145.57</v>
       </c>
       <c r="K11" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L11" s="101" t="n">
-        <v>39</v>
+        <v>66.75</v>
+      </c>
+      <c r="L11" s="101">
+        <f>IF(J11&gt;0,(J11-K11)/J11,"")</f>
+        <v/>
       </c>
       <c r="M11" s="102" t="inlineStr"/>
     </row>
@@ -31913,13 +32427,14 @@
         </is>
       </c>
       <c r="J12" s="142" t="n">
-        <v>215.14</v>
+        <v>145.57</v>
       </c>
       <c r="K12" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L12" s="98" t="n">
-        <v>39</v>
+        <v>66.75</v>
+      </c>
+      <c r="L12" s="98">
+        <f>IF(J12&gt;0,(J12-K12)/J12,"")</f>
+        <v/>
       </c>
       <c r="M12" s="99" t="inlineStr"/>
     </row>
@@ -31962,13 +32477,14 @@
         </is>
       </c>
       <c r="J13" s="141" t="n">
-        <v>215.14</v>
+        <v>145.57</v>
       </c>
       <c r="K13" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L13" s="101" t="n">
-        <v>39</v>
+        <v>27.6</v>
+      </c>
+      <c r="L13" s="101">
+        <f>IF(J13&gt;0,(J13-K13)/J13,"")</f>
+        <v/>
       </c>
       <c r="M13" s="102" t="inlineStr"/>
     </row>
@@ -32014,13 +32530,14 @@
         </is>
       </c>
       <c r="J15" s="142" t="n">
-        <v>215.14</v>
+        <v>145.57</v>
       </c>
       <c r="K15" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L15" s="98" t="n">
-        <v>39</v>
+        <v>27.6</v>
+      </c>
+      <c r="L15" s="98">
+        <f>IF(J15&gt;0,(J15-K15)/J15,"")</f>
+        <v/>
       </c>
       <c r="M15" s="99" t="inlineStr"/>
     </row>
@@ -32073,10 +32590,11 @@
         <v>215.14</v>
       </c>
       <c r="K17" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L17" s="101" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L17" s="101">
+        <f>IF(J17&gt;0,(J17-K17)/J17,"")</f>
+        <v/>
       </c>
       <c r="M17" s="102" t="inlineStr"/>
     </row>
@@ -32122,10 +32640,11 @@
         <v>215.14</v>
       </c>
       <c r="K18" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L18" s="98" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L18" s="98">
+        <f>IF(J18&gt;0,(J18-K18)/J18,"")</f>
+        <v/>
       </c>
       <c r="M18" s="99" t="inlineStr"/>
     </row>
@@ -32171,10 +32690,11 @@
         <v>215.14</v>
       </c>
       <c r="K19" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L19" s="101" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L19" s="101">
+        <f>IF(J19&gt;0,(J19-K19)/J19,"")</f>
+        <v/>
       </c>
       <c r="M19" s="102" t="inlineStr"/>
     </row>
@@ -32220,10 +32740,11 @@
         <v>215.14</v>
       </c>
       <c r="K20" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L20" s="98" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L20" s="98">
+        <f>IF(J20&gt;0,(J20-K20)/J20,"")</f>
+        <v/>
       </c>
       <c r="M20" s="99" t="inlineStr"/>
     </row>
@@ -32269,10 +32790,11 @@
         <v>215.14</v>
       </c>
       <c r="K21" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L21" s="101" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L21" s="101">
+        <f>IF(J21&gt;0,(J21-K21)/J21,"")</f>
+        <v/>
       </c>
       <c r="M21" s="102" t="inlineStr"/>
     </row>
@@ -32318,10 +32840,11 @@
         <v>215.14</v>
       </c>
       <c r="K22" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L22" s="98" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L22" s="98">
+        <f>IF(J22&gt;0,(J22-K22)/J22,"")</f>
+        <v/>
       </c>
       <c r="M22" s="99" t="inlineStr"/>
     </row>
@@ -32367,10 +32890,11 @@
         <v>215.14</v>
       </c>
       <c r="K23" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L23" s="101" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L23" s="101">
+        <f>IF(J23&gt;0,(J23-K23)/J23,"")</f>
+        <v/>
       </c>
       <c r="M23" s="102" t="inlineStr"/>
     </row>
@@ -32416,10 +32940,11 @@
         <v>215.14</v>
       </c>
       <c r="K24" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L24" s="98" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L24" s="98">
+        <f>IF(J24&gt;0,(J24-K24)/J24,"")</f>
+        <v/>
       </c>
       <c r="M24" s="99" t="inlineStr"/>
     </row>
@@ -32465,10 +32990,11 @@
         <v>215.14</v>
       </c>
       <c r="K25" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L25" s="101" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L25" s="101">
+        <f>IF(J25&gt;0,(J25-K25)/J25,"")</f>
+        <v/>
       </c>
       <c r="M25" s="102" t="inlineStr"/>
     </row>
@@ -32514,10 +33040,11 @@
         <v>215.14</v>
       </c>
       <c r="K26" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L26" s="98" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L26" s="98">
+        <f>IF(J26&gt;0,(J26-K26)/J26,"")</f>
+        <v/>
       </c>
       <c r="M26" s="99" t="inlineStr"/>
     </row>
@@ -32563,10 +33090,11 @@
         <v>215.14</v>
       </c>
       <c r="K27" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L27" s="101" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L27" s="101">
+        <f>IF(J27&gt;0,(J27-K27)/J27,"")</f>
+        <v/>
       </c>
       <c r="M27" s="102" t="inlineStr"/>
     </row>
@@ -32612,10 +33140,11 @@
         <v>215.14</v>
       </c>
       <c r="K28" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L28" s="98" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L28" s="98">
+        <f>IF(J28&gt;0,(J28-K28)/J28,"")</f>
+        <v/>
       </c>
       <c r="M28" s="99" t="inlineStr"/>
     </row>
@@ -32661,10 +33190,11 @@
         <v>215.14</v>
       </c>
       <c r="K29" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L29" s="101" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L29" s="101">
+        <f>IF(J29&gt;0,(J29-K29)/J29,"")</f>
+        <v/>
       </c>
       <c r="M29" s="102" t="inlineStr"/>
     </row>
@@ -32710,10 +33240,11 @@
         <v>215.14</v>
       </c>
       <c r="K30" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L30" s="98" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L30" s="98">
+        <f>IF(J30&gt;0,(J30-K30)/J30,"")</f>
+        <v/>
       </c>
       <c r="M30" s="99" t="inlineStr"/>
     </row>
@@ -32759,10 +33290,11 @@
         <v>215.14</v>
       </c>
       <c r="K31" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L31" s="101" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L31" s="101">
+        <f>IF(J31&gt;0,(J31-K31)/J31,"")</f>
+        <v/>
       </c>
       <c r="M31" s="102" t="inlineStr"/>
     </row>
@@ -32808,10 +33340,11 @@
         <v>215.14</v>
       </c>
       <c r="K32" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L32" s="98" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L32" s="98">
+        <f>IF(J32&gt;0,(J32-K32)/J32,"")</f>
+        <v/>
       </c>
       <c r="M32" s="99" t="inlineStr"/>
     </row>
@@ -32857,10 +33390,11 @@
         <v>215.14</v>
       </c>
       <c r="K33" s="143" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="L33" s="101" t="n">
-        <v>39</v>
+        <v>199.9</v>
+      </c>
+      <c r="L33" s="101">
+        <f>IF(J33&gt;0,(J33-K33)/J33,"")</f>
+        <v/>
       </c>
       <c r="M33" s="102" t="inlineStr"/>
     </row>
@@ -32909,10 +33443,11 @@
         <v>275</v>
       </c>
       <c r="K35" s="143" t="n">
-        <v>107.25</v>
-      </c>
-      <c r="L35" s="98" t="n">
-        <v>39</v>
+        <v>275</v>
+      </c>
+      <c r="L35" s="98">
+        <f>IF(J35&gt;0,(J35-K35)/J35,"")</f>
+        <v/>
       </c>
       <c r="M35" s="99" t="inlineStr">
         <is>
@@ -32958,10 +33493,11 @@
         <v>275</v>
       </c>
       <c r="K36" s="143" t="n">
-        <v>107.25</v>
-      </c>
-      <c r="L36" s="101" t="n">
-        <v>39</v>
+        <v>275</v>
+      </c>
+      <c r="L36" s="101">
+        <f>IF(J36&gt;0,(J36-K36)/J36,"")</f>
+        <v/>
       </c>
       <c r="M36" s="102" t="inlineStr">
         <is>
@@ -33007,10 +33543,11 @@
         <v>275</v>
       </c>
       <c r="K37" s="143" t="n">
-        <v>107.25</v>
-      </c>
-      <c r="L37" s="98" t="n">
-        <v>39</v>
+        <v>275</v>
+      </c>
+      <c r="L37" s="98">
+        <f>IF(J37&gt;0,(J37-K37)/J37,"")</f>
+        <v/>
       </c>
       <c r="M37" s="99" t="inlineStr">
         <is>
@@ -33212,7 +33749,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="90" t="inlineStr">
         <is>
-          <t>39 itens   |   Valor: R$ 17.860,75   |   Desgaste medio: 3,0/5</t>
+          <t>43 itens   |   Valor: R$ 17.629,93   |   Desgaste medio: 3,0/5</t>
         </is>
       </c>
     </row>
@@ -33329,10 +33866,11 @@
         <v>1720</v>
       </c>
       <c r="K6" s="143" t="n">
-        <v>670.8</v>
-      </c>
-      <c r="L6" s="98" t="n">
-        <v>39</v>
+        <v>1720</v>
+      </c>
+      <c r="L6" s="98">
+        <f>IF(J6&gt;0,(J6-K6)/J6,"")</f>
+        <v/>
       </c>
       <c r="M6" s="99" t="inlineStr"/>
     </row>
@@ -33378,13 +33916,14 @@
         </is>
       </c>
       <c r="J8" s="141" t="n">
-        <v>884.95</v>
+        <v>346.29</v>
       </c>
       <c r="K8" s="143" t="n">
-        <v>345.13</v>
-      </c>
-      <c r="L8" s="101" t="n">
-        <v>39</v>
+        <v>570.62</v>
+      </c>
+      <c r="L8" s="101">
+        <f>IF(J8&gt;0,(J8-K8)/J8,"")</f>
+        <v/>
       </c>
       <c r="M8" s="102" t="inlineStr"/>
     </row>
@@ -33423,13 +33962,14 @@
         </is>
       </c>
       <c r="J9" s="142" t="n">
-        <v>884.95</v>
+        <v>346.29</v>
       </c>
       <c r="K9" s="143" t="n">
-        <v>345.13</v>
-      </c>
-      <c r="L9" s="98" t="n">
-        <v>39</v>
+        <v>570.62</v>
+      </c>
+      <c r="L9" s="98">
+        <f>IF(J9&gt;0,(J9-K9)/J9,"")</f>
+        <v/>
       </c>
       <c r="M9" s="99" t="inlineStr"/>
     </row>
@@ -33468,13 +34008,14 @@
         </is>
       </c>
       <c r="J10" s="141" t="n">
-        <v>884.95</v>
+        <v>346.29</v>
       </c>
       <c r="K10" s="143" t="n">
-        <v>345.13</v>
-      </c>
-      <c r="L10" s="101" t="n">
-        <v>39</v>
+        <v>570.62</v>
+      </c>
+      <c r="L10" s="101">
+        <f>IF(J10&gt;0,(J10-K10)/J10,"")</f>
+        <v/>
       </c>
       <c r="M10" s="102" t="inlineStr"/>
     </row>
@@ -33523,10 +34064,11 @@
         <v>1499.9</v>
       </c>
       <c r="K12" s="143" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="L12" s="98" t="n">
-        <v>39</v>
+        <v>981.3</v>
+      </c>
+      <c r="L12" s="98">
+        <f>IF(J12&gt;0,(J12-K12)/J12,"")</f>
+        <v/>
       </c>
       <c r="M12" s="99" t="inlineStr"/>
     </row>
@@ -33568,10 +34110,11 @@
         <v>1499.9</v>
       </c>
       <c r="K13" s="143" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="L13" s="101" t="n">
-        <v>39</v>
+        <v>1499.9</v>
+      </c>
+      <c r="L13" s="101">
+        <f>IF(J13&gt;0,(J13-K13)/J13,"")</f>
+        <v/>
       </c>
       <c r="M13" s="102" t="inlineStr"/>
     </row>
@@ -33613,10 +34156,11 @@
         <v>1499.9</v>
       </c>
       <c r="K14" s="143" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="L14" s="98" t="n">
-        <v>39</v>
+        <v>1499.9</v>
+      </c>
+      <c r="L14" s="98">
+        <f>IF(J14&gt;0,(J14-K14)/J14,"")</f>
+        <v/>
       </c>
       <c r="M14" s="99" t="inlineStr"/>
     </row>
@@ -33658,10 +34202,11 @@
         <v>1499.9</v>
       </c>
       <c r="K15" s="143" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="L15" s="101" t="n">
-        <v>39</v>
+        <v>1499.9</v>
+      </c>
+      <c r="L15" s="101">
+        <f>IF(J15&gt;0,(J15-K15)/J15,"")</f>
+        <v/>
       </c>
       <c r="M15" s="102" t="inlineStr"/>
     </row>
@@ -33703,10 +34248,11 @@
         <v>1499.9</v>
       </c>
       <c r="K16" s="143" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="L16" s="98" t="n">
-        <v>39</v>
+        <v>1499.9</v>
+      </c>
+      <c r="L16" s="98">
+        <f>IF(J16&gt;0,(J16-K16)/J16,"")</f>
+        <v/>
       </c>
       <c r="M16" s="99" t="inlineStr"/>
     </row>
@@ -33747,9 +34293,16 @@
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="J18" s="53" t="n"/>
-      <c r="K18" s="122" t="n"/>
-      <c r="L18" s="123" t="n"/>
+      <c r="J18" s="141" t="n">
+        <v>346.29</v>
+      </c>
+      <c r="K18" s="143" t="n">
+        <v>19</v>
+      </c>
+      <c r="L18" s="101">
+        <f>IF(J18&gt;0,(J18-K18)/J18,"")</f>
+        <v/>
+      </c>
       <c r="M18" s="102" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -33782,9 +34335,16 @@
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="J19" s="58" t="n"/>
-      <c r="K19" s="122" t="n"/>
-      <c r="L19" s="124" t="n"/>
+      <c r="J19" s="142" t="n">
+        <v>346.29</v>
+      </c>
+      <c r="K19" s="143" t="n">
+        <v>19</v>
+      </c>
+      <c r="L19" s="98">
+        <f>IF(J19&gt;0,(J19-K19)/J19,"")</f>
+        <v/>
+      </c>
       <c r="M19" s="99" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -33817,9 +34377,16 @@
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="J20" s="53" t="n"/>
-      <c r="K20" s="122" t="n"/>
-      <c r="L20" s="123" t="n"/>
+      <c r="J20" s="141" t="n">
+        <v>346.29</v>
+      </c>
+      <c r="K20" s="143" t="n">
+        <v>19</v>
+      </c>
+      <c r="L20" s="101">
+        <f>IF(J20&gt;0,(J20-K20)/J20,"")</f>
+        <v/>
+      </c>
       <c r="M20" s="102" t="inlineStr"/>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -33852,9 +34419,16 @@
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="J21" s="58" t="n"/>
-      <c r="K21" s="122" t="n"/>
-      <c r="L21" s="124" t="n"/>
+      <c r="J21" s="142" t="n">
+        <v>346.29</v>
+      </c>
+      <c r="K21" s="143" t="n">
+        <v>19</v>
+      </c>
+      <c r="L21" s="98">
+        <f>IF(J21&gt;0,(J21-K21)/J21,"")</f>
+        <v/>
+      </c>
       <c r="M21" s="99" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
@@ -33906,10 +34480,11 @@
         <v>270</v>
       </c>
       <c r="K23" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L23" s="101" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L23" s="101">
+        <f>IF(J23&gt;0,(J23-K23)/J23,"")</f>
+        <v/>
       </c>
       <c r="M23" s="102" t="inlineStr"/>
     </row>
@@ -33955,10 +34530,11 @@
         <v>270</v>
       </c>
       <c r="K24" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L24" s="98" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L24" s="98">
+        <f>IF(J24&gt;0,(J24-K24)/J24,"")</f>
+        <v/>
       </c>
       <c r="M24" s="99" t="inlineStr"/>
     </row>
@@ -34004,10 +34580,11 @@
         <v>270</v>
       </c>
       <c r="K25" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L25" s="101" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L25" s="101">
+        <f>IF(J25&gt;0,(J25-K25)/J25,"")</f>
+        <v/>
       </c>
       <c r="M25" s="102" t="inlineStr"/>
     </row>
@@ -34053,10 +34630,11 @@
         <v>270</v>
       </c>
       <c r="K26" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L26" s="98" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L26" s="98">
+        <f>IF(J26&gt;0,(J26-K26)/J26,"")</f>
+        <v/>
       </c>
       <c r="M26" s="99" t="inlineStr"/>
     </row>
@@ -34102,10 +34680,11 @@
         <v>270</v>
       </c>
       <c r="K27" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L27" s="101" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L27" s="101">
+        <f>IF(J27&gt;0,(J27-K27)/J27,"")</f>
+        <v/>
       </c>
       <c r="M27" s="102" t="inlineStr"/>
     </row>
@@ -34151,10 +34730,11 @@
         <v>270</v>
       </c>
       <c r="K28" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L28" s="98" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L28" s="98">
+        <f>IF(J28&gt;0,(J28-K28)/J28,"")</f>
+        <v/>
       </c>
       <c r="M28" s="99" t="inlineStr"/>
     </row>
@@ -34200,10 +34780,11 @@
         <v>270</v>
       </c>
       <c r="K29" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L29" s="101" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L29" s="101">
+        <f>IF(J29&gt;0,(J29-K29)/J29,"")</f>
+        <v/>
       </c>
       <c r="M29" s="102" t="inlineStr"/>
     </row>
@@ -34249,10 +34830,11 @@
         <v>270</v>
       </c>
       <c r="K30" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L30" s="98" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L30" s="98">
+        <f>IF(J30&gt;0,(J30-K30)/J30,"")</f>
+        <v/>
       </c>
       <c r="M30" s="99" t="inlineStr"/>
     </row>
@@ -34298,10 +34880,11 @@
         <v>270</v>
       </c>
       <c r="K31" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L31" s="101" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L31" s="101">
+        <f>IF(J31&gt;0,(J31-K31)/J31,"")</f>
+        <v/>
       </c>
       <c r="M31" s="102" t="inlineStr"/>
     </row>
@@ -34347,10 +34930,11 @@
         <v>270</v>
       </c>
       <c r="K32" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L32" s="98" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L32" s="98">
+        <f>IF(J32&gt;0,(J32-K32)/J32,"")</f>
+        <v/>
       </c>
       <c r="M32" s="99" t="inlineStr"/>
     </row>
@@ -34396,10 +34980,11 @@
         <v>270</v>
       </c>
       <c r="K33" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L33" s="101" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L33" s="101">
+        <f>IF(J33&gt;0,(J33-K33)/J33,"")</f>
+        <v/>
       </c>
       <c r="M33" s="102" t="inlineStr"/>
     </row>
@@ -34445,10 +35030,11 @@
         <v>270</v>
       </c>
       <c r="K34" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L34" s="98" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L34" s="98">
+        <f>IF(J34&gt;0,(J34-K34)/J34,"")</f>
+        <v/>
       </c>
       <c r="M34" s="99" t="inlineStr"/>
     </row>
@@ -34494,10 +35080,11 @@
         <v>270</v>
       </c>
       <c r="K35" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L35" s="101" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L35" s="101">
+        <f>IF(J35&gt;0,(J35-K35)/J35,"")</f>
+        <v/>
       </c>
       <c r="M35" s="102" t="inlineStr"/>
     </row>
@@ -34543,10 +35130,11 @@
         <v>270</v>
       </c>
       <c r="K36" s="143" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="L36" s="98" t="n">
-        <v>39</v>
+        <v>159.95</v>
+      </c>
+      <c r="L36" s="98">
+        <f>IF(J36&gt;0,(J36-K36)/J36,"")</f>
+        <v/>
       </c>
       <c r="M36" s="99" t="inlineStr"/>
     </row>
@@ -34599,10 +35187,11 @@
         <v>137.9</v>
       </c>
       <c r="K38" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L38" s="101" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L38" s="101">
+        <f>IF(J38&gt;0,(J38-K38)/J38,"")</f>
+        <v/>
       </c>
       <c r="M38" s="102" t="inlineStr"/>
     </row>
@@ -34648,10 +35237,11 @@
         <v>137.9</v>
       </c>
       <c r="K39" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L39" s="98" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L39" s="98">
+        <f>IF(J39&gt;0,(J39-K39)/J39,"")</f>
+        <v/>
       </c>
       <c r="M39" s="99" t="inlineStr"/>
     </row>
@@ -34697,10 +35287,11 @@
         <v>137.9</v>
       </c>
       <c r="K40" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L40" s="101" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L40" s="101">
+        <f>IF(J40&gt;0,(J40-K40)/J40,"")</f>
+        <v/>
       </c>
       <c r="M40" s="102" t="inlineStr"/>
     </row>
@@ -34746,10 +35337,11 @@
         <v>137.9</v>
       </c>
       <c r="K41" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L41" s="98" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L41" s="98">
+        <f>IF(J41&gt;0,(J41-K41)/J41,"")</f>
+        <v/>
       </c>
       <c r="M41" s="99" t="inlineStr"/>
     </row>
@@ -34795,10 +35387,11 @@
         <v>137.9</v>
       </c>
       <c r="K42" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L42" s="101" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L42" s="101">
+        <f>IF(J42&gt;0,(J42-K42)/J42,"")</f>
+        <v/>
       </c>
       <c r="M42" s="102" t="inlineStr"/>
     </row>
@@ -34844,10 +35437,11 @@
         <v>137.9</v>
       </c>
       <c r="K43" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L43" s="98" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L43" s="98">
+        <f>IF(J43&gt;0,(J43-K43)/J43,"")</f>
+        <v/>
       </c>
       <c r="M43" s="99" t="inlineStr"/>
     </row>
@@ -34893,10 +35487,11 @@
         <v>137.9</v>
       </c>
       <c r="K44" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L44" s="101" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L44" s="101">
+        <f>IF(J44&gt;0,(J44-K44)/J44,"")</f>
+        <v/>
       </c>
       <c r="M44" s="102" t="inlineStr"/>
     </row>
@@ -34942,10 +35537,11 @@
         <v>137.9</v>
       </c>
       <c r="K45" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L45" s="98" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L45" s="98">
+        <f>IF(J45&gt;0,(J45-K45)/J45,"")</f>
+        <v/>
       </c>
       <c r="M45" s="99" t="inlineStr"/>
     </row>
@@ -34991,10 +35587,11 @@
         <v>137.9</v>
       </c>
       <c r="K46" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L46" s="101" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L46" s="101">
+        <f>IF(J46&gt;0,(J46-K46)/J46,"")</f>
+        <v/>
       </c>
       <c r="M46" s="102" t="inlineStr"/>
     </row>
@@ -35040,10 +35637,11 @@
         <v>137.9</v>
       </c>
       <c r="K47" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L47" s="98" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L47" s="98">
+        <f>IF(J47&gt;0,(J47-K47)/J47,"")</f>
+        <v/>
       </c>
       <c r="M47" s="99" t="inlineStr"/>
     </row>
@@ -35089,10 +35687,11 @@
         <v>137.9</v>
       </c>
       <c r="K48" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L48" s="101" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L48" s="101">
+        <f>IF(J48&gt;0,(J48-K48)/J48,"")</f>
+        <v/>
       </c>
       <c r="M48" s="102" t="inlineStr"/>
     </row>
@@ -35138,10 +35737,11 @@
         <v>137.9</v>
       </c>
       <c r="K49" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L49" s="98" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L49" s="98">
+        <f>IF(J49&gt;0,(J49-K49)/J49,"")</f>
+        <v/>
       </c>
       <c r="M49" s="99" t="inlineStr"/>
     </row>
@@ -35187,10 +35787,11 @@
         <v>137.9</v>
       </c>
       <c r="K50" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L50" s="101" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L50" s="101">
+        <f>IF(J50&gt;0,(J50-K50)/J50,"")</f>
+        <v/>
       </c>
       <c r="M50" s="102" t="inlineStr"/>
     </row>
@@ -35236,10 +35837,11 @@
         <v>137.9</v>
       </c>
       <c r="K51" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L51" s="98" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L51" s="98">
+        <f>IF(J51&gt;0,(J51-K51)/J51,"")</f>
+        <v/>
       </c>
       <c r="M51" s="99" t="inlineStr"/>
     </row>
@@ -35285,10 +35887,11 @@
         <v>137.9</v>
       </c>
       <c r="K52" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L52" s="101" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L52" s="101">
+        <f>IF(J52&gt;0,(J52-K52)/J52,"")</f>
+        <v/>
       </c>
       <c r="M52" s="102" t="inlineStr"/>
     </row>
@@ -35334,10 +35937,11 @@
         <v>137.9</v>
       </c>
       <c r="K53" s="143" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="L53" s="98" t="n">
-        <v>39</v>
+        <v>137.9</v>
+      </c>
+      <c r="L53" s="98">
+        <f>IF(J53&gt;0,(J53-K53)/J53,"")</f>
+        <v/>
       </c>
       <c r="M53" s="99" t="inlineStr"/>
     </row>
@@ -35375,8 +35979,8 @@
   <autoFilter ref="A4:M4"/>
   <mergeCells count="10">
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A5:M5"/>
     <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A5:M5"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A17:M17"/>
@@ -35668,10 +36272,11 @@
         <v>565</v>
       </c>
       <c r="K6" s="143" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="L6" s="98" t="n">
-        <v>26</v>
+        <v>528.85</v>
+      </c>
+      <c r="L6" s="98">
+        <f>IF(J6&gt;0,(J6-K6)/J6,"")</f>
+        <v/>
       </c>
       <c r="M6" s="99" t="inlineStr"/>
     </row>
@@ -35713,10 +36318,11 @@
         <v>565</v>
       </c>
       <c r="K7" s="143" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="L7" s="101" t="n">
-        <v>26</v>
+        <v>528.85</v>
+      </c>
+      <c r="L7" s="101">
+        <f>IF(J7&gt;0,(J7-K7)/J7,"")</f>
+        <v/>
       </c>
       <c r="M7" s="102" t="inlineStr"/>
     </row>
@@ -35765,10 +36371,11 @@
         <v>565</v>
       </c>
       <c r="K9" s="143" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="L9" s="98" t="n">
-        <v>26</v>
+        <v>528.85</v>
+      </c>
+      <c r="L9" s="98">
+        <f>IF(J9&gt;0,(J9-K9)/J9,"")</f>
+        <v/>
       </c>
       <c r="M9" s="99" t="inlineStr"/>
     </row>
@@ -35821,10 +36428,11 @@
         <v>565</v>
       </c>
       <c r="K11" s="143" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="L11" s="101" t="n">
-        <v>26</v>
+        <v>15.6</v>
+      </c>
+      <c r="L11" s="101">
+        <f>IF(J11&gt;0,(J11-K11)/J11,"")</f>
+        <v/>
       </c>
       <c r="M11" s="102" t="inlineStr"/>
     </row>
@@ -35870,10 +36478,11 @@
         <v>565</v>
       </c>
       <c r="K12" s="143" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="L12" s="98" t="n">
-        <v>26</v>
+        <v>17</v>
+      </c>
+      <c r="L12" s="98">
+        <f>IF(J12&gt;0,(J12-K12)/J12,"")</f>
+        <v/>
       </c>
       <c r="M12" s="99" t="inlineStr"/>
     </row>
@@ -35930,10 +36539,11 @@
         <v>1420</v>
       </c>
       <c r="K14" s="143" t="n">
-        <v>369.2</v>
-      </c>
-      <c r="L14" s="101" t="n">
-        <v>26</v>
+        <v>1420</v>
+      </c>
+      <c r="L14" s="101">
+        <f>IF(J14&gt;0,(J14-K14)/J14,"")</f>
+        <v/>
       </c>
       <c r="M14" s="102" t="inlineStr"/>
     </row>
@@ -35975,10 +36585,11 @@
         <v>565</v>
       </c>
       <c r="K15" s="143" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="L15" s="98" t="n">
-        <v>26</v>
+        <v>565</v>
+      </c>
+      <c r="L15" s="98">
+        <f>IF(J15&gt;0,(J15-K15)/J15,"")</f>
+        <v/>
       </c>
       <c r="M15" s="99" t="inlineStr"/>
     </row>
@@ -36024,10 +36635,11 @@
         <v>565</v>
       </c>
       <c r="K16" s="143" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="L16" s="101" t="n">
-        <v>26</v>
+        <v>990</v>
+      </c>
+      <c r="L16" s="101">
+        <f>IF(J16&gt;0,(J16-K16)/J16,"")</f>
+        <v/>
       </c>
       <c r="M16" s="102" t="inlineStr"/>
     </row>
@@ -36073,10 +36685,11 @@
         <v>565</v>
       </c>
       <c r="K17" s="143" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="L17" s="98" t="n">
-        <v>26</v>
+        <v>990</v>
+      </c>
+      <c r="L17" s="98">
+        <f>IF(J17&gt;0,(J17-K17)/J17,"")</f>
+        <v/>
       </c>
       <c r="M17" s="99" t="inlineStr"/>
     </row>
@@ -36122,10 +36735,11 @@
         <v>226</v>
       </c>
       <c r="K18" s="143" t="n">
-        <v>58.76</v>
-      </c>
-      <c r="L18" s="101" t="n">
-        <v>26</v>
+        <v>375</v>
+      </c>
+      <c r="L18" s="101">
+        <f>IF(J18&gt;0,(J18-K18)/J18,"")</f>
+        <v/>
       </c>
       <c r="M18" s="102" t="inlineStr"/>
     </row>
@@ -36175,10 +36789,11 @@
         <v>1420</v>
       </c>
       <c r="K19" s="143" t="n">
-        <v>369.2</v>
-      </c>
-      <c r="L19" s="98" t="n">
-        <v>26</v>
+        <v>1420</v>
+      </c>
+      <c r="L19" s="98">
+        <f>IF(J19&gt;0,(J19-K19)/J19,"")</f>
+        <v/>
       </c>
       <c r="M19" s="99" t="inlineStr"/>
     </row>
@@ -36224,10 +36839,11 @@
         <v>260</v>
       </c>
       <c r="K20" s="143" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="L20" s="101" t="n">
-        <v>26</v>
+        <v>375</v>
+      </c>
+      <c r="L20" s="101">
+        <f>IF(J20&gt;0,(J20-K20)/J20,"")</f>
+        <v/>
       </c>
       <c r="M20" s="102" t="inlineStr"/>
     </row>
@@ -36277,10 +36893,11 @@
         <v>595</v>
       </c>
       <c r="K21" s="143" t="n">
-        <v>154.7</v>
-      </c>
-      <c r="L21" s="98" t="n">
-        <v>26</v>
+        <v>595</v>
+      </c>
+      <c r="L21" s="98">
+        <f>IF(J21&gt;0,(J21-K21)/J21,"")</f>
+        <v/>
       </c>
       <c r="M21" s="99" t="inlineStr"/>
     </row>
@@ -36462,7 +37079,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="90" t="inlineStr">
         <is>
-          <t>9 itens   |   Valor: R$ 13.146,12   |   Desgaste medio: 3,0/5</t>
+          <t>9 itens   |   Valor: R$ 13.022,82   |   Desgaste medio: 3,0/5</t>
         </is>
       </c>
     </row>
@@ -36584,13 +37201,14 @@
         </is>
       </c>
       <c r="J6" s="142" t="n">
-        <v>1096.7</v>
+        <v>943.4</v>
       </c>
       <c r="K6" s="143" t="n">
-        <v>427.71</v>
-      </c>
-      <c r="L6" s="98" t="n">
-        <v>39</v>
+        <v>1999</v>
+      </c>
+      <c r="L6" s="98">
+        <f>IF(J6&gt;0,(J6-K6)/J6,"")</f>
+        <v/>
       </c>
       <c r="M6" s="99" t="inlineStr"/>
     </row>
@@ -36647,10 +37265,11 @@
         <v>2484.68</v>
       </c>
       <c r="K8" s="143" t="n">
-        <v>969.03</v>
-      </c>
-      <c r="L8" s="101" t="n">
-        <v>39</v>
+        <v>2026</v>
+      </c>
+      <c r="L8" s="101">
+        <f>IF(J8&gt;0,(J8-K8)/J8,"")</f>
+        <v/>
       </c>
       <c r="M8" s="102" t="inlineStr"/>
     </row>
@@ -36700,10 +37319,11 @@
         <v>1250</v>
       </c>
       <c r="K9" s="143" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="L9" s="98" t="n">
-        <v>39</v>
+        <v>1999</v>
+      </c>
+      <c r="L9" s="98">
+        <f>IF(J9&gt;0,(J9-K9)/J9,"")</f>
+        <v/>
       </c>
       <c r="M9" s="99" t="inlineStr"/>
     </row>
@@ -36749,10 +37369,11 @@
         <v>3719.35</v>
       </c>
       <c r="K10" s="143" t="n">
-        <v>1450.55</v>
-      </c>
-      <c r="L10" s="101" t="n">
-        <v>39</v>
+        <v>2053</v>
+      </c>
+      <c r="L10" s="101">
+        <f>IF(J10&gt;0,(J10-K10)/J10,"")</f>
+        <v/>
       </c>
       <c r="M10" s="102" t="inlineStr"/>
     </row>
@@ -36809,10 +37430,11 @@
         <v>370</v>
       </c>
       <c r="K12" s="143" t="n">
-        <v>144.3</v>
-      </c>
-      <c r="L12" s="98" t="n">
-        <v>39</v>
+        <v>382.49</v>
+      </c>
+      <c r="L12" s="98">
+        <f>IF(J12&gt;0,(J12-K12)/J12,"")</f>
+        <v/>
       </c>
       <c r="M12" s="99" t="inlineStr"/>
     </row>
@@ -36859,13 +37481,14 @@
         </is>
       </c>
       <c r="J13" s="141" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="K13" s="143" t="n">
-        <v>144.3</v>
-      </c>
-      <c r="L13" s="101" t="n">
-        <v>39</v>
+        <v>2243</v>
+      </c>
+      <c r="L13" s="101">
+        <f>IF(J13&gt;0,(J13-K13)/J13,"")</f>
+        <v/>
       </c>
       <c r="M13" s="102" t="inlineStr"/>
     </row>
@@ -36918,10 +37541,11 @@
         <v>943.4</v>
       </c>
       <c r="K15" s="143" t="n">
-        <v>367.93</v>
-      </c>
-      <c r="L15" s="98" t="n">
-        <v>39</v>
+        <v>943.4</v>
+      </c>
+      <c r="L15" s="98">
+        <f>IF(J15&gt;0,(J15-K15)/J15,"")</f>
+        <v/>
       </c>
       <c r="M15" s="99" t="inlineStr"/>
     </row>
@@ -36970,10 +37594,11 @@
         <v>62.99</v>
       </c>
       <c r="K17" s="143" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="L17" s="101" t="n">
-        <v>39</v>
+        <v>62.99</v>
+      </c>
+      <c r="L17" s="101">
+        <f>IF(J17&gt;0,(J17-K17)/J17,"")</f>
+        <v/>
       </c>
       <c r="M17" s="102" t="inlineStr"/>
     </row>
@@ -37030,10 +37655,11 @@
         <v>2849</v>
       </c>
       <c r="K19" s="143" t="n">
-        <v>1111.11</v>
-      </c>
-      <c r="L19" s="98" t="n">
-        <v>39</v>
+        <v>3299.99</v>
+      </c>
+      <c r="L19" s="98">
+        <f>IF(J19&gt;0,(J19-K19)/J19,"")</f>
+        <v/>
       </c>
       <c r="M19" s="99" t="inlineStr"/>
     </row>
@@ -37072,8 +37698,8 @@
   <mergeCells count="10">
     <mergeCell ref="A14:M14"/>
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A5:M5"/>
     <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A5:M5"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="A21:F21"/>
